--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/01-agenda-de-prazos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/01-agenda-de-prazos.xlsx
@@ -240,7 +240,9 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -937,7 +939,7 @@
     <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5">
         <f>Config!$B$4&amp;" · Painel de prazos · "&amp;TEXT(Config!$B$5,"dd/mm/yyyy")</f>
         <v/>
@@ -2166,7 +2168,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="33">
+  <mergeCells count="34">
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A49:B49"/>
@@ -2195,6 +2197,7 @@
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A1:L1"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="K4:L4"/>
@@ -2243,7 +2246,7 @@
     <col width="4" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Configurações</t>
@@ -2477,8 +2480,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2505,7 +2509,7 @@
     <col hidden="1" width="6" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Prazos</t>
@@ -11727,7 +11731,8 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <autoFilter ref="A4:I404"/>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:I404">

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/01-agenda-de-prazos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/01-agenda-de-prazos.xlsx
@@ -834,7 +834,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Copie a tabela "O que vence primeiro" e use o prompt "Prazos 02: montar a agenda da semana por responsável" da biblioteca do kit.</t>
+          <t>Copie a tabela "O que vence primeiro" e use o prompt "Prazos 04 · Distribuir a semana entre as pessoas" da biblioteca do kit.</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/01-agenda-de-prazos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/01-agenda-de-prazos.xlsx
@@ -733,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -817,94 +817,106 @@
     <row r="9" ht="46" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Limite</t>
+          <t>Exemplo</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>A planilha organiza e avisa. A contagem do prazo, a conferência da data na fonte oficial e o cumprimento continuam sendo responsabilidade de quem responde pelo caso.</t>
+          <t>Os prazos do exemplo são os dos 38 casos da planilha 13 · Carteira (a 13 é a fonte do cadastro de casos); o prazo principal de cada caso é a mesma "próxima ação" da planilha 02. Audiência já realizada não conta como atraso: marque Feito.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Com a IA</t>
+          <t>Limite</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Copie a tabela "O que vence primeiro" e use o prompt "Prazos 04 · Distribuir a semana entre as pessoas" da biblioteca do kit.</t>
+          <t>A planilha organiza e avisa. A contagem do prazo, a conferência da data na fonte oficial e o cumprimento continuam sendo responsabilidade de quem responde pelo caso.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Legenda</t>
+          <t>Com a IA</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Células amarelas: você preenche. Brancas: calculadas. Não é preciso mexer em nada fora do amarelo.</t>
+          <t>Copie a tabela "O que vence primeiro" e use o prompt "Prazos 04 · Distribuir a semana entre as pessoas" da biblioteca do kit.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="46" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Proteção</t>
+          <t>Legenda</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Fórmulas protegidas sem senha. Para editar: Revisar &gt; Desproteger planilha (Excel) ou Dados &gt; Proteger intervalos (Google Sheets).</t>
+          <t>Células amarelas: você preenche. Brancas: calculadas. Não é preciso mexer em nada fora do amarelo.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Requisitos</t>
+          <t>Proteção</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Excel 2019 ou mais novo, Microsoft 365 ou Google Sheets. No celular abre nos aplicativos; para preencher, use o computador.</t>
+          <t>Fórmulas protegidas sem senha. Para editar: Revisar &gt; Desproteger planilha (Excel) ou Dados &gt; Proteger intervalos (Google Sheets).</t>
         </is>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Google Sheets</t>
+          <t>Requisitos</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Excel 2016 ou mais novo, Microsoft 365 ou Google Sheets (só funções do Excel 2007+; nada de MÍNIMOSES, MÁXIMOSES ou UNIRTEXTO). No celular abre nos aplicativos; para preencher, use o computador.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Exemplos</t>
+          <t>Google Sheets</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar. Datas de prazo do exemplo são relativas a hoje.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>Exemplos</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar. Datas de prazo do exemplo são relativas a hoje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -922,7 +934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -940,9 +952,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5">
+      <c r="A1" s="5" t="str">
         <f>Config!$B$4&amp;" · Painel de prazos · "&amp;TEXT(Config!$B$5,"dd/mm/yyyy")</f>
-        <v/>
+        <v>Ferraz &amp; Lima Advocacia (exemplo fictício) · Painel de prazos · 14/09/2026</v>
       </c>
     </row>
     <row r="2">
@@ -965,14 +977,14 @@
         </is>
       </c>
       <c r="D4" s="10" t="n"/>
-      <c r="E4" s="11">
+      <c r="E4" s="11" t="str">
         <f>"Próximos "&amp;Config!$B$6&amp;" dias"</f>
-        <v/>
+        <v>Próximos 7 dias</v>
       </c>
       <c r="F4" s="12" t="n"/>
-      <c r="G4" s="13">
+      <c r="G4" s="13" t="str">
         <f>"De "&amp;(Config!$B$6+1)&amp;" a "&amp;Config!$B$7&amp;" dias"</f>
-        <v/>
+        <v>De 8 a 30 dias</v>
       </c>
       <c r="H4" s="14" t="n"/>
       <c r="I4" s="13" t="inlineStr">
@@ -991,32 +1003,32 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="17">
         <f>COUNTIFS(Prazos!$I$5:$I$404,"Atrasado")</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="18">
         <f>COUNTIFS(Prazos!$I$5:$I$404,"Hoje")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="19">
         <f>COUNTIFS(Prazos!$I$5:$I$404,"Até "&amp;Config!$B$6&amp;" dias")</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="20">
         <f>COUNTIFS(Prazos!$I$5:$I$404,"Até "&amp;Config!$B$7&amp;" dias")</f>
-        <v/>
+        <v>13</v>
       </c>
       <c r="H5" s="14" t="n"/>
       <c r="I5" s="20">
         <f>COUNTIF(Prazos!$J$5:$J$404,"&gt;0")+COUNTIFS(Prazos!$I$5:$I$404,"Sem data")</f>
-        <v/>
+        <v>36</v>
       </c>
       <c r="J5" s="14" t="n"/>
       <c r="K5" s="21">
         <f>COUNTIFS(Prazos!$I$5:$I$404,"Feito")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="L5" s="16" t="n"/>
     </row>
@@ -1030,7 +1042,7 @@
     <row r="8">
       <c r="A8" s="23" t="inlineStr">
         <is>
-          <t>Ordem: atrasados (mais tempo de atraso primeiro), hoje, depois os mais próximos. Mostra os 15 primeiros; os demais ficam na aba Prazos, que pode ser filtrada por situação.</t>
+          <t>Ordem: atrasados (mais tempo de atraso primeiro), hoje, depois os mais próximos. Mostra os 30 primeiros (cabe a semana inteira); os demais ficam na aba Prazos, que pode ser filtrada por situação.</t>
         </is>
       </c>
     </row>
@@ -1080,1087 +1092,1582 @@
       <c r="A10" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,1)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,1),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,1),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="C10" s="26">
+        <v>7099226-69.2026.8.26.0433</v>
+      </c>
+      <c r="C10" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,1)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,1),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,1),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="D10" s="26">
+        <v>Luciana Farias</v>
+      </c>
+      <c r="D10" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,1)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,1),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,1),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Juntada de documentos</v>
       </c>
       <c r="E10" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,1)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,1),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,1),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>46273.0</v>
       </c>
       <c r="F10" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,1)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,1),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,1),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="G10" s="25">
+        <v>-6</v>
+      </c>
+      <c r="G10" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,1)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,1),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,1),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="H10" s="25">
+        <v>Atrasado</v>
+      </c>
+      <c r="H10" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,1)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,1),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,1),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Júlia Prado</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,2)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,2),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,2),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="C11" s="26">
+        <v>CONS-2026-06</v>
+      </c>
+      <c r="C11" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,2)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,2),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,2),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="D11" s="26">
+        <v>Transportadora Rota Sul</v>
+      </c>
+      <c r="D11" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,2)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,2),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,2),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Reunião com cliente</v>
       </c>
       <c r="E11" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,2)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,2),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,2),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>46274.0</v>
       </c>
       <c r="F11" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,2)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,2),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,2),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="G11" s="25">
+        <v>-5</v>
+      </c>
+      <c r="G11" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,2)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,2),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,2),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="H11" s="25">
+        <v>Atrasado</v>
+      </c>
+      <c r="H11" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,2)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,2),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,2),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Rafael Lima</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,3)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,3),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,3),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="C12" s="26">
+        <v>5900991-46.2026.8.26.0469</v>
+      </c>
+      <c r="C12" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,3)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,3),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,3),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="D12" s="26">
+        <v>José Antônio Ribeiro</v>
+      </c>
+      <c r="D12" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,3)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,3),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,3),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Manifestação sobre laudo</v>
       </c>
       <c r="E12" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,3)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,3),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,3),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>46275.0</v>
       </c>
       <c r="F12" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,3)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,3),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,3),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="G12" s="25">
+        <v>-4</v>
+      </c>
+      <c r="G12" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,3)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,3),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,3),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="H12" s="25">
+        <v>Atrasado</v>
+      </c>
+      <c r="H12" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,3)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,3),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,3),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Rafael Lima</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,4)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,4),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,4),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="C13" s="26">
+        <v>9586960-92.2026.8.26.0106</v>
+      </c>
+      <c r="C13" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,4)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,4),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,4),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="D13" s="26">
+        <v>Construtora Horizonte</v>
+      </c>
+      <c r="D13" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,4)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,4),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,4),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Réplica</v>
       </c>
       <c r="E13" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,4)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,4),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,4),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>46276.0</v>
       </c>
       <c r="F13" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,4)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,4),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,4),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="G13" s="25">
+        <v>-3</v>
+      </c>
+      <c r="G13" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,4)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,4),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,4),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="H13" s="25">
+        <v>Atrasado</v>
+      </c>
+      <c r="H13" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,4)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,4),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,4),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Marina Ferraz</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,5)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,5),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,5),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="C14" s="26">
+        <v>9616569-91.2026.8.26.0079</v>
+      </c>
+      <c r="C14" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,5)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,5),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,5),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="D14" s="26">
+        <v>Patrícia Gomes</v>
+      </c>
+      <c r="D14" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,5)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,5),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,5),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Impugnação</v>
       </c>
       <c r="E14" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,5)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,5),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,5),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>46277.0</v>
       </c>
       <c r="F14" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,5)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,5),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,5),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="G14" s="25">
+        <v>-2</v>
+      </c>
+      <c r="G14" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,5)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,5),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,5),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="H14" s="25">
+        <v>Atrasado</v>
+      </c>
+      <c r="H14" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,5)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,5),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,5),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Marina Ferraz</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,6)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,6),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,6),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="C15" s="26">
+        <v>5025425-10.2025.8.26.0629</v>
+      </c>
+      <c r="C15" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,6)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,6),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,6),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="D15" s="26">
+        <v>Roberto Almeida</v>
+      </c>
+      <c r="D15" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,6)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,6),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,6),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Embargos de declaração</v>
       </c>
       <c r="E15" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,6)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,6),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,6),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>46278.0</v>
       </c>
       <c r="F15" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,6)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,6),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,6),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="G15" s="25">
+        <v>-1</v>
+      </c>
+      <c r="G15" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,6)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,6),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,6),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="25">
+        <v>Atrasado</v>
+      </c>
+      <c r="H15" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,6)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,6),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,6),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Marina Ferraz</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="B16" s="26">
+      <c r="B16" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,7)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,7),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,7),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="C16" s="26">
+        <v>9605863-76.2026.8.26.0026</v>
+      </c>
+      <c r="C16" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,7)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,7),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,7),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="D16" s="26">
+        <v>Marcos Vinícius Teles</v>
+      </c>
+      <c r="D16" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,7)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,7),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,7),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Manifestação sobre o recurso</v>
       </c>
       <c r="E16" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,7)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,7),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,7),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>46278.0</v>
       </c>
       <c r="F16" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,7)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,7),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,7),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="G16" s="25">
+        <v>-1</v>
+      </c>
+      <c r="G16" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,7)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,7),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,7),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="25">
+        <v>Atrasado</v>
+      </c>
+      <c r="H16" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,7)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,7),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,7),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Rafael Lima</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="B17" s="26">
+      <c r="B17" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,8)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,8),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,8),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="C17" s="26">
+        <v>CONS-2026-03</v>
+      </c>
+      <c r="C17" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,8)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,8),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,8),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="D17" s="26">
+        <v>Marcos Vinícius Teles</v>
+      </c>
+      <c r="D17" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,8)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,8),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,8),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Entrega de parecer</v>
       </c>
       <c r="E17" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,8)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,8),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,8),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>46279.0</v>
       </c>
       <c r="F17" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,8)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,8),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,8),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="G17" s="25">
+        <v>0</v>
+      </c>
+      <c r="G17" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,8)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,8),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,8),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="25">
+        <v>Hoje</v>
+      </c>
+      <c r="H17" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,8)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,8),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,8),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Rafael Lima</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="B18" s="26">
+      <c r="B18" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,9)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,9),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,9),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="C18" s="26">
+        <v>2645033-67.2026.8.26.0012</v>
+      </c>
+      <c r="C18" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,9)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,9),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,9),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="D18" s="26">
+        <v>Clínica Bem-Estar</v>
+      </c>
+      <c r="D18" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,9)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,9),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,9),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Contestação</v>
       </c>
       <c r="E18" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,9)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,9),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,9),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>46279.0</v>
       </c>
       <c r="F18" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,9)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,9),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,9),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="G18" s="25">
+        <v>0</v>
+      </c>
+      <c r="G18" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,9)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,9),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,9),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="H18" s="25">
+        <v>Hoje</v>
+      </c>
+      <c r="H18" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,9)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,9),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,9),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Marina Ferraz</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,10)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,10),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,10),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="C19" s="26">
+        <v>6832730-55.2026.8.26.0386</v>
+      </c>
+      <c r="C19" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,10)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,10),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,10),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="D19" s="26">
+        <v>Patrícia Gomes</v>
+      </c>
+      <c r="D19" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,10)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,10),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,10),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Minuta de acordo</v>
       </c>
       <c r="E19" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,10)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,10),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,10),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>46279.0</v>
       </c>
       <c r="F19" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,10)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,10),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,10),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="G19" s="25">
+        <v>0</v>
+      </c>
+      <c r="G19" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,10)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,10),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,10),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="H19" s="25">
+        <v>Hoje</v>
+      </c>
+      <c r="H19" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,10)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,10),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,10),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Marina Ferraz</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,11)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,11),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,11),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="C20" s="26">
+        <v>7679821-77.2026.8.26.0265</v>
+      </c>
+      <c r="C20" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,11)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,11),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,11),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="D20" s="26">
+        <v>Helena Duarte</v>
+      </c>
+      <c r="D20" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,11)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,11),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,11),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Réplica</v>
       </c>
       <c r="E20" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,11)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,11),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,11),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>46280.0</v>
       </c>
       <c r="F20" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,11)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,11),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,11),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="G20" s="25">
+        <v>1</v>
+      </c>
+      <c r="G20" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,11)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,11),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,11),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="H20" s="25">
+        <v>Até 7 dias</v>
+      </c>
+      <c r="H20" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,11)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,11),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,11),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Rafael Lima</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,12)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,12),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,12),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="C21" s="26">
+        <v>2998500-50.2026.8.26.0515</v>
+      </c>
+      <c r="C21" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,12)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,12),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,12),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="D21" s="26">
+        <v>Ana Beatriz Moreira</v>
+      </c>
+      <c r="D21" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,12)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,12),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,12),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Prazo interno</v>
       </c>
       <c r="E21" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,12)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,12),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,12),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>46280.0</v>
       </c>
       <c r="F21" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,12)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,12),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,12),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="G21" s="25">
+        <v>1</v>
+      </c>
+      <c r="G21" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,12)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,12),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,12),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="H21" s="25">
+        <v>Até 7 dias</v>
+      </c>
+      <c r="H21" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,12)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,12),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,12),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Rafael Lima</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="25" t="n">
         <v>13</v>
       </c>
-      <c r="B22" s="26">
+      <c r="B22" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,13)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,13),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,13),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="C22" s="26">
+        <v>2998500-50.2026.8.26.0515</v>
+      </c>
+      <c r="C22" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,13)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,13),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,13),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="D22" s="26">
+        <v>Ana Beatriz Moreira</v>
+      </c>
+      <c r="D22" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,13)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,13),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,13),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Audiência de conciliação</v>
       </c>
       <c r="E22" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,13)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,13),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,13),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>46281.0</v>
       </c>
       <c r="F22" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,13)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,13),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,13),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="G22" s="25">
+        <v>2</v>
+      </c>
+      <c r="G22" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,13)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,13),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,13),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="25">
+        <v>Até 7 dias</v>
+      </c>
+      <c r="H22" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,13)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,13),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,13),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Rafael Lima</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="25" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="26">
+      <c r="B23" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,14)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,14),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,14),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="C23" s="26">
+        <v>6710873-21.2025.8.26.0571</v>
+      </c>
+      <c r="C23" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,14)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,14),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,14),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="D23" s="26">
+        <v>Escola Aurora</v>
+      </c>
+      <c r="D23" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,14)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,14),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,14),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Recurso de apelação</v>
       </c>
       <c r="E23" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,14)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,14),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,14),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>46281.0</v>
       </c>
       <c r="F23" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,14)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,14),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,14),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="G23" s="25">
+        <v>2</v>
+      </c>
+      <c r="G23" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,14)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,14),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,14),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="H23" s="25">
+        <v>Até 7 dias</v>
+      </c>
+      <c r="H23" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,14)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,14),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,14),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Marina Ferraz</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="25" t="n">
         <v>15</v>
       </c>
-      <c r="B24" s="26">
+      <c r="B24" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,15)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,15),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,15),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="C24" s="26">
+        <v>CONS-2026-04</v>
+      </c>
+      <c r="C24" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,15)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,15),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,15),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="D24" s="26">
+        <v>Escola Aurora</v>
+      </c>
+      <c r="D24" s="26" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,15)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,15),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,15),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Reunião com cliente</v>
       </c>
       <c r="E24" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,15)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,15),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,15),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>46282.0</v>
       </c>
       <c r="F24" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,15)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,15),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,15),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="G24" s="25">
+        <v>3</v>
+      </c>
+      <c r="G24" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,15)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,15),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,15),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="25">
+        <v>Até 7 dias</v>
+      </c>
+      <c r="H24" s="25" t="str">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,15)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,15),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,15),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v/>
+        <v>Marina Ferraz</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="25" t="n">
+        <v>16</v>
+      </c>
+      <c r="B25" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,16)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,16),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,16),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>8045862-82.2026.8.26.0491</v>
+      </c>
+      <c r="C25" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,16)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,16),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,16),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Carlos Eduardo Nunes</v>
+      </c>
+      <c r="D25" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,16)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,16),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,16),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Embargos de declaração</v>
+      </c>
+      <c r="E25" s="27">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,16)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,16),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,16),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>46282.0</v>
+      </c>
+      <c r="F25" s="28">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,16)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,16),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,16),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>3</v>
+      </c>
+      <c r="G25" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,16)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,16),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,16),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Até 7 dias</v>
+      </c>
+      <c r="H25" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,16)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,16),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,16),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Rafael Lima</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="22" t="inlineStr">
-        <is>
-          <t>Carga por responsável</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="24" t="inlineStr">
-        <is>
-          <t>Responsável</t>
-        </is>
-      </c>
-      <c r="B27" s="29" t="n"/>
-      <c r="C27" s="24" t="inlineStr">
-        <is>
-          <t>Abertos</t>
-        </is>
-      </c>
-      <c r="D27" s="24" t="inlineStr">
-        <is>
-          <t>Atrasados</t>
-        </is>
-      </c>
-      <c r="E27" s="24" t="inlineStr">
-        <is>
-          <t>Hoje</t>
-        </is>
-      </c>
-      <c r="F27" s="24" t="inlineStr">
-        <is>
-          <t>Em alerta</t>
-        </is>
-      </c>
-      <c r="G27" s="24" t="inlineStr">
-        <is>
-          <t>Mais antigo em aberto</t>
-        </is>
-      </c>
-      <c r="H27" s="24" t="inlineStr">
-        <is>
-          <t>Feitos</t>
-        </is>
+      <c r="A26" s="25" t="n">
+        <v>17</v>
+      </c>
+      <c r="B26" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,17)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,17),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,17),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>CONS-2026-02</v>
+      </c>
+      <c r="C26" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,17)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,17),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,17),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Loja Verde Comércio</v>
+      </c>
+      <c r="D26" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,17)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,17),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,17),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Entrega de parecer</v>
+      </c>
+      <c r="E26" s="27">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,17)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,17),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,17),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>46283.0</v>
+      </c>
+      <c r="F26" s="28">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,17)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,17),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,17),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>4</v>
+      </c>
+      <c r="G26" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,17)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,17),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,17),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Até 7 dias</v>
+      </c>
+      <c r="H26" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,17)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,17),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,17),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Marina Ferraz</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="25" t="n">
+        <v>18</v>
+      </c>
+      <c r="B27" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,18)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,18),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,18),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>9225646-96.2025.8.26.0322</v>
+      </c>
+      <c r="C27" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,18)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,18),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,18),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Transportadora Rota Sul</v>
+      </c>
+      <c r="D27" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,18)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,18),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,18),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Manifestação sobre laudo</v>
+      </c>
+      <c r="E27" s="27">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,18)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,18),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,18),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>46283.0</v>
+      </c>
+      <c r="F27" s="28">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,18)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,18),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,18),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>4</v>
+      </c>
+      <c r="G27" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,18)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,18),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,18),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Até 7 dias</v>
+      </c>
+      <c r="H27" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,18)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,18),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,18),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Rafael Lima</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="26">
-        <f>IF(Config!$B$10="","",Config!$B$10)</f>
-        <v/>
-      </c>
-      <c r="B28" s="25" t="n"/>
-      <c r="C28" s="25">
-        <f>IF(Config!$B$10="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$10,Prazos!$J$5:$J$404,"&gt;0")+COUNTIFS(Prazos!$E$5:$E$404,Config!$B$10,Prazos!$I$5:$I$404,"Sem data"))</f>
-        <v/>
-      </c>
-      <c r="D28" s="25">
-        <f>IF(Config!$B$10="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$10,Prazos!$I$5:$I$404,"Atrasado"))</f>
-        <v/>
-      </c>
-      <c r="E28" s="25">
-        <f>IF(Config!$B$10="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$10,Prazos!$I$5:$I$404,"Hoje"))</f>
-        <v/>
-      </c>
-      <c r="F28" s="25">
-        <f>IF(Config!$B$10="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$10,Prazos!$I$5:$I$404,"Até "&amp;Config!$B$6&amp;" dias"))</f>
-        <v/>
-      </c>
-      <c r="G28" s="27">
-        <f>IF(Config!$B$10="","",IFERROR(IF(_xlfn.MINIFS(Prazos!$D$5:$D$404,Prazos!$E$5:$E$404,Config!$B$10,Prazos!$J$5:$J$404,"&gt;0")=0,"",_xlfn.MINIFS(Prazos!$D$5:$D$404,Prazos!$E$5:$E$404,Config!$B$10,Prazos!$J$5:$J$404,"&gt;0")),""))</f>
-        <v/>
-      </c>
-      <c r="H28" s="25">
-        <f>IF(Config!$B$10="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$10,Prazos!$I$5:$I$404,"Feito"))</f>
-        <v/>
+      <c r="A28" s="25" t="n">
+        <v>19</v>
+      </c>
+      <c r="B28" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,19)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,19),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,19),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>CONS-2025-05</v>
+      </c>
+      <c r="C28" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,19)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,19),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,19),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Clínica Bem-Estar</v>
+      </c>
+      <c r="D28" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,19)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,19),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,19),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Reunião com cliente</v>
+      </c>
+      <c r="E28" s="27">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,19)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,19),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,19),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>46284.0</v>
+      </c>
+      <c r="F28" s="28">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,19)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,19),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,19),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>5</v>
+      </c>
+      <c r="G28" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,19)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,19),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,19),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Até 7 dias</v>
+      </c>
+      <c r="H28" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,19)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,19),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,19),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Marina Ferraz</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="26">
-        <f>IF(Config!$B$11="","",Config!$B$11)</f>
-        <v/>
-      </c>
-      <c r="B29" s="25" t="n"/>
-      <c r="C29" s="25">
-        <f>IF(Config!$B$11="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$11,Prazos!$J$5:$J$404,"&gt;0")+COUNTIFS(Prazos!$E$5:$E$404,Config!$B$11,Prazos!$I$5:$I$404,"Sem data"))</f>
-        <v/>
-      </c>
-      <c r="D29" s="25">
-        <f>IF(Config!$B$11="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$11,Prazos!$I$5:$I$404,"Atrasado"))</f>
-        <v/>
-      </c>
-      <c r="E29" s="25">
-        <f>IF(Config!$B$11="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$11,Prazos!$I$5:$I$404,"Hoje"))</f>
-        <v/>
-      </c>
-      <c r="F29" s="25">
-        <f>IF(Config!$B$11="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$11,Prazos!$I$5:$I$404,"Até "&amp;Config!$B$6&amp;" dias"))</f>
-        <v/>
-      </c>
-      <c r="G29" s="27">
-        <f>IF(Config!$B$11="","",IFERROR(IF(_xlfn.MINIFS(Prazos!$D$5:$D$404,Prazos!$E$5:$E$404,Config!$B$11,Prazos!$J$5:$J$404,"&gt;0")=0,"",_xlfn.MINIFS(Prazos!$D$5:$D$404,Prazos!$E$5:$E$404,Config!$B$11,Prazos!$J$5:$J$404,"&gt;0")),""))</f>
-        <v/>
-      </c>
-      <c r="H29" s="25">
-        <f>IF(Config!$B$11="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$11,Prazos!$I$5:$I$404,"Feito"))</f>
-        <v/>
+      <c r="A29" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B29" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,20)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,20),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,20),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>8056747-83.2026.8.26.0561</v>
+      </c>
+      <c r="C29" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,20)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,20),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,20),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Bistrô 42</v>
+      </c>
+      <c r="D29" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,20)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,20),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,20),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Juntada de documentos</v>
+      </c>
+      <c r="E29" s="27">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,20)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,20),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,20),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>46284.0</v>
+      </c>
+      <c r="F29" s="28">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,20)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,20),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,20),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>5</v>
+      </c>
+      <c r="G29" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,20)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,20),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,20),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Até 7 dias</v>
+      </c>
+      <c r="H29" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,20)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,20),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,20),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Júlia Prado</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="26">
-        <f>IF(Config!$B$12="","",Config!$B$12)</f>
-        <v/>
-      </c>
-      <c r="B30" s="25" t="n"/>
-      <c r="C30" s="25">
-        <f>IF(Config!$B$12="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$12,Prazos!$J$5:$J$404,"&gt;0")+COUNTIFS(Prazos!$E$5:$E$404,Config!$B$12,Prazos!$I$5:$I$404,"Sem data"))</f>
-        <v/>
-      </c>
-      <c r="D30" s="25">
-        <f>IF(Config!$B$12="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$12,Prazos!$I$5:$I$404,"Atrasado"))</f>
-        <v/>
-      </c>
-      <c r="E30" s="25">
-        <f>IF(Config!$B$12="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$12,Prazos!$I$5:$I$404,"Hoje"))</f>
-        <v/>
-      </c>
-      <c r="F30" s="25">
-        <f>IF(Config!$B$12="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$12,Prazos!$I$5:$I$404,"Até "&amp;Config!$B$6&amp;" dias"))</f>
-        <v/>
-      </c>
-      <c r="G30" s="27">
-        <f>IF(Config!$B$12="","",IFERROR(IF(_xlfn.MINIFS(Prazos!$D$5:$D$404,Prazos!$E$5:$E$404,Config!$B$12,Prazos!$J$5:$J$404,"&gt;0")=0,"",_xlfn.MINIFS(Prazos!$D$5:$D$404,Prazos!$E$5:$E$404,Config!$B$12,Prazos!$J$5:$J$404,"&gt;0")),""))</f>
-        <v/>
-      </c>
-      <c r="H30" s="25">
-        <f>IF(Config!$B$12="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$12,Prazos!$I$5:$I$404,"Feito"))</f>
-        <v/>
+      <c r="A30" s="25" t="n">
+        <v>21</v>
+      </c>
+      <c r="B30" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,21)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,21),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,21),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>4746093-86.2026.8.26.0637</v>
+      </c>
+      <c r="C30" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,21)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,21),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,21),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Carlos Eduardo Nunes</v>
+      </c>
+      <c r="D30" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,21)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,21),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,21),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Juntada de documentos</v>
+      </c>
+      <c r="E30" s="27">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,21)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,21),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,21),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>46285.0</v>
+      </c>
+      <c r="F30" s="28">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,21)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,21),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,21),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>6</v>
+      </c>
+      <c r="G30" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,21)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,21),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,21),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Até 7 dias</v>
+      </c>
+      <c r="H30" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,21)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,21),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,21),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Júlia Prado</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="26">
-        <f>IF(Config!$B$13="","",Config!$B$13)</f>
-        <v/>
-      </c>
-      <c r="B31" s="25" t="n"/>
-      <c r="C31" s="25">
-        <f>IF(Config!$B$13="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$13,Prazos!$J$5:$J$404,"&gt;0")+COUNTIFS(Prazos!$E$5:$E$404,Config!$B$13,Prazos!$I$5:$I$404,"Sem data"))</f>
-        <v/>
-      </c>
-      <c r="D31" s="25">
-        <f>IF(Config!$B$13="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$13,Prazos!$I$5:$I$404,"Atrasado"))</f>
-        <v/>
-      </c>
-      <c r="E31" s="25">
-        <f>IF(Config!$B$13="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$13,Prazos!$I$5:$I$404,"Hoje"))</f>
-        <v/>
-      </c>
-      <c r="F31" s="25">
-        <f>IF(Config!$B$13="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$13,Prazos!$I$5:$I$404,"Até "&amp;Config!$B$6&amp;" dias"))</f>
-        <v/>
-      </c>
-      <c r="G31" s="27">
-        <f>IF(Config!$B$13="","",IFERROR(IF(_xlfn.MINIFS(Prazos!$D$5:$D$404,Prazos!$E$5:$E$404,Config!$B$13,Prazos!$J$5:$J$404,"&gt;0")=0,"",_xlfn.MINIFS(Prazos!$D$5:$D$404,Prazos!$E$5:$E$404,Config!$B$13,Prazos!$J$5:$J$404,"&gt;0")),""))</f>
-        <v/>
-      </c>
-      <c r="H31" s="25">
-        <f>IF(Config!$B$13="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$13,Prazos!$I$5:$I$404,"Feito"))</f>
-        <v/>
+      <c r="A31" s="25" t="n">
+        <v>22</v>
+      </c>
+      <c r="B31" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,22)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,22),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,22),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>2354318-24.2026.8.26.0295</v>
+      </c>
+      <c r="C31" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,22)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,22),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,22),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Roberto Almeida</v>
+      </c>
+      <c r="D31" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,22)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,22),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,22),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Contrarrazões</v>
+      </c>
+      <c r="E31" s="27">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,22)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,22),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,22),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>46287.0</v>
+      </c>
+      <c r="F31" s="28">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,22)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,22),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,22),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>8</v>
+      </c>
+      <c r="G31" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,22)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,22),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,22),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Até 30 dias</v>
+      </c>
+      <c r="H31" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,22)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,22),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,22),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Marina Ferraz</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="26">
-        <f>IF(Config!$B$14="","",Config!$B$14)</f>
-        <v/>
-      </c>
-      <c r="B32" s="25" t="n"/>
-      <c r="C32" s="25">
-        <f>IF(Config!$B$14="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$14,Prazos!$J$5:$J$404,"&gt;0")+COUNTIFS(Prazos!$E$5:$E$404,Config!$B$14,Prazos!$I$5:$I$404,"Sem data"))</f>
-        <v/>
-      </c>
-      <c r="D32" s="25">
-        <f>IF(Config!$B$14="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$14,Prazos!$I$5:$I$404,"Atrasado"))</f>
-        <v/>
-      </c>
-      <c r="E32" s="25">
-        <f>IF(Config!$B$14="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$14,Prazos!$I$5:$I$404,"Hoje"))</f>
-        <v/>
-      </c>
-      <c r="F32" s="25">
-        <f>IF(Config!$B$14="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$14,Prazos!$I$5:$I$404,"Até "&amp;Config!$B$6&amp;" dias"))</f>
-        <v/>
-      </c>
-      <c r="G32" s="27">
-        <f>IF(Config!$B$14="","",IFERROR(IF(_xlfn.MINIFS(Prazos!$D$5:$D$404,Prazos!$E$5:$E$404,Config!$B$14,Prazos!$J$5:$J$404,"&gt;0")=0,"",_xlfn.MINIFS(Prazos!$D$5:$D$404,Prazos!$E$5:$E$404,Config!$B$14,Prazos!$J$5:$J$404,"&gt;0")),""))</f>
-        <v/>
-      </c>
-      <c r="H32" s="25">
-        <f>IF(Config!$B$14="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$14,Prazos!$I$5:$I$404,"Feito"))</f>
-        <v/>
+      <c r="A32" s="25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B32" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,23)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,23),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,23),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>CONS-2026-01</v>
+      </c>
+      <c r="C32" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,23)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,23),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,23),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Padaria do Sol Ltda</v>
+      </c>
+      <c r="D32" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,23)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,23),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,23),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Reunião com cliente</v>
+      </c>
+      <c r="E32" s="27">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,23)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,23),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,23),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>46288.0</v>
+      </c>
+      <c r="F32" s="28">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,23)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,23),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,23),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>9</v>
+      </c>
+      <c r="G32" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,23)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,23),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,23),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Até 30 dias</v>
+      </c>
+      <c r="H32" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,23)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,23),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,23),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Marina Ferraz</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="26">
-        <f>IF(Config!$B$15="","",Config!$B$15)</f>
-        <v/>
-      </c>
-      <c r="B33" s="25" t="n"/>
-      <c r="C33" s="25">
-        <f>IF(Config!$B$15="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$15,Prazos!$J$5:$J$404,"&gt;0")+COUNTIFS(Prazos!$E$5:$E$404,Config!$B$15,Prazos!$I$5:$I$404,"Sem data"))</f>
-        <v/>
-      </c>
-      <c r="D33" s="25">
-        <f>IF(Config!$B$15="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$15,Prazos!$I$5:$I$404,"Atrasado"))</f>
-        <v/>
-      </c>
-      <c r="E33" s="25">
-        <f>IF(Config!$B$15="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$15,Prazos!$I$5:$I$404,"Hoje"))</f>
-        <v/>
-      </c>
-      <c r="F33" s="25">
-        <f>IF(Config!$B$15="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$15,Prazos!$I$5:$I$404,"Até "&amp;Config!$B$6&amp;" dias"))</f>
-        <v/>
-      </c>
-      <c r="G33" s="27">
-        <f>IF(Config!$B$15="","",IFERROR(IF(_xlfn.MINIFS(Prazos!$D$5:$D$404,Prazos!$E$5:$E$404,Config!$B$15,Prazos!$J$5:$J$404,"&gt;0")=0,"",_xlfn.MINIFS(Prazos!$D$5:$D$404,Prazos!$E$5:$E$404,Config!$B$15,Prazos!$J$5:$J$404,"&gt;0")),""))</f>
-        <v/>
-      </c>
-      <c r="H33" s="25">
-        <f>IF(Config!$B$15="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$15,Prazos!$I$5:$I$404,"Feito"))</f>
-        <v/>
+      <c r="A33" s="25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B33" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,24)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,24),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,24),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>8056747-83.2026.8.26.0561</v>
+      </c>
+      <c r="C33" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,24)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,24),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,24),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Bistrô 42</v>
+      </c>
+      <c r="D33" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,24)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,24),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,24),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Audiência de instrução</v>
+      </c>
+      <c r="E33" s="27">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,24)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,24),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,24),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>46288.0</v>
+      </c>
+      <c r="F33" s="28">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,24)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,24),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,24),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>9</v>
+      </c>
+      <c r="G33" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,24)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,24),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,24),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Até 30 dias</v>
+      </c>
+      <c r="H33" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,24)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,24),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,24),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Rafael Lima</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="26">
-        <f>IF(Config!$B$16="","",Config!$B$16)</f>
-        <v/>
-      </c>
-      <c r="B34" s="25" t="n"/>
-      <c r="C34" s="25">
-        <f>IF(Config!$B$16="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$16,Prazos!$J$5:$J$404,"&gt;0")+COUNTIFS(Prazos!$E$5:$E$404,Config!$B$16,Prazos!$I$5:$I$404,"Sem data"))</f>
-        <v/>
-      </c>
-      <c r="D34" s="25">
-        <f>IF(Config!$B$16="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$16,Prazos!$I$5:$I$404,"Atrasado"))</f>
-        <v/>
-      </c>
-      <c r="E34" s="25">
-        <f>IF(Config!$B$16="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$16,Prazos!$I$5:$I$404,"Hoje"))</f>
-        <v/>
-      </c>
-      <c r="F34" s="25">
-        <f>IF(Config!$B$16="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$16,Prazos!$I$5:$I$404,"Até "&amp;Config!$B$6&amp;" dias"))</f>
-        <v/>
-      </c>
-      <c r="G34" s="27">
-        <f>IF(Config!$B$16="","",IFERROR(IF(_xlfn.MINIFS(Prazos!$D$5:$D$404,Prazos!$E$5:$E$404,Config!$B$16,Prazos!$J$5:$J$404,"&gt;0")=0,"",_xlfn.MINIFS(Prazos!$D$5:$D$404,Prazos!$E$5:$E$404,Config!$B$16,Prazos!$J$5:$J$404,"&gt;0")),""))</f>
-        <v/>
-      </c>
-      <c r="H34" s="25">
-        <f>IF(Config!$B$16="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$16,Prazos!$I$5:$I$404,"Feito"))</f>
-        <v/>
+      <c r="A34" s="25" t="n">
+        <v>25</v>
+      </c>
+      <c r="B34" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,25)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,25),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,25),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>3363714-92.2025.8.26.0592</v>
+      </c>
+      <c r="C34" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,25)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,25),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,25),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Oficina Mecânica Central</v>
+      </c>
+      <c r="D34" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,25)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,25),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,25),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Alegações finais</v>
+      </c>
+      <c r="E34" s="27">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,25)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,25),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,25),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>46289.0</v>
+      </c>
+      <c r="F34" s="28">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,25)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,25),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,25),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>10</v>
+      </c>
+      <c r="G34" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,25)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,25),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,25),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Até 30 dias</v>
+      </c>
+      <c r="H34" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,25)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,25),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,25),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Rafael Lima</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="26">
-        <f>IF(Config!$B$17="","",Config!$B$17)</f>
-        <v/>
-      </c>
-      <c r="B35" s="25" t="n"/>
-      <c r="C35" s="25">
-        <f>IF(Config!$B$17="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$17,Prazos!$J$5:$J$404,"&gt;0")+COUNTIFS(Prazos!$E$5:$E$404,Config!$B$17,Prazos!$I$5:$I$404,"Sem data"))</f>
-        <v/>
-      </c>
-      <c r="D35" s="25">
-        <f>IF(Config!$B$17="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$17,Prazos!$I$5:$I$404,"Atrasado"))</f>
-        <v/>
-      </c>
-      <c r="E35" s="25">
-        <f>IF(Config!$B$17="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$17,Prazos!$I$5:$I$404,"Hoje"))</f>
-        <v/>
-      </c>
-      <c r="F35" s="25">
-        <f>IF(Config!$B$17="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$17,Prazos!$I$5:$I$404,"Até "&amp;Config!$B$6&amp;" dias"))</f>
-        <v/>
-      </c>
-      <c r="G35" s="27">
-        <f>IF(Config!$B$17="","",IFERROR(IF(_xlfn.MINIFS(Prazos!$D$5:$D$404,Prazos!$E$5:$E$404,Config!$B$17,Prazos!$J$5:$J$404,"&gt;0")=0,"",_xlfn.MINIFS(Prazos!$D$5:$D$404,Prazos!$E$5:$E$404,Config!$B$17,Prazos!$J$5:$J$404,"&gt;0")),""))</f>
-        <v/>
-      </c>
-      <c r="H35" s="25">
-        <f>IF(Config!$B$17="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$17,Prazos!$I$5:$I$404,"Feito"))</f>
-        <v/>
+      <c r="A35" s="25" t="n">
+        <v>26</v>
+      </c>
+      <c r="B35" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,26)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,26),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,26),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>6184138-13.2026.8.26.0378</v>
+      </c>
+      <c r="C35" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,26)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,26),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,26),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Oficina Mecânica Central</v>
+      </c>
+      <c r="D35" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,26)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,26),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,26),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Audiência de conciliação</v>
+      </c>
+      <c r="E35" s="27">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,26)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,26),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,26),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>46291.0</v>
+      </c>
+      <c r="F35" s="28">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,26)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,26),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,26),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>12</v>
+      </c>
+      <c r="G35" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,26)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,26),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,26),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Até 30 dias</v>
+      </c>
+      <c r="H35" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,26)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,26),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,26),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Rafael Lima</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="26">
-        <f>IF(Config!$B$18="","",Config!$B$18)</f>
-        <v/>
-      </c>
-      <c r="B36" s="25" t="n"/>
-      <c r="C36" s="25">
-        <f>IF(Config!$B$18="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$18,Prazos!$J$5:$J$404,"&gt;0")+COUNTIFS(Prazos!$E$5:$E$404,Config!$B$18,Prazos!$I$5:$I$404,"Sem data"))</f>
-        <v/>
-      </c>
-      <c r="D36" s="25">
-        <f>IF(Config!$B$18="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$18,Prazos!$I$5:$I$404,"Atrasado"))</f>
-        <v/>
-      </c>
-      <c r="E36" s="25">
-        <f>IF(Config!$B$18="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$18,Prazos!$I$5:$I$404,"Hoje"))</f>
-        <v/>
-      </c>
-      <c r="F36" s="25">
-        <f>IF(Config!$B$18="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$18,Prazos!$I$5:$I$404,"Até "&amp;Config!$B$6&amp;" dias"))</f>
-        <v/>
-      </c>
-      <c r="G36" s="27">
-        <f>IF(Config!$B$18="","",IFERROR(IF(_xlfn.MINIFS(Prazos!$D$5:$D$404,Prazos!$E$5:$E$404,Config!$B$18,Prazos!$J$5:$J$404,"&gt;0")=0,"",_xlfn.MINIFS(Prazos!$D$5:$D$404,Prazos!$E$5:$E$404,Config!$B$18,Prazos!$J$5:$J$404,"&gt;0")),""))</f>
-        <v/>
-      </c>
-      <c r="H36" s="25">
-        <f>IF(Config!$B$18="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$18,Prazos!$I$5:$I$404,"Feito"))</f>
-        <v/>
+      <c r="A36" s="25" t="n">
+        <v>27</v>
+      </c>
+      <c r="B36" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,27)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,27),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,27),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>3363714-92.2025.8.26.0592</v>
+      </c>
+      <c r="C36" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,27)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,27),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,27),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Oficina Mecânica Central</v>
+      </c>
+      <c r="D36" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,27)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,27),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,27),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Reunião com cliente</v>
+      </c>
+      <c r="E36" s="27">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,27)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,27),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,27),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>46291.0</v>
+      </c>
+      <c r="F36" s="28">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,27)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,27),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,27),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>12</v>
+      </c>
+      <c r="G36" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,27)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,27),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,27),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Até 30 dias</v>
+      </c>
+      <c r="H36" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,27)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,27),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,27),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Rafael Lima</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="26">
-        <f>IF(Config!$B$19="","",Config!$B$19)</f>
-        <v/>
-      </c>
-      <c r="B37" s="25" t="n"/>
-      <c r="C37" s="25">
-        <f>IF(Config!$B$19="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$19,Prazos!$J$5:$J$404,"&gt;0")+COUNTIFS(Prazos!$E$5:$E$404,Config!$B$19,Prazos!$I$5:$I$404,"Sem data"))</f>
-        <v/>
-      </c>
-      <c r="D37" s="25">
-        <f>IF(Config!$B$19="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$19,Prazos!$I$5:$I$404,"Atrasado"))</f>
-        <v/>
-      </c>
-      <c r="E37" s="25">
-        <f>IF(Config!$B$19="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$19,Prazos!$I$5:$I$404,"Hoje"))</f>
-        <v/>
-      </c>
-      <c r="F37" s="25">
-        <f>IF(Config!$B$19="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$19,Prazos!$I$5:$I$404,"Até "&amp;Config!$B$6&amp;" dias"))</f>
-        <v/>
-      </c>
-      <c r="G37" s="27">
-        <f>IF(Config!$B$19="","",IFERROR(IF(_xlfn.MINIFS(Prazos!$D$5:$D$404,Prazos!$E$5:$E$404,Config!$B$19,Prazos!$J$5:$J$404,"&gt;0")=0,"",_xlfn.MINIFS(Prazos!$D$5:$D$404,Prazos!$E$5:$E$404,Config!$B$19,Prazos!$J$5:$J$404,"&gt;0")),""))</f>
-        <v/>
-      </c>
-      <c r="H37" s="25">
-        <f>IF(Config!$B$19="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$19,Prazos!$I$5:$I$404,"Feito"))</f>
-        <v/>
+      <c r="A37" s="25" t="n">
+        <v>28</v>
+      </c>
+      <c r="B37" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,28)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,28),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,28),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>9236009-85.2025.8.26.0452</v>
+      </c>
+      <c r="C37" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,28)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,28),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,28),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Bistrô 42</v>
+      </c>
+      <c r="D37" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,28)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,28),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,28),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Cumprimento de sentença</v>
+      </c>
+      <c r="E37" s="27">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,28)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,28),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,28),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>46294.0</v>
+      </c>
+      <c r="F37" s="28">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,28)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,28),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,28),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>15</v>
+      </c>
+      <c r="G37" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,28)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,28),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,28),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Até 30 dias</v>
+      </c>
+      <c r="H37" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,28)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,28),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,28),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Rafael Lima</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="23" t="inlineStr">
-        <is>
-          <t>Prazos sem responsável não entram nesta tabela: confira na aba Prazos, filtrando a coluna Responsável por vazio.</t>
-        </is>
+      <c r="A38" s="25" t="n">
+        <v>29</v>
+      </c>
+      <c r="B38" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,29)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,29),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,29),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>CONS-2026-07</v>
+      </c>
+      <c r="C38" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,29)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,29),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,29),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Agência Prisma</v>
+      </c>
+      <c r="D38" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,29)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,29),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,29),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Entrega de parecer</v>
+      </c>
+      <c r="E38" s="27">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,29)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,29),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,29),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>46295.0</v>
+      </c>
+      <c r="F38" s="28">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,29)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,29),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,29),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>16</v>
+      </c>
+      <c r="G38" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,29)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,29),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,29),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Até 30 dias</v>
+      </c>
+      <c r="H38" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,29)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,29),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,29),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Marina Ferraz</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="25" t="n">
+        <v>30</v>
+      </c>
+      <c r="B39" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,30)&gt;0,IF(INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,30),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$A$5:$A$404,MATCH(LARGE(Prazos!$J$5:$J$404,30),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>4526984-60.2026.8.26.0258</v>
+      </c>
+      <c r="C39" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,30)&gt;0,IF(INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,30),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$B$5:$B$404,MATCH(LARGE(Prazos!$J$5:$J$404,30),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Transportadora Rota Sul</v>
+      </c>
+      <c r="D39" s="26" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,30)&gt;0,IF(INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,30),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$C$5:$C$404,MATCH(LARGE(Prazos!$J$5:$J$404,30),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Juntada de documentos</v>
+      </c>
+      <c r="E39" s="27">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,30)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,30),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,30),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>46295.0</v>
+      </c>
+      <c r="F39" s="28">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,30)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,30),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,30),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>16</v>
+      </c>
+      <c r="G39" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,30)&gt;0,IF(INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,30),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$I$5:$I$404,MATCH(LARGE(Prazos!$J$5:$J$404,30),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Até 30 dias</v>
+      </c>
+      <c r="H39" s="25" t="str">
+        <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,30)&gt;0,IF(INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,30),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$E$5:$E$404,MATCH(LARGE(Prazos!$J$5:$J$404,30),Prazos!$J$5:$J$404,0))),""),"")</f>
+        <v>Júlia Prado</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="22" t="inlineStr">
         <is>
-          <t>Próximos 7 dias, dia a dia</t>
+          <t>Carga por responsável</t>
         </is>
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
       <c r="A42" s="24" t="inlineStr">
         <is>
+          <t>Responsável</t>
+        </is>
+      </c>
+      <c r="B42" s="29" t="n"/>
+      <c r="C42" s="24" t="inlineStr">
+        <is>
+          <t>Abertos</t>
+        </is>
+      </c>
+      <c r="D42" s="24" t="inlineStr">
+        <is>
+          <t>Atrasados</t>
+        </is>
+      </c>
+      <c r="E42" s="24" t="inlineStr">
+        <is>
+          <t>Hoje</t>
+        </is>
+      </c>
+      <c r="F42" s="24" t="inlineStr">
+        <is>
+          <t>Em alerta</t>
+        </is>
+      </c>
+      <c r="G42" s="24" t="inlineStr">
+        <is>
+          <t>Mais antigo em aberto</t>
+        </is>
+      </c>
+      <c r="H42" s="24" t="inlineStr">
+        <is>
+          <t>Feitos</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="26" t="str">
+        <f>IF(Config!$B$10="","",Config!$B$10)</f>
+        <v>Marina Ferraz</v>
+      </c>
+      <c r="B43" s="25" t="n"/>
+      <c r="C43" s="25">
+        <f>IF(Config!$B$10="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$10,Prazos!$J$5:$J$404,"&gt;0")+COUNTIFS(Prazos!$E$5:$E$404,Config!$B$10,Prazos!$I$5:$I$404,"Sem data"))</f>
+        <v>15</v>
+      </c>
+      <c r="D43" s="25">
+        <f>IF(Config!$B$10="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$10,Prazos!$I$5:$I$404,"Atrasado"))</f>
+        <v>3</v>
+      </c>
+      <c r="E43" s="25">
+        <f>IF(Config!$B$10="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$10,Prazos!$I$5:$I$404,"Hoje"))</f>
+        <v>2</v>
+      </c>
+      <c r="F43" s="25">
+        <f>IF(Config!$B$10="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$10,Prazos!$I$5:$I$404,"Até "&amp;Config!$B$6&amp;" dias"))</f>
+        <v>4</v>
+      </c>
+      <c r="G43" s="27">
+        <f>IF(Config!$B$10="","",IFERROR(IF(SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$10)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$10)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))&gt;=1E+10,"",SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$10)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$10)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))),""))</f>
+        <v>46276.0</v>
+      </c>
+      <c r="H43" s="25">
+        <f>IF(Config!$B$10="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$10,Prazos!$I$5:$I$404,"Feito"))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="26" t="str">
+        <f>IF(Config!$B$11="","",Config!$B$11)</f>
+        <v>Rafael Lima</v>
+      </c>
+      <c r="B44" s="25" t="n"/>
+      <c r="C44" s="25">
+        <f>IF(Config!$B$11="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$11,Prazos!$J$5:$J$404,"&gt;0")+COUNTIFS(Prazos!$E$5:$E$404,Config!$B$11,Prazos!$I$5:$I$404,"Sem data"))</f>
+        <v>16</v>
+      </c>
+      <c r="D44" s="25">
+        <f>IF(Config!$B$11="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$11,Prazos!$I$5:$I$404,"Atrasado"))</f>
+        <v>3</v>
+      </c>
+      <c r="E44" s="25">
+        <f>IF(Config!$B$11="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$11,Prazos!$I$5:$I$404,"Hoje"))</f>
+        <v>1</v>
+      </c>
+      <c r="F44" s="25">
+        <f>IF(Config!$B$11="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$11,Prazos!$I$5:$I$404,"Até "&amp;Config!$B$6&amp;" dias"))</f>
+        <v>5</v>
+      </c>
+      <c r="G44" s="27">
+        <f>IF(Config!$B$11="","",IFERROR(IF(SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$11)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$11)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))&gt;=1E+10,"",SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$11)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$11)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))),""))</f>
+        <v>46274.0</v>
+      </c>
+      <c r="H44" s="25">
+        <f>IF(Config!$B$11="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$11,Prazos!$I$5:$I$404,"Feito"))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="26" t="str">
+        <f>IF(Config!$B$12="","",Config!$B$12)</f>
+        <v>Júlia Prado</v>
+      </c>
+      <c r="B45" s="25" t="n"/>
+      <c r="C45" s="25">
+        <f>IF(Config!$B$12="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$12,Prazos!$J$5:$J$404,"&gt;0")+COUNTIFS(Prazos!$E$5:$E$404,Config!$B$12,Prazos!$I$5:$I$404,"Sem data"))</f>
+        <v>5</v>
+      </c>
+      <c r="D45" s="25">
+        <f>IF(Config!$B$12="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$12,Prazos!$I$5:$I$404,"Atrasado"))</f>
+        <v>1</v>
+      </c>
+      <c r="E45" s="25">
+        <f>IF(Config!$B$12="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$12,Prazos!$I$5:$I$404,"Hoje"))</f>
+        <v>0</v>
+      </c>
+      <c r="F45" s="25">
+        <f>IF(Config!$B$12="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$12,Prazos!$I$5:$I$404,"Até "&amp;Config!$B$6&amp;" dias"))</f>
+        <v>2</v>
+      </c>
+      <c r="G45" s="27">
+        <f>IF(Config!$B$12="","",IFERROR(IF(SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$12)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$12)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))&gt;=1E+10,"",SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$12)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$12)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))),""))</f>
+        <v>46273.0</v>
+      </c>
+      <c r="H45" s="25">
+        <f>IF(Config!$B$12="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$12,Prazos!$I$5:$I$404,"Feito"))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="26">
+        <f>IF(Config!$B$13="","",Config!$B$13)</f>
+        <v/>
+      </c>
+      <c r="B46" s="25" t="n"/>
+      <c r="C46" s="25">
+        <f>IF(Config!$B$13="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$13,Prazos!$J$5:$J$404,"&gt;0")+COUNTIFS(Prazos!$E$5:$E$404,Config!$B$13,Prazos!$I$5:$I$404,"Sem data"))</f>
+        <v/>
+      </c>
+      <c r="D46" s="25">
+        <f>IF(Config!$B$13="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$13,Prazos!$I$5:$I$404,"Atrasado"))</f>
+        <v/>
+      </c>
+      <c r="E46" s="25">
+        <f>IF(Config!$B$13="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$13,Prazos!$I$5:$I$404,"Hoje"))</f>
+        <v/>
+      </c>
+      <c r="F46" s="25">
+        <f>IF(Config!$B$13="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$13,Prazos!$I$5:$I$404,"Até "&amp;Config!$B$6&amp;" dias"))</f>
+        <v/>
+      </c>
+      <c r="G46" s="27">
+        <f>IF(Config!$B$13="","",IFERROR(IF(SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$13)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$13)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))&gt;=1E+10,"",SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$13)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$13)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))),""))</f>
+        <v/>
+      </c>
+      <c r="H46" s="25">
+        <f>IF(Config!$B$13="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$13,Prazos!$I$5:$I$404,"Feito"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="26">
+        <f>IF(Config!$B$14="","",Config!$B$14)</f>
+        <v/>
+      </c>
+      <c r="B47" s="25" t="n"/>
+      <c r="C47" s="25">
+        <f>IF(Config!$B$14="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$14,Prazos!$J$5:$J$404,"&gt;0")+COUNTIFS(Prazos!$E$5:$E$404,Config!$B$14,Prazos!$I$5:$I$404,"Sem data"))</f>
+        <v/>
+      </c>
+      <c r="D47" s="25">
+        <f>IF(Config!$B$14="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$14,Prazos!$I$5:$I$404,"Atrasado"))</f>
+        <v/>
+      </c>
+      <c r="E47" s="25">
+        <f>IF(Config!$B$14="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$14,Prazos!$I$5:$I$404,"Hoje"))</f>
+        <v/>
+      </c>
+      <c r="F47" s="25">
+        <f>IF(Config!$B$14="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$14,Prazos!$I$5:$I$404,"Até "&amp;Config!$B$6&amp;" dias"))</f>
+        <v/>
+      </c>
+      <c r="G47" s="27">
+        <f>IF(Config!$B$14="","",IFERROR(IF(SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$14)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$14)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))&gt;=1E+10,"",SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$14)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$14)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))),""))</f>
+        <v/>
+      </c>
+      <c r="H47" s="25">
+        <f>IF(Config!$B$14="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$14,Prazos!$I$5:$I$404,"Feito"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="26">
+        <f>IF(Config!$B$15="","",Config!$B$15)</f>
+        <v/>
+      </c>
+      <c r="B48" s="25" t="n"/>
+      <c r="C48" s="25">
+        <f>IF(Config!$B$15="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$15,Prazos!$J$5:$J$404,"&gt;0")+COUNTIFS(Prazos!$E$5:$E$404,Config!$B$15,Prazos!$I$5:$I$404,"Sem data"))</f>
+        <v/>
+      </c>
+      <c r="D48" s="25">
+        <f>IF(Config!$B$15="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$15,Prazos!$I$5:$I$404,"Atrasado"))</f>
+        <v/>
+      </c>
+      <c r="E48" s="25">
+        <f>IF(Config!$B$15="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$15,Prazos!$I$5:$I$404,"Hoje"))</f>
+        <v/>
+      </c>
+      <c r="F48" s="25">
+        <f>IF(Config!$B$15="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$15,Prazos!$I$5:$I$404,"Até "&amp;Config!$B$6&amp;" dias"))</f>
+        <v/>
+      </c>
+      <c r="G48" s="27">
+        <f>IF(Config!$B$15="","",IFERROR(IF(SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$15)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$15)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))&gt;=1E+10,"",SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$15)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$15)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))),""))</f>
+        <v/>
+      </c>
+      <c r="H48" s="25">
+        <f>IF(Config!$B$15="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$15,Prazos!$I$5:$I$404,"Feito"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="26">
+        <f>IF(Config!$B$16="","",Config!$B$16)</f>
+        <v/>
+      </c>
+      <c r="B49" s="25" t="n"/>
+      <c r="C49" s="25">
+        <f>IF(Config!$B$16="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$16,Prazos!$J$5:$J$404,"&gt;0")+COUNTIFS(Prazos!$E$5:$E$404,Config!$B$16,Prazos!$I$5:$I$404,"Sem data"))</f>
+        <v/>
+      </c>
+      <c r="D49" s="25">
+        <f>IF(Config!$B$16="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$16,Prazos!$I$5:$I$404,"Atrasado"))</f>
+        <v/>
+      </c>
+      <c r="E49" s="25">
+        <f>IF(Config!$B$16="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$16,Prazos!$I$5:$I$404,"Hoje"))</f>
+        <v/>
+      </c>
+      <c r="F49" s="25">
+        <f>IF(Config!$B$16="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$16,Prazos!$I$5:$I$404,"Até "&amp;Config!$B$6&amp;" dias"))</f>
+        <v/>
+      </c>
+      <c r="G49" s="27">
+        <f>IF(Config!$B$16="","",IFERROR(IF(SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$16)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$16)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))&gt;=1E+10,"",SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$16)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$16)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))),""))</f>
+        <v/>
+      </c>
+      <c r="H49" s="25">
+        <f>IF(Config!$B$16="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$16,Prazos!$I$5:$I$404,"Feito"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="26">
+        <f>IF(Config!$B$17="","",Config!$B$17)</f>
+        <v/>
+      </c>
+      <c r="B50" s="25" t="n"/>
+      <c r="C50" s="25">
+        <f>IF(Config!$B$17="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$17,Prazos!$J$5:$J$404,"&gt;0")+COUNTIFS(Prazos!$E$5:$E$404,Config!$B$17,Prazos!$I$5:$I$404,"Sem data"))</f>
+        <v/>
+      </c>
+      <c r="D50" s="25">
+        <f>IF(Config!$B$17="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$17,Prazos!$I$5:$I$404,"Atrasado"))</f>
+        <v/>
+      </c>
+      <c r="E50" s="25">
+        <f>IF(Config!$B$17="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$17,Prazos!$I$5:$I$404,"Hoje"))</f>
+        <v/>
+      </c>
+      <c r="F50" s="25">
+        <f>IF(Config!$B$17="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$17,Prazos!$I$5:$I$404,"Até "&amp;Config!$B$6&amp;" dias"))</f>
+        <v/>
+      </c>
+      <c r="G50" s="27">
+        <f>IF(Config!$B$17="","",IFERROR(IF(SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$17)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$17)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))&gt;=1E+10,"",SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$17)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$17)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))),""))</f>
+        <v/>
+      </c>
+      <c r="H50" s="25">
+        <f>IF(Config!$B$17="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$17,Prazos!$I$5:$I$404,"Feito"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="26">
+        <f>IF(Config!$B$18="","",Config!$B$18)</f>
+        <v/>
+      </c>
+      <c r="B51" s="25" t="n"/>
+      <c r="C51" s="25">
+        <f>IF(Config!$B$18="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$18,Prazos!$J$5:$J$404,"&gt;0")+COUNTIFS(Prazos!$E$5:$E$404,Config!$B$18,Prazos!$I$5:$I$404,"Sem data"))</f>
+        <v/>
+      </c>
+      <c r="D51" s="25">
+        <f>IF(Config!$B$18="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$18,Prazos!$I$5:$I$404,"Atrasado"))</f>
+        <v/>
+      </c>
+      <c r="E51" s="25">
+        <f>IF(Config!$B$18="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$18,Prazos!$I$5:$I$404,"Hoje"))</f>
+        <v/>
+      </c>
+      <c r="F51" s="25">
+        <f>IF(Config!$B$18="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$18,Prazos!$I$5:$I$404,"Até "&amp;Config!$B$6&amp;" dias"))</f>
+        <v/>
+      </c>
+      <c r="G51" s="27">
+        <f>IF(Config!$B$18="","",IFERROR(IF(SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$18)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$18)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))&gt;=1E+10,"",SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$18)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$18)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))),""))</f>
+        <v/>
+      </c>
+      <c r="H51" s="25">
+        <f>IF(Config!$B$18="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$18,Prazos!$I$5:$I$404,"Feito"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="26">
+        <f>IF(Config!$B$19="","",Config!$B$19)</f>
+        <v/>
+      </c>
+      <c r="B52" s="25" t="n"/>
+      <c r="C52" s="25">
+        <f>IF(Config!$B$19="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$19,Prazos!$J$5:$J$404,"&gt;0")+COUNTIFS(Prazos!$E$5:$E$404,Config!$B$19,Prazos!$I$5:$I$404,"Sem data"))</f>
+        <v/>
+      </c>
+      <c r="D52" s="25">
+        <f>IF(Config!$B$19="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$19,Prazos!$I$5:$I$404,"Atrasado"))</f>
+        <v/>
+      </c>
+      <c r="E52" s="25">
+        <f>IF(Config!$B$19="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$19,Prazos!$I$5:$I$404,"Hoje"))</f>
+        <v/>
+      </c>
+      <c r="F52" s="25">
+        <f>IF(Config!$B$19="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$19,Prazos!$I$5:$I$404,"Até "&amp;Config!$B$6&amp;" dias"))</f>
+        <v/>
+      </c>
+      <c r="G52" s="27">
+        <f>IF(Config!$B$19="","",IFERROR(IF(SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$19)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$19)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))&gt;=1E+10,"",SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$19)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$19)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))),""))</f>
+        <v/>
+      </c>
+      <c r="H52" s="25">
+        <f>IF(Config!$B$19="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$19,Prazos!$I$5:$I$404,"Feito"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="23" t="inlineStr">
+        <is>
+          <t>Prazos sem responsável não entram nesta tabela: confira na aba Prazos, filtrando a coluna Responsável por vazio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="22" t="inlineStr">
+        <is>
+          <t>Próximos 7 dias, dia a dia</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="26" customHeight="1">
+      <c r="A57" s="24" t="inlineStr">
+        <is>
           <t>Dia</t>
         </is>
       </c>
-      <c r="B42" s="24" t="n"/>
-      <c r="C42" s="24" t="inlineStr">
+      <c r="B57" s="24" t="n"/>
+      <c r="C57" s="24" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="D42" s="24" t="inlineStr">
+      <c r="D57" s="24" t="inlineStr">
         <is>
           <t>Prazos abertos</t>
         </is>
       </c>
-      <c r="E42" s="24">
+      <c r="E57" s="24" t="str">
         <f>IF(Config!$B$10="","",Config!$B$10)</f>
-        <v/>
-      </c>
-      <c r="F42" s="24">
+        <v>Marina Ferraz</v>
+      </c>
+      <c r="F57" s="24" t="str">
         <f>IF(Config!$B$11="","",Config!$B$11)</f>
-        <v/>
-      </c>
-      <c r="G42" s="24">
+        <v>Rafael Lima</v>
+      </c>
+      <c r="G57" s="24" t="str">
         <f>IF(Config!$B$12="","",Config!$B$12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="25">
-        <f>CHOOSE(WEEKDAY(C43),"domingo","segunda","terça","quarta","quinta","sexta","sábado")</f>
-        <v/>
-      </c>
-      <c r="B43" s="25" t="n"/>
-      <c r="C43" s="27">
+        <v>Júlia Prado</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="25" t="str">
+        <f>CHOOSE(WEEKDAY(C58),"domingo","segunda","terça","quarta","quinta","sexta","sábado")</f>
+        <v>segunda</v>
+      </c>
+      <c r="B58" s="25" t="n"/>
+      <c r="C58" s="27">
         <f>Config!$B$5+0</f>
-        <v/>
-      </c>
-      <c r="D43" s="25">
-        <f>COUNTIFS(Prazos!$D$5:$D$404,C43,Prazos!$F$5:$F$404,"&lt;&gt;Sim")</f>
-        <v/>
-      </c>
-      <c r="E43" s="25">
-        <f>IF(Config!$B$10="","",COUNTIFS(Prazos!$D$5:$D$404,C43,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$10))</f>
-        <v/>
-      </c>
-      <c r="F43" s="25">
-        <f>IF(Config!$B$11="","",COUNTIFS(Prazos!$D$5:$D$404,C43,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$11))</f>
-        <v/>
-      </c>
-      <c r="G43" s="25">
-        <f>IF(Config!$B$12="","",COUNTIFS(Prazos!$D$5:$D$404,C43,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$12))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="25">
-        <f>CHOOSE(WEEKDAY(C44),"domingo","segunda","terça","quarta","quinta","sexta","sábado")</f>
-        <v/>
-      </c>
-      <c r="B44" s="25" t="n"/>
-      <c r="C44" s="27">
+        <v>46279.0</v>
+      </c>
+      <c r="D58" s="25">
+        <f>COUNTIFS(Prazos!$D$5:$D$404,C58,Prazos!$F$5:$F$404,"&lt;&gt;Sim")</f>
+        <v>3</v>
+      </c>
+      <c r="E58" s="25">
+        <f>IF(Config!$B$10="","",COUNTIFS(Prazos!$D$5:$D$404,C58,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$10))</f>
+        <v>2</v>
+      </c>
+      <c r="F58" s="25">
+        <f>IF(Config!$B$11="","",COUNTIFS(Prazos!$D$5:$D$404,C58,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$11))</f>
+        <v>1</v>
+      </c>
+      <c r="G58" s="25">
+        <f>IF(Config!$B$12="","",COUNTIFS(Prazos!$D$5:$D$404,C58,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$12))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="25" t="str">
+        <f>CHOOSE(WEEKDAY(C59),"domingo","segunda","terça","quarta","quinta","sexta","sábado")</f>
+        <v>terça</v>
+      </c>
+      <c r="B59" s="25" t="n"/>
+      <c r="C59" s="27">
         <f>Config!$B$5+1</f>
-        <v/>
-      </c>
-      <c r="D44" s="25">
-        <f>COUNTIFS(Prazos!$D$5:$D$404,C44,Prazos!$F$5:$F$404,"&lt;&gt;Sim")</f>
-        <v/>
-      </c>
-      <c r="E44" s="25">
-        <f>IF(Config!$B$10="","",COUNTIFS(Prazos!$D$5:$D$404,C44,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$10))</f>
-        <v/>
-      </c>
-      <c r="F44" s="25">
-        <f>IF(Config!$B$11="","",COUNTIFS(Prazos!$D$5:$D$404,C44,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$11))</f>
-        <v/>
-      </c>
-      <c r="G44" s="25">
-        <f>IF(Config!$B$12="","",COUNTIFS(Prazos!$D$5:$D$404,C44,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$12))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="25">
-        <f>CHOOSE(WEEKDAY(C45),"domingo","segunda","terça","quarta","quinta","sexta","sábado")</f>
-        <v/>
-      </c>
-      <c r="B45" s="25" t="n"/>
-      <c r="C45" s="27">
+        <v>46280.0</v>
+      </c>
+      <c r="D59" s="25">
+        <f>COUNTIFS(Prazos!$D$5:$D$404,C59,Prazos!$F$5:$F$404,"&lt;&gt;Sim")</f>
+        <v>2</v>
+      </c>
+      <c r="E59" s="25">
+        <f>IF(Config!$B$10="","",COUNTIFS(Prazos!$D$5:$D$404,C59,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$10))</f>
+        <v>0</v>
+      </c>
+      <c r="F59" s="25">
+        <f>IF(Config!$B$11="","",COUNTIFS(Prazos!$D$5:$D$404,C59,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$11))</f>
+        <v>2</v>
+      </c>
+      <c r="G59" s="25">
+        <f>IF(Config!$B$12="","",COUNTIFS(Prazos!$D$5:$D$404,C59,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$12))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="25" t="str">
+        <f>CHOOSE(WEEKDAY(C60),"domingo","segunda","terça","quarta","quinta","sexta","sábado")</f>
+        <v>quarta</v>
+      </c>
+      <c r="B60" s="25" t="n"/>
+      <c r="C60" s="27">
         <f>Config!$B$5+2</f>
-        <v/>
-      </c>
-      <c r="D45" s="25">
-        <f>COUNTIFS(Prazos!$D$5:$D$404,C45,Prazos!$F$5:$F$404,"&lt;&gt;Sim")</f>
-        <v/>
-      </c>
-      <c r="E45" s="25">
-        <f>IF(Config!$B$10="","",COUNTIFS(Prazos!$D$5:$D$404,C45,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$10))</f>
-        <v/>
-      </c>
-      <c r="F45" s="25">
-        <f>IF(Config!$B$11="","",COUNTIFS(Prazos!$D$5:$D$404,C45,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$11))</f>
-        <v/>
-      </c>
-      <c r="G45" s="25">
-        <f>IF(Config!$B$12="","",COUNTIFS(Prazos!$D$5:$D$404,C45,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$12))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="25">
-        <f>CHOOSE(WEEKDAY(C46),"domingo","segunda","terça","quarta","quinta","sexta","sábado")</f>
-        <v/>
-      </c>
-      <c r="B46" s="25" t="n"/>
-      <c r="C46" s="27">
+        <v>46281.0</v>
+      </c>
+      <c r="D60" s="25">
+        <f>COUNTIFS(Prazos!$D$5:$D$404,C60,Prazos!$F$5:$F$404,"&lt;&gt;Sim")</f>
+        <v>2</v>
+      </c>
+      <c r="E60" s="25">
+        <f>IF(Config!$B$10="","",COUNTIFS(Prazos!$D$5:$D$404,C60,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$10))</f>
+        <v>1</v>
+      </c>
+      <c r="F60" s="25">
+        <f>IF(Config!$B$11="","",COUNTIFS(Prazos!$D$5:$D$404,C60,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$11))</f>
+        <v>1</v>
+      </c>
+      <c r="G60" s="25">
+        <f>IF(Config!$B$12="","",COUNTIFS(Prazos!$D$5:$D$404,C60,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$12))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="25" t="str">
+        <f>CHOOSE(WEEKDAY(C61),"domingo","segunda","terça","quarta","quinta","sexta","sábado")</f>
+        <v>quinta</v>
+      </c>
+      <c r="B61" s="25" t="n"/>
+      <c r="C61" s="27">
         <f>Config!$B$5+3</f>
-        <v/>
-      </c>
-      <c r="D46" s="25">
-        <f>COUNTIFS(Prazos!$D$5:$D$404,C46,Prazos!$F$5:$F$404,"&lt;&gt;Sim")</f>
-        <v/>
-      </c>
-      <c r="E46" s="25">
-        <f>IF(Config!$B$10="","",COUNTIFS(Prazos!$D$5:$D$404,C46,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$10))</f>
-        <v/>
-      </c>
-      <c r="F46" s="25">
-        <f>IF(Config!$B$11="","",COUNTIFS(Prazos!$D$5:$D$404,C46,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$11))</f>
-        <v/>
-      </c>
-      <c r="G46" s="25">
-        <f>IF(Config!$B$12="","",COUNTIFS(Prazos!$D$5:$D$404,C46,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$12))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="25">
-        <f>CHOOSE(WEEKDAY(C47),"domingo","segunda","terça","quarta","quinta","sexta","sábado")</f>
-        <v/>
-      </c>
-      <c r="B47" s="25" t="n"/>
-      <c r="C47" s="27">
+        <v>46282.0</v>
+      </c>
+      <c r="D61" s="25">
+        <f>COUNTIFS(Prazos!$D$5:$D$404,C61,Prazos!$F$5:$F$404,"&lt;&gt;Sim")</f>
+        <v>2</v>
+      </c>
+      <c r="E61" s="25">
+        <f>IF(Config!$B$10="","",COUNTIFS(Prazos!$D$5:$D$404,C61,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$10))</f>
+        <v>1</v>
+      </c>
+      <c r="F61" s="25">
+        <f>IF(Config!$B$11="","",COUNTIFS(Prazos!$D$5:$D$404,C61,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$11))</f>
+        <v>1</v>
+      </c>
+      <c r="G61" s="25">
+        <f>IF(Config!$B$12="","",COUNTIFS(Prazos!$D$5:$D$404,C61,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$12))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="25" t="str">
+        <f>CHOOSE(WEEKDAY(C62),"domingo","segunda","terça","quarta","quinta","sexta","sábado")</f>
+        <v>sexta</v>
+      </c>
+      <c r="B62" s="25" t="n"/>
+      <c r="C62" s="27">
         <f>Config!$B$5+4</f>
-        <v/>
-      </c>
-      <c r="D47" s="25">
-        <f>COUNTIFS(Prazos!$D$5:$D$404,C47,Prazos!$F$5:$F$404,"&lt;&gt;Sim")</f>
-        <v/>
-      </c>
-      <c r="E47" s="25">
-        <f>IF(Config!$B$10="","",COUNTIFS(Prazos!$D$5:$D$404,C47,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$10))</f>
-        <v/>
-      </c>
-      <c r="F47" s="25">
-        <f>IF(Config!$B$11="","",COUNTIFS(Prazos!$D$5:$D$404,C47,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$11))</f>
-        <v/>
-      </c>
-      <c r="G47" s="25">
-        <f>IF(Config!$B$12="","",COUNTIFS(Prazos!$D$5:$D$404,C47,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$12))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="25">
-        <f>CHOOSE(WEEKDAY(C48),"domingo","segunda","terça","quarta","quinta","sexta","sábado")</f>
-        <v/>
-      </c>
-      <c r="B48" s="25" t="n"/>
-      <c r="C48" s="27">
+        <v>46283.0</v>
+      </c>
+      <c r="D62" s="25">
+        <f>COUNTIFS(Prazos!$D$5:$D$404,C62,Prazos!$F$5:$F$404,"&lt;&gt;Sim")</f>
+        <v>2</v>
+      </c>
+      <c r="E62" s="25">
+        <f>IF(Config!$B$10="","",COUNTIFS(Prazos!$D$5:$D$404,C62,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$10))</f>
+        <v>1</v>
+      </c>
+      <c r="F62" s="25">
+        <f>IF(Config!$B$11="","",COUNTIFS(Prazos!$D$5:$D$404,C62,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$11))</f>
+        <v>1</v>
+      </c>
+      <c r="G62" s="25">
+        <f>IF(Config!$B$12="","",COUNTIFS(Prazos!$D$5:$D$404,C62,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$12))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="25" t="str">
+        <f>CHOOSE(WEEKDAY(C63),"domingo","segunda","terça","quarta","quinta","sexta","sábado")</f>
+        <v>sábado</v>
+      </c>
+      <c r="B63" s="25" t="n"/>
+      <c r="C63" s="27">
         <f>Config!$B$5+5</f>
-        <v/>
-      </c>
-      <c r="D48" s="25">
-        <f>COUNTIFS(Prazos!$D$5:$D$404,C48,Prazos!$F$5:$F$404,"&lt;&gt;Sim")</f>
-        <v/>
-      </c>
-      <c r="E48" s="25">
-        <f>IF(Config!$B$10="","",COUNTIFS(Prazos!$D$5:$D$404,C48,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$10))</f>
-        <v/>
-      </c>
-      <c r="F48" s="25">
-        <f>IF(Config!$B$11="","",COUNTIFS(Prazos!$D$5:$D$404,C48,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$11))</f>
-        <v/>
-      </c>
-      <c r="G48" s="25">
-        <f>IF(Config!$B$12="","",COUNTIFS(Prazos!$D$5:$D$404,C48,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$12))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="25">
-        <f>CHOOSE(WEEKDAY(C49),"domingo","segunda","terça","quarta","quinta","sexta","sábado")</f>
-        <v/>
-      </c>
-      <c r="B49" s="25" t="n"/>
-      <c r="C49" s="27">
+        <v>46284.0</v>
+      </c>
+      <c r="D63" s="25">
+        <f>COUNTIFS(Prazos!$D$5:$D$404,C63,Prazos!$F$5:$F$404,"&lt;&gt;Sim")</f>
+        <v>2</v>
+      </c>
+      <c r="E63" s="25">
+        <f>IF(Config!$B$10="","",COUNTIFS(Prazos!$D$5:$D$404,C63,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$10))</f>
+        <v>1</v>
+      </c>
+      <c r="F63" s="25">
+        <f>IF(Config!$B$11="","",COUNTIFS(Prazos!$D$5:$D$404,C63,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$11))</f>
+        <v>0</v>
+      </c>
+      <c r="G63" s="25">
+        <f>IF(Config!$B$12="","",COUNTIFS(Prazos!$D$5:$D$404,C63,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$12))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="25" t="str">
+        <f>CHOOSE(WEEKDAY(C64),"domingo","segunda","terça","quarta","quinta","sexta","sábado")</f>
+        <v>domingo</v>
+      </c>
+      <c r="B64" s="25" t="n"/>
+      <c r="C64" s="27">
         <f>Config!$B$5+6</f>
-        <v/>
-      </c>
-      <c r="D49" s="25">
-        <f>COUNTIFS(Prazos!$D$5:$D$404,C49,Prazos!$F$5:$F$404,"&lt;&gt;Sim")</f>
-        <v/>
-      </c>
-      <c r="E49" s="25">
-        <f>IF(Config!$B$10="","",COUNTIFS(Prazos!$D$5:$D$404,C49,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$10))</f>
-        <v/>
-      </c>
-      <c r="F49" s="25">
-        <f>IF(Config!$B$11="","",COUNTIFS(Prazos!$D$5:$D$404,C49,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$11))</f>
-        <v/>
-      </c>
-      <c r="G49" s="25">
-        <f>IF(Config!$B$12="","",COUNTIFS(Prazos!$D$5:$D$404,C49,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$12))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="23" t="inlineStr">
+        <v>46285.0</v>
+      </c>
+      <c r="D64" s="25">
+        <f>COUNTIFS(Prazos!$D$5:$D$404,C64,Prazos!$F$5:$F$404,"&lt;&gt;Sim")</f>
+        <v>1</v>
+      </c>
+      <c r="E64" s="25">
+        <f>IF(Config!$B$10="","",COUNTIFS(Prazos!$D$5:$D$404,C64,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$10))</f>
+        <v>0</v>
+      </c>
+      <c r="F64" s="25">
+        <f>IF(Config!$B$11="","",COUNTIFS(Prazos!$D$5:$D$404,C64,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$11))</f>
+        <v>0</v>
+      </c>
+      <c r="G64" s="25">
+        <f>IF(Config!$B$12="","",COUNTIFS(Prazos!$D$5:$D$404,C64,Prazos!$F$5:$F$404,"&lt;&gt;Sim",Prazos!$E$5:$E$404,Config!$B$12))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="23" t="inlineStr">
         <is>
           <t>Os atrasados não aparecem aqui: estão no primeiro quadro e no topo de "O que vence primeiro".</t>
         </is>
@@ -2170,41 +2677,41 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="34">
     <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
     <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A51:B51"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="K5:L5"/>
-    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A61:B61"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A46:B46"/>
     <mergeCell ref="A8:L8"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A57:B57"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="G5:H5"/>
-    <mergeCell ref="A32:B32"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="I5:J5"/>
-    <mergeCell ref="A35:B35"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
+    <mergeCell ref="A62:B62"/>
     <mergeCell ref="I4:J4"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A52:B52"/>
     <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A63:B63"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A28:B28"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A58:B58"/>
   </mergeCells>
-  <conditionalFormatting sqref="A10:H24">
+  <conditionalFormatting sqref="A10:H39">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$G10="Atrasado"</formula>
     </cfRule>
@@ -2215,14 +2722,14 @@
       <formula>LEFT($G10,4)="Até "</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D28:D37">
+  <conditionalFormatting sqref="D43:D52">
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>AND(ISNUMBER(D28),D28&gt;0)</formula>
+      <formula>AND(ISNUMBER(D43),D43&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A43:G49">
+  <conditionalFormatting sqref="A58:G64">
     <cfRule type="expression" priority="5" dxfId="4">
-      <formula>$D43&gt;0</formula>
+      <formula>$D58&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2235,7 +2742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2280,7 +2787,7 @@
       </c>
       <c r="B5" s="32">
         <f>TODAY()</f>
-        <v/>
+        <v>46279.0</v>
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
@@ -2394,7 +2901,7 @@
       <c r="B16" s="31" t="n"/>
       <c r="D16" s="31" t="inlineStr">
         <is>
-          <t>Recurso ordinário</t>
+          <t>Embargos de declaração</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2909,7 @@
       <c r="B17" s="31" t="n"/>
       <c r="D17" s="31" t="inlineStr">
         <is>
-          <t>Contrarrazões</t>
+          <t>Recurso de apelação</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2917,7 @@
       <c r="B18" s="31" t="n"/>
       <c r="D18" s="31" t="inlineStr">
         <is>
-          <t>Embargos</t>
+          <t>Contrarrazões</t>
         </is>
       </c>
     </row>
@@ -2418,48 +2925,72 @@
       <c r="B19" s="31" t="n"/>
       <c r="D19" s="31" t="inlineStr">
         <is>
-          <t>Cumprimento de sentença</t>
+          <t>Manifestação sobre o recurso</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="D20" s="31" t="inlineStr">
         <is>
-          <t>Juntada de documentos</t>
+          <t>Cumprimento de sentença</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="D21" s="31" t="inlineStr">
         <is>
-          <t>Reunião com cliente</t>
+          <t>Manifestação sobre a penhora</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="D22" s="31" t="inlineStr">
         <is>
+          <t>Impugnação</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="D23" s="31" t="inlineStr">
+        <is>
+          <t>Minuta de acordo</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="D24" s="31" t="inlineStr">
+        <is>
+          <t>Homologação do acordo</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="D25" s="31" t="inlineStr">
+        <is>
+          <t>Entrega de parecer</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="D26" s="31" t="inlineStr">
+        <is>
+          <t>Juntada de documentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="D27" s="31" t="inlineStr">
+        <is>
+          <t>Reunião com cliente</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="D28" s="31" t="inlineStr">
+        <is>
           <t>Prazo interno</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="D23" s="31" t="n"/>
-    </row>
-    <row r="24">
-      <c r="D24" s="31" t="n"/>
-    </row>
-    <row r="25">
-      <c r="D25" s="31" t="n"/>
-    </row>
-    <row r="26">
-      <c r="D26" s="31" t="n"/>
-    </row>
-    <row r="27">
-      <c r="D27" s="31" t="n"/>
-    </row>
-    <row r="28">
-      <c r="D28" s="31" t="n"/>
     </row>
     <row r="29">
       <c r="D29" s="31" t="n"/>
@@ -2475,6 +3006,13 @@
       <c r="A32" s="23" t="inlineStr">
         <is>
           <t>O tipo de prazo é só um rótulo para organizar a agenda. Conte os dias e confira a data na fonte oficial: a planilha avisa, não calcula prazo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>No exemplo, a estagiária (Júlia Prado) responde pelos prazos de juntada de documentos; o caso continua com o sócio responsável (por isso ela tem prazos aqui e nenhum caso nas planilhas 02, 04 e 13).</t>
         </is>
       </c>
     </row>
@@ -2578,7 +3116,7 @@
     <row r="5">
       <c r="A5" s="31" t="inlineStr">
         <is>
-          <t>9236009-85.2026.8.26.0452</t>
+          <t>CONS-2026-01</t>
         </is>
       </c>
       <c r="B5" s="31" t="inlineStr">
@@ -2588,12 +3126,12 @@
       </c>
       <c r="C5" s="33" t="inlineStr">
         <is>
-          <t>Cumprimento de sentença</t>
+          <t>Reunião com cliente</t>
         </is>
       </c>
       <c r="D5" s="34">
-        <f>TODAY()+60</f>
-        <v/>
+        <f>TODAY()+9</f>
+        <v>46288.0</v>
       </c>
       <c r="E5" s="33" t="inlineStr">
         <is>
@@ -2601,24 +3139,28 @@
         </is>
       </c>
       <c r="F5" s="33" t="n"/>
-      <c r="G5" s="31" t="n"/>
+      <c r="G5" s="31" t="inlineStr">
+        <is>
+          <t>Reunião mensal da assessoria</t>
+        </is>
+      </c>
       <c r="H5" s="28">
         <f>IF(OR(I5="",I5="Feito",I5="Sem data"),"",D5-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I5" s="25">
+        <v>9</v>
+      </c>
+      <c r="I5" s="25" t="str">
         <f>IF(AND(A5="",C5="",D5=""),"",IF(F5="Sim","Feito",IF(D5="","Sem data",IF(D5&lt;Config!$B$5,"Atrasado",IF(D5=Config!$B$5,"Hoje",IF(D5-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D5-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Até 30 dias</v>
       </c>
       <c r="J5" s="35">
         <f>IF(OR(I5="",I5="Feito",I5="Sem data"),0,IF(I5="Atrasado",3000+MIN(Config!$B$5-D5,60),IF(I5="Hoje",2500,IF(D5-Config!$B$5&lt;=Config!$B$6,2000-(D5-Config!$B$5),IF(D5-Config!$B$5&lt;=Config!$B$7,1000-(D5-Config!$B$5),500-MIN(D5-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>990.99995</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="31" t="inlineStr">
         <is>
-          <t>9225646-96.2026.8.26.0322</t>
+          <t>2998500-50.2026.8.26.0515</t>
         </is>
       </c>
       <c r="B6" s="31" t="inlineStr">
@@ -2628,12 +3170,12 @@
       </c>
       <c r="C6" s="33" t="inlineStr">
         <is>
-          <t>Contrarrazões</t>
+          <t>Audiência de conciliação</t>
         </is>
       </c>
       <c r="D6" s="34">
-        <f>TODAY()-3</f>
-        <v/>
+        <f>TODAY()+2</f>
+        <v>46281.0</v>
       </c>
       <c r="E6" s="33" t="inlineStr">
         <is>
@@ -2643,26 +3185,26 @@
       <c r="F6" s="33" t="n"/>
       <c r="G6" s="31" t="inlineStr">
         <is>
-          <t>Confirmar com o cliente ainda hoje</t>
+          <t>Cliente confirmou presença</t>
         </is>
       </c>
       <c r="H6" s="28">
         <f>IF(OR(I6="",I6="Feito",I6="Sem data"),"",D6-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I6" s="25">
+        <v>2</v>
+      </c>
+      <c r="I6" s="25" t="str">
         <f>IF(AND(A6="",C6="",D6=""),"",IF(F6="Sim","Feito",IF(D6="","Sem data",IF(D6&lt;Config!$B$5,"Atrasado",IF(D6=Config!$B$5,"Hoje",IF(D6-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D6-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Até 7 dias</v>
       </c>
       <c r="J6" s="35">
         <f>IF(OR(I6="",I6="Feito",I6="Sem data"),0,IF(I6="Atrasado",3000+MIN(Config!$B$5-D6,60),IF(I6="Hoje",2500,IF(D6-Config!$B$5&lt;=Config!$B$6,2000-(D6-Config!$B$5),IF(D6-Config!$B$5&lt;=Config!$B$7,1000-(D6-Config!$B$5),500-MIN(D6-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>1997.99994</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="31" t="inlineStr">
         <is>
-          <t>6710873-21.2025.8.26.0571</t>
+          <t>9586960-92.2026.8.26.0106</t>
         </is>
       </c>
       <c r="B7" s="31" t="inlineStr">
@@ -2672,12 +3214,12 @@
       </c>
       <c r="C7" s="33" t="inlineStr">
         <is>
-          <t>Reunião com cliente</t>
+          <t>Réplica</t>
         </is>
       </c>
       <c r="D7" s="34">
-        <f>TODAY()</f>
-        <v/>
+        <f>TODAY()-3</f>
+        <v>46276.0</v>
       </c>
       <c r="E7" s="33" t="inlineStr">
         <is>
@@ -2687,26 +3229,26 @@
       <c r="F7" s="33" t="n"/>
       <c r="G7" s="31" t="inlineStr">
         <is>
-          <t>Pasta separada na mesa</t>
+          <t>Confirmar com o cliente ainda hoje</t>
         </is>
       </c>
       <c r="H7" s="28">
         <f>IF(OR(I7="",I7="Feito",I7="Sem data"),"",D7-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I7" s="25">
+        <v>-3</v>
+      </c>
+      <c r="I7" s="25" t="str">
         <f>IF(AND(A7="",C7="",D7=""),"",IF(F7="Sim","Feito",IF(D7="","Sem data",IF(D7&lt;Config!$B$5,"Atrasado",IF(D7=Config!$B$5,"Hoje",IF(D7-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D7-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Atrasado</v>
       </c>
       <c r="J7" s="35">
         <f>IF(OR(I7="",I7="Feito",I7="Sem data"),0,IF(I7="Atrasado",3000+MIN(Config!$B$5-D7,60),IF(I7="Hoje",2500,IF(D7-Config!$B$5&lt;=Config!$B$6,2000-(D7-Config!$B$5),IF(D7-Config!$B$5&lt;=Config!$B$7,1000-(D7-Config!$B$5),500-MIN(D7-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>3002.99993</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="31" t="inlineStr">
         <is>
-          <t>8735513-64.2025.8.26.0093</t>
+          <t>4746093-86.2026.8.26.0637</t>
         </is>
       </c>
       <c r="B8" s="31" t="inlineStr">
@@ -2716,41 +3258,41 @@
       </c>
       <c r="C8" s="33" t="inlineStr">
         <is>
-          <t>Alegações finais</t>
+          <t>Juntada de documentos</t>
         </is>
       </c>
       <c r="D8" s="34">
-        <f>TODAY()+15</f>
-        <v/>
+        <f>TODAY()+6</f>
+        <v>46285.0</v>
       </c>
       <c r="E8" s="33" t="inlineStr">
         <is>
-          <t>Rafael Lima</t>
+          <t>Júlia Prado</t>
         </is>
       </c>
       <c r="F8" s="33" t="n"/>
       <c r="G8" s="31" t="inlineStr">
         <is>
-          <t>Rascunho começado</t>
+          <t>Pedir 2 comprovantes ao cliente</t>
         </is>
       </c>
       <c r="H8" s="28">
         <f>IF(OR(I8="",I8="Feito",I8="Sem data"),"",D8-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I8" s="25">
+        <v>6</v>
+      </c>
+      <c r="I8" s="25" t="str">
         <f>IF(AND(A8="",C8="",D8=""),"",IF(F8="Sim","Feito",IF(D8="","Sem data",IF(D8&lt;Config!$B$5,"Atrasado",IF(D8=Config!$B$5,"Hoje",IF(D8-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D8-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Até 7 dias</v>
       </c>
       <c r="J8" s="35">
         <f>IF(OR(I8="",I8="Feito",I8="Sem data"),0,IF(I8="Atrasado",3000+MIN(Config!$B$5-D8,60),IF(I8="Hoje",2500,IF(D8-Config!$B$5&lt;=Config!$B$6,2000-(D8-Config!$B$5),IF(D8-Config!$B$5&lt;=Config!$B$7,1000-(D8-Config!$B$5),500-MIN(D8-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>1993.99992</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="31" t="inlineStr">
         <is>
-          <t>9802211-43.2025.8.26.0431</t>
+          <t>CONS-2026-02</t>
         </is>
       </c>
       <c r="B9" s="31" t="inlineStr">
@@ -2760,12 +3302,12 @@
       </c>
       <c r="C9" s="33" t="inlineStr">
         <is>
-          <t>Cumprimento de sentença</t>
+          <t>Entrega de parecer</t>
         </is>
       </c>
       <c r="D9" s="34">
-        <f>TODAY()+35</f>
-        <v/>
+        <f>TODAY()+4</f>
+        <v>46283.0</v>
       </c>
       <c r="E9" s="33" t="inlineStr">
         <is>
@@ -2773,39 +3315,43 @@
         </is>
       </c>
       <c r="F9" s="33" t="n"/>
-      <c r="G9" s="31" t="n"/>
+      <c r="G9" s="31" t="inlineStr">
+        <is>
+          <t>Rascunho começado</t>
+        </is>
+      </c>
       <c r="H9" s="28">
         <f>IF(OR(I9="",I9="Feito",I9="Sem data"),"",D9-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I9" s="25">
+        <v>4</v>
+      </c>
+      <c r="I9" s="25" t="str">
         <f>IF(AND(A9="",C9="",D9=""),"",IF(F9="Sim","Feito",IF(D9="","Sem data",IF(D9&lt;Config!$B$5,"Atrasado",IF(D9=Config!$B$5,"Hoje",IF(D9-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D9-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Até 7 dias</v>
       </c>
       <c r="J9" s="35">
         <f>IF(OR(I9="",I9="Feito",I9="Sem data"),0,IF(I9="Atrasado",3000+MIN(Config!$B$5-D9,60),IF(I9="Hoje",2500,IF(D9-Config!$B$5&lt;=Config!$B$6,2000-(D9-Config!$B$5),IF(D9-Config!$B$5&lt;=Config!$B$7,1000-(D9-Config!$B$5),500-MIN(D9-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>1995.99991</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="31" t="inlineStr">
         <is>
-          <t>8875326-79.2026.8.26.0258</t>
+          <t>CONS-2026-03</t>
         </is>
       </c>
       <c r="B10" s="31" t="inlineStr">
         <is>
-          <t>Bistrô 42</t>
+          <t>Marcos Vinícius Teles</t>
         </is>
       </c>
       <c r="C10" s="33" t="inlineStr">
         <is>
-          <t>Contrarrazões</t>
+          <t>Entrega de parecer</t>
         </is>
       </c>
       <c r="D10" s="34">
-        <f>TODAY()+27</f>
-        <v/>
+        <f>TODAY()</f>
+        <v>46279.0</v>
       </c>
       <c r="E10" s="33" t="inlineStr">
         <is>
@@ -2813,39 +3359,43 @@
         </is>
       </c>
       <c r="F10" s="33" t="n"/>
-      <c r="G10" s="31" t="n"/>
+      <c r="G10" s="31" t="inlineStr">
+        <is>
+          <t>Parecer revisado; enviar hoje</t>
+        </is>
+      </c>
       <c r="H10" s="28">
         <f>IF(OR(I10="",I10="Feito",I10="Sem data"),"",D10-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I10" s="25">
+        <v>0</v>
+      </c>
+      <c r="I10" s="25" t="str">
         <f>IF(AND(A10="",C10="",D10=""),"",IF(F10="Sim","Feito",IF(D10="","Sem data",IF(D10&lt;Config!$B$5,"Atrasado",IF(D10=Config!$B$5,"Hoje",IF(D10-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D10-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Hoje</v>
       </c>
       <c r="J10" s="35">
         <f>IF(OR(I10="",I10="Feito",I10="Sem data"),0,IF(I10="Atrasado",3000+MIN(Config!$B$5-D10,60),IF(I10="Hoje",2500,IF(D10-Config!$B$5&lt;=Config!$B$6,2000-(D10-Config!$B$5),IF(D10-Config!$B$5&lt;=Config!$B$7,1000-(D10-Config!$B$5),500-MIN(D10-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>2499.9999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="31" t="inlineStr">
         <is>
-          <t>4397912-47.2025.8.26.0276</t>
+          <t>CONS-2026-04</t>
         </is>
       </c>
       <c r="B11" s="31" t="inlineStr">
         <is>
-          <t>Roberto Almeida</t>
+          <t>Escola Aurora</t>
         </is>
       </c>
       <c r="C11" s="33" t="inlineStr">
         <is>
-          <t>Cumprimento de sentença</t>
+          <t>Reunião com cliente</t>
         </is>
       </c>
       <c r="D11" s="34">
-        <f>TODAY()+18</f>
-        <v/>
+        <f>TODAY()+3</f>
+        <v>46282.0</v>
       </c>
       <c r="E11" s="33" t="inlineStr">
         <is>
@@ -2853,39 +3403,43 @@
         </is>
       </c>
       <c r="F11" s="33" t="n"/>
-      <c r="G11" s="31" t="n"/>
+      <c r="G11" s="31" t="inlineStr">
+        <is>
+          <t>Reunião mensal da assessoria</t>
+        </is>
+      </c>
       <c r="H11" s="28">
         <f>IF(OR(I11="",I11="Feito",I11="Sem data"),"",D11-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I11" s="25">
+        <v>3</v>
+      </c>
+      <c r="I11" s="25" t="str">
         <f>IF(AND(A11="",C11="",D11=""),"",IF(F11="Sim","Feito",IF(D11="","Sem data",IF(D11&lt;Config!$B$5,"Atrasado",IF(D11=Config!$B$5,"Hoje",IF(D11-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D11-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Até 7 dias</v>
       </c>
       <c r="J11" s="35">
         <f>IF(OR(I11="",I11="Feito",I11="Sem data"),0,IF(I11="Atrasado",3000+MIN(Config!$B$5-D11,60),IF(I11="Hoje",2500,IF(D11-Config!$B$5&lt;=Config!$B$6,2000-(D11-Config!$B$5),IF(D11-Config!$B$5&lt;=Config!$B$7,1000-(D11-Config!$B$5),500-MIN(D11-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>1996.99989</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="31" t="inlineStr">
         <is>
-          <t>5470559-73.2026.8.26.0380</t>
+          <t>8056747-83.2026.8.26.0561</t>
         </is>
       </c>
       <c r="B12" s="31" t="inlineStr">
         <is>
-          <t>Transportadora Rota Sul</t>
+          <t>Bistrô 42</t>
         </is>
       </c>
       <c r="C12" s="33" t="inlineStr">
         <is>
-          <t>Contrarrazões</t>
+          <t>Audiência de instrução</t>
         </is>
       </c>
       <c r="D12" s="34">
-        <f>TODAY()</f>
-        <v/>
+        <f>TODAY()+9</f>
+        <v>46288.0</v>
       </c>
       <c r="E12" s="33" t="inlineStr">
         <is>
@@ -2895,85 +3449,81 @@
       <c r="F12" s="33" t="n"/>
       <c r="G12" s="31" t="inlineStr">
         <is>
-          <t>Pasta separada na mesa</t>
+          <t>Sala 3, 14h; testemunha avisada</t>
         </is>
       </c>
       <c r="H12" s="28">
         <f>IF(OR(I12="",I12="Feito",I12="Sem data"),"",D12-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I12" s="25">
+        <v>9</v>
+      </c>
+      <c r="I12" s="25" t="str">
         <f>IF(AND(A12="",C12="",D12=""),"",IF(F12="Sim","Feito",IF(D12="","Sem data",IF(D12&lt;Config!$B$5,"Atrasado",IF(D12=Config!$B$5,"Hoje",IF(D12-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D12-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Até 30 dias</v>
       </c>
       <c r="J12" s="35">
         <f>IF(OR(I12="",I12="Feito",I12="Sem data"),0,IF(I12="Atrasado",3000+MIN(Config!$B$5-D12,60),IF(I12="Hoje",2500,IF(D12-Config!$B$5&lt;=Config!$B$6,2000-(D12-Config!$B$5),IF(D12-Config!$B$5&lt;=Config!$B$7,1000-(D12-Config!$B$5),500-MIN(D12-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>990.99988</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="31" t="inlineStr">
         <is>
-          <t>8570388-84.2025.8.26.0560</t>
+          <t>9236009-85.2025.8.26.0452</t>
         </is>
       </c>
       <c r="B13" s="31" t="inlineStr">
         <is>
-          <t>Patrícia Gomes</t>
+          <t>Bistrô 42</t>
         </is>
       </c>
       <c r="C13" s="33" t="inlineStr">
         <is>
-          <t>Contestação</t>
+          <t>Cumprimento de sentença</t>
         </is>
       </c>
       <c r="D13" s="34">
-        <f>TODAY()</f>
-        <v/>
+        <f>TODAY()+15</f>
+        <v>46294.0</v>
       </c>
       <c r="E13" s="33" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="F13" s="33" t="n"/>
-      <c r="G13" s="31" t="inlineStr">
-        <is>
-          <t>Pasta separada na mesa</t>
-        </is>
-      </c>
+      <c r="G13" s="31" t="n"/>
       <c r="H13" s="28">
         <f>IF(OR(I13="",I13="Feito",I13="Sem data"),"",D13-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I13" s="25">
+        <v>15</v>
+      </c>
+      <c r="I13" s="25" t="str">
         <f>IF(AND(A13="",C13="",D13=""),"",IF(F13="Sim","Feito",IF(D13="","Sem data",IF(D13&lt;Config!$B$5,"Atrasado",IF(D13=Config!$B$5,"Hoje",IF(D13-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D13-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Até 30 dias</v>
       </c>
       <c r="J13" s="35">
         <f>IF(OR(I13="",I13="Feito",I13="Sem data"),0,IF(I13="Atrasado",3000+MIN(Config!$B$5-D13,60),IF(I13="Hoje",2500,IF(D13-Config!$B$5&lt;=Config!$B$6,2000-(D13-Config!$B$5),IF(D13-Config!$B$5&lt;=Config!$B$7,1000-(D13-Config!$B$5),500-MIN(D13-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>984.99987</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="31" t="inlineStr">
         <is>
-          <t>6258696-95.2026.8.26.0598</t>
+          <t>5025425-10.2025.8.26.0629</t>
         </is>
       </c>
       <c r="B14" s="31" t="inlineStr">
         <is>
-          <t>Escola Aurora</t>
+          <t>Roberto Almeida</t>
         </is>
       </c>
       <c r="C14" s="33" t="inlineStr">
         <is>
-          <t>Contestação</t>
+          <t>Embargos de declaração</t>
         </is>
       </c>
       <c r="D14" s="34">
-        <f>TODAY()+2</f>
-        <v/>
+        <f>TODAY()-1</f>
+        <v>46278.0</v>
       </c>
       <c r="E14" s="33" t="inlineStr">
         <is>
@@ -2983,85 +3533,81 @@
       <c r="F14" s="33" t="n"/>
       <c r="G14" s="31" t="inlineStr">
         <is>
-          <t>Cliente confirmou presença</t>
+          <t>Minuta pronta; protocolar hoje</t>
         </is>
       </c>
       <c r="H14" s="28">
         <f>IF(OR(I14="",I14="Feito",I14="Sem data"),"",D14-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I14" s="25">
+        <v>-1</v>
+      </c>
+      <c r="I14" s="25" t="str">
         <f>IF(AND(A14="",C14="",D14=""),"",IF(F14="Sim","Feito",IF(D14="","Sem data",IF(D14&lt;Config!$B$5,"Atrasado",IF(D14=Config!$B$5,"Hoje",IF(D14-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D14-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Atrasado</v>
       </c>
       <c r="J14" s="35">
         <f>IF(OR(I14="",I14="Feito",I14="Sem data"),0,IF(I14="Atrasado",3000+MIN(Config!$B$5-D14,60),IF(I14="Hoje",2500,IF(D14-Config!$B$5&lt;=Config!$B$6,2000-(D14-Config!$B$5),IF(D14-Config!$B$5&lt;=Config!$B$7,1000-(D14-Config!$B$5),500-MIN(D14-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>3000.99986</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="31" t="inlineStr">
         <is>
-          <t>4300029-58.2025.8.26.0015</t>
+          <t>2354318-24.2026.8.26.0295</t>
         </is>
       </c>
       <c r="B15" s="31" t="inlineStr">
         <is>
-          <t>Oficina Mecânica Central</t>
+          <t>Roberto Almeida</t>
         </is>
       </c>
       <c r="C15" s="33" t="inlineStr">
         <is>
-          <t>Audiência de conciliação</t>
+          <t>Contrarrazões</t>
         </is>
       </c>
       <c r="D15" s="34">
-        <f>TODAY()+2</f>
-        <v/>
+        <f>TODAY()+8</f>
+        <v>46287.0</v>
       </c>
       <c r="E15" s="33" t="inlineStr">
         <is>
-          <t>Rafael Lima</t>
+          <t>Marina Ferraz</t>
         </is>
       </c>
       <c r="F15" s="33" t="n"/>
-      <c r="G15" s="31" t="inlineStr">
-        <is>
-          <t>Cliente confirmou presença</t>
-        </is>
-      </c>
+      <c r="G15" s="31" t="n"/>
       <c r="H15" s="28">
         <f>IF(OR(I15="",I15="Feito",I15="Sem data"),"",D15-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I15" s="25">
+        <v>8</v>
+      </c>
+      <c r="I15" s="25" t="str">
         <f>IF(AND(A15="",C15="",D15=""),"",IF(F15="Sim","Feito",IF(D15="","Sem data",IF(D15&lt;Config!$B$5,"Atrasado",IF(D15=Config!$B$5,"Hoje",IF(D15-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D15-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Até 30 dias</v>
       </c>
       <c r="J15" s="35">
         <f>IF(OR(I15="",I15="Feito",I15="Sem data"),0,IF(I15="Atrasado",3000+MIN(Config!$B$5-D15,60),IF(I15="Hoje",2500,IF(D15-Config!$B$5&lt;=Config!$B$6,2000-(D15-Config!$B$5),IF(D15-Config!$B$5&lt;=Config!$B$7,1000-(D15-Config!$B$5),500-MIN(D15-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>991.99985</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="31" t="inlineStr">
         <is>
-          <t>8986364-51.2026.8.26.0700</t>
+          <t>CONS-2025-05</t>
         </is>
       </c>
       <c r="B16" s="31" t="inlineStr">
         <is>
-          <t>Luciana Farias</t>
+          <t>Clínica Bem-Estar</t>
         </is>
       </c>
       <c r="C16" s="33" t="inlineStr">
         <is>
-          <t>Audiência de conciliação</t>
+          <t>Reunião com cliente</t>
         </is>
       </c>
       <c r="D16" s="34">
-        <f>TODAY()-3</f>
-        <v/>
+        <f>TODAY()+5</f>
+        <v>46284.0</v>
       </c>
       <c r="E16" s="33" t="inlineStr">
         <is>
@@ -3071,41 +3617,41 @@
       <c r="F16" s="33" t="n"/>
       <c r="G16" s="31" t="inlineStr">
         <is>
-          <t>Confirmar com o cliente ainda hoje</t>
+          <t>Revisão semestral do contrato</t>
         </is>
       </c>
       <c r="H16" s="28">
         <f>IF(OR(I16="",I16="Feito",I16="Sem data"),"",D16-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I16" s="25">
+        <v>5</v>
+      </c>
+      <c r="I16" s="25" t="str">
         <f>IF(AND(A16="",C16="",D16=""),"",IF(F16="Sim","Feito",IF(D16="","Sem data",IF(D16&lt;Config!$B$5,"Atrasado",IF(D16=Config!$B$5,"Hoje",IF(D16-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D16-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Até 7 dias</v>
       </c>
       <c r="J16" s="35">
         <f>IF(OR(I16="",I16="Feito",I16="Sem data"),0,IF(I16="Atrasado",3000+MIN(Config!$B$5-D16,60),IF(I16="Hoje",2500,IF(D16-Config!$B$5&lt;=Config!$B$6,2000-(D16-Config!$B$5),IF(D16-Config!$B$5&lt;=Config!$B$7,1000-(D16-Config!$B$5),500-MIN(D16-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>1994.99984</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="31" t="inlineStr">
         <is>
-          <t>9717671-36.2026.8.26.0445</t>
+          <t>2645033-67.2026.8.26.0012</t>
         </is>
       </c>
       <c r="B17" s="31" t="inlineStr">
         <is>
-          <t>Agência Prisma</t>
+          <t>Clínica Bem-Estar</t>
         </is>
       </c>
       <c r="C17" s="33" t="inlineStr">
         <is>
-          <t>Audiência de instrução</t>
+          <t>Contestação</t>
         </is>
       </c>
       <c r="D17" s="34">
-        <f>TODAY()+3</f>
-        <v/>
+        <f>TODAY()</f>
+        <v>46279.0</v>
       </c>
       <c r="E17" s="33" t="inlineStr">
         <is>
@@ -3113,39 +3659,43 @@
         </is>
       </c>
       <c r="F17" s="33" t="n"/>
-      <c r="G17" s="31" t="n"/>
+      <c r="G17" s="31" t="inlineStr">
+        <is>
+          <t>Pasta separada na mesa</t>
+        </is>
+      </c>
       <c r="H17" s="28">
         <f>IF(OR(I17="",I17="Feito",I17="Sem data"),"",D17-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I17" s="25">
+        <v>0</v>
+      </c>
+      <c r="I17" s="25" t="str">
         <f>IF(AND(A17="",C17="",D17=""),"",IF(F17="Sim","Feito",IF(D17="","Sem data",IF(D17&lt;Config!$B$5,"Atrasado",IF(D17=Config!$B$5,"Hoje",IF(D17-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D17-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Hoje</v>
       </c>
       <c r="J17" s="35">
         <f>IF(OR(I17="",I17="Feito",I17="Sem data"),0,IF(I17="Atrasado",3000+MIN(Config!$B$5-D17,60),IF(I17="Hoje",2500,IF(D17-Config!$B$5&lt;=Config!$B$6,2000-(D17-Config!$B$5),IF(D17-Config!$B$5&lt;=Config!$B$7,1000-(D17-Config!$B$5),500-MIN(D17-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>2499.99983</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="31" t="inlineStr">
         <is>
-          <t>1808451-67.2026.8.26.0657</t>
+          <t>9225646-96.2025.8.26.0322</t>
         </is>
       </c>
       <c r="B18" s="31" t="inlineStr">
         <is>
-          <t>Helena Duarte</t>
+          <t>Transportadora Rota Sul</t>
         </is>
       </c>
       <c r="C18" s="33" t="inlineStr">
         <is>
-          <t>Contestação</t>
+          <t>Manifestação sobre laudo</t>
         </is>
       </c>
       <c r="D18" s="34">
-        <f>TODAY()+3</f>
-        <v/>
+        <f>TODAY()+4</f>
+        <v>46283.0</v>
       </c>
       <c r="E18" s="33" t="inlineStr">
         <is>
@@ -3153,39 +3703,43 @@
         </is>
       </c>
       <c r="F18" s="33" t="n"/>
-      <c r="G18" s="31" t="n"/>
+      <c r="G18" s="31" t="inlineStr">
+        <is>
+          <t>Levar via impressa</t>
+        </is>
+      </c>
       <c r="H18" s="28">
         <f>IF(OR(I18="",I18="Feito",I18="Sem data"),"",D18-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I18" s="25">
+        <v>4</v>
+      </c>
+      <c r="I18" s="25" t="str">
         <f>IF(AND(A18="",C18="",D18=""),"",IF(F18="Sim","Feito",IF(D18="","Sem data",IF(D18&lt;Config!$B$5,"Atrasado",IF(D18=Config!$B$5,"Hoje",IF(D18-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D18-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Até 7 dias</v>
       </c>
       <c r="J18" s="35">
         <f>IF(OR(I18="",I18="Feito",I18="Sem data"),0,IF(I18="Atrasado",3000+MIN(Config!$B$5-D18,60),IF(I18="Hoje",2500,IF(D18-Config!$B$5&lt;=Config!$B$6,2000-(D18-Config!$B$5),IF(D18-Config!$B$5&lt;=Config!$B$7,1000-(D18-Config!$B$5),500-MIN(D18-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>1995.99982</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="31" t="inlineStr">
         <is>
-          <t>3930894-43.2025.8.26.0476</t>
+          <t>4526984-60.2026.8.26.0258</t>
         </is>
       </c>
       <c r="B19" s="31" t="inlineStr">
         <is>
-          <t>Ana Beatriz Moreira</t>
+          <t>Transportadora Rota Sul</t>
         </is>
       </c>
       <c r="C19" s="33" t="inlineStr">
         <is>
-          <t>Alegações finais</t>
+          <t>Audiência de conciliação</t>
         </is>
       </c>
       <c r="D19" s="34">
-        <f>TODAY()+3</f>
-        <v/>
+        <f>TODAY()+20</f>
+        <v>46299.0</v>
       </c>
       <c r="E19" s="33" t="inlineStr">
         <is>
@@ -3196,116 +3750,124 @@
       <c r="G19" s="31" t="n"/>
       <c r="H19" s="28">
         <f>IF(OR(I19="",I19="Feito",I19="Sem data"),"",D19-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I19" s="25">
+        <v>20</v>
+      </c>
+      <c r="I19" s="25" t="str">
         <f>IF(AND(A19="",C19="",D19=""),"",IF(F19="Sim","Feito",IF(D19="","Sem data",IF(D19&lt;Config!$B$5,"Atrasado",IF(D19=Config!$B$5,"Hoje",IF(D19-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D19-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Até 30 dias</v>
       </c>
       <c r="J19" s="35">
         <f>IF(OR(I19="",I19="Feito",I19="Sem data"),0,IF(I19="Atrasado",3000+MIN(Config!$B$5-D19,60),IF(I19="Hoje",2500,IF(D19-Config!$B$5&lt;=Config!$B$6,2000-(D19-Config!$B$5),IF(D19-Config!$B$5&lt;=Config!$B$7,1000-(D19-Config!$B$5),500-MIN(D19-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>979.99981</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="31" t="inlineStr">
         <is>
-          <t>9802987-45.2025.8.26.0097</t>
+          <t>CONS-2026-06</t>
         </is>
       </c>
       <c r="B20" s="31" t="inlineStr">
         <is>
-          <t>Construtora Horizonte</t>
+          <t>Transportadora Rota Sul</t>
         </is>
       </c>
       <c r="C20" s="33" t="inlineStr">
         <is>
-          <t>Audiência de conciliação</t>
+          <t>Reunião com cliente</t>
         </is>
       </c>
       <c r="D20" s="34">
-        <f>TODAY()+1</f>
-        <v/>
+        <f>TODAY()-5</f>
+        <v>46274.0</v>
       </c>
       <c r="E20" s="33" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="F20" s="33" t="n"/>
-      <c r="G20" s="31" t="n"/>
+      <c r="G20" s="31" t="inlineStr">
+        <is>
+          <t>Cliente pediu para remarcar; sem nova data</t>
+        </is>
+      </c>
       <c r="H20" s="28">
         <f>IF(OR(I20="",I20="Feito",I20="Sem data"),"",D20-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I20" s="25">
+        <v>-5</v>
+      </c>
+      <c r="I20" s="25" t="str">
         <f>IF(AND(A20="",C20="",D20=""),"",IF(F20="Sim","Feito",IF(D20="","Sem data",IF(D20&lt;Config!$B$5,"Atrasado",IF(D20=Config!$B$5,"Hoje",IF(D20-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D20-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Atrasado</v>
       </c>
       <c r="J20" s="35">
         <f>IF(OR(I20="",I20="Feito",I20="Sem data"),0,IF(I20="Atrasado",3000+MIN(Config!$B$5-D20,60),IF(I20="Hoje",2500,IF(D20-Config!$B$5&lt;=Config!$B$6,2000-(D20-Config!$B$5),IF(D20-Config!$B$5&lt;=Config!$B$7,1000-(D20-Config!$B$5),500-MIN(D20-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>3004.9998</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="31" t="inlineStr">
         <is>
-          <t>6904743-30.2025.8.26.0361</t>
+          <t>6832730-55.2026.8.26.0386</t>
         </is>
       </c>
       <c r="B21" s="31" t="inlineStr">
         <is>
-          <t>Carlos Eduardo Nunes</t>
+          <t>Patrícia Gomes</t>
         </is>
       </c>
       <c r="C21" s="33" t="inlineStr">
         <is>
-          <t>Contestação</t>
+          <t>Minuta de acordo</t>
         </is>
       </c>
       <c r="D21" s="34">
-        <f>TODAY()+3</f>
-        <v/>
+        <f>TODAY()</f>
+        <v>46279.0</v>
       </c>
       <c r="E21" s="33" t="inlineStr">
         <is>
-          <t>Rafael Lima</t>
+          <t>Marina Ferraz</t>
         </is>
       </c>
       <c r="F21" s="33" t="n"/>
-      <c r="G21" s="31" t="n"/>
+      <c r="G21" s="31" t="inlineStr">
+        <is>
+          <t>Enviar a minuta para a outra parte</t>
+        </is>
+      </c>
       <c r="H21" s="28">
         <f>IF(OR(I21="",I21="Feito",I21="Sem data"),"",D21-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I21" s="25">
+        <v>0</v>
+      </c>
+      <c r="I21" s="25" t="str">
         <f>IF(AND(A21="",C21="",D21=""),"",IF(F21="Sim","Feito",IF(D21="","Sem data",IF(D21&lt;Config!$B$5,"Atrasado",IF(D21=Config!$B$5,"Hoje",IF(D21-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D21-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Hoje</v>
       </c>
       <c r="J21" s="35">
         <f>IF(OR(I21="",I21="Feito",I21="Sem data"),0,IF(I21="Atrasado",3000+MIN(Config!$B$5-D21,60),IF(I21="Hoje",2500,IF(D21-Config!$B$5&lt;=Config!$B$6,2000-(D21-Config!$B$5),IF(D21-Config!$B$5&lt;=Config!$B$7,1000-(D21-Config!$B$5),500-MIN(D21-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>2499.99979</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="31" t="inlineStr">
         <is>
-          <t>5497983-95.2025.8.26.0570</t>
+          <t>9616569-91.2026.8.26.0079</t>
         </is>
       </c>
       <c r="B22" s="31" t="inlineStr">
         <is>
-          <t>Loja Verde Comércio</t>
+          <t>Patrícia Gomes</t>
         </is>
       </c>
       <c r="C22" s="33" t="inlineStr">
         <is>
-          <t>Embargos</t>
+          <t>Impugnação</t>
         </is>
       </c>
       <c r="D22" s="34">
-        <f>TODAY()+10</f>
-        <v/>
+        <f>TODAY()-2</f>
+        <v>46277.0</v>
       </c>
       <c r="E22" s="33" t="inlineStr">
         <is>
@@ -3313,73 +3875,77 @@
         </is>
       </c>
       <c r="F22" s="33" t="n"/>
-      <c r="G22" s="31" t="n"/>
+      <c r="G22" s="31" t="inlineStr">
+        <is>
+          <t>Aguardando documentos do cliente</t>
+        </is>
+      </c>
       <c r="H22" s="28">
         <f>IF(OR(I22="",I22="Feito",I22="Sem data"),"",D22-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I22" s="25">
+        <v>-2</v>
+      </c>
+      <c r="I22" s="25" t="str">
         <f>IF(AND(A22="",C22="",D22=""),"",IF(F22="Sim","Feito",IF(D22="","Sem data",IF(D22&lt;Config!$B$5,"Atrasado",IF(D22=Config!$B$5,"Hoje",IF(D22-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D22-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Atrasado</v>
       </c>
       <c r="J22" s="35">
         <f>IF(OR(I22="",I22="Feito",I22="Sem data"),0,IF(I22="Atrasado",3000+MIN(Config!$B$5-D22,60),IF(I22="Hoje",2500,IF(D22-Config!$B$5&lt;=Config!$B$6,2000-(D22-Config!$B$5),IF(D22-Config!$B$5&lt;=Config!$B$7,1000-(D22-Config!$B$5),500-MIN(D22-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>3001.99978</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="31" t="inlineStr">
         <is>
-          <t>4112092-92.2025.8.26.0646</t>
+          <t>6710873-21.2025.8.26.0571</t>
         </is>
       </c>
       <c r="B23" s="31" t="inlineStr">
         <is>
-          <t>Fernanda Castro</t>
+          <t>Escola Aurora</t>
         </is>
       </c>
       <c r="C23" s="33" t="inlineStr">
         <is>
-          <t>Alegações finais</t>
+          <t>Recurso de apelação</t>
         </is>
       </c>
       <c r="D23" s="34">
-        <f>TODAY()-1</f>
-        <v/>
+        <f>TODAY()+2</f>
+        <v>46281.0</v>
       </c>
       <c r="E23" s="33" t="inlineStr">
         <is>
-          <t>Rafael Lima</t>
+          <t>Marina Ferraz</t>
         </is>
       </c>
       <c r="F23" s="33" t="n"/>
       <c r="G23" s="31" t="inlineStr">
         <is>
-          <t>Aguardando documentos do cliente</t>
+          <t>Cliente decidiu recorrer</t>
         </is>
       </c>
       <c r="H23" s="28">
         <f>IF(OR(I23="",I23="Feito",I23="Sem data"),"",D23-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I23" s="25">
+        <v>2</v>
+      </c>
+      <c r="I23" s="25" t="str">
         <f>IF(AND(A23="",C23="",D23=""),"",IF(F23="Sim","Feito",IF(D23="","Sem data",IF(D23&lt;Config!$B$5,"Atrasado",IF(D23=Config!$B$5,"Hoje",IF(D23-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D23-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Até 7 dias</v>
       </c>
       <c r="J23" s="35">
         <f>IF(OR(I23="",I23="Feito",I23="Sem data"),0,IF(I23="Atrasado",3000+MIN(Config!$B$5-D23,60),IF(I23="Hoje",2500,IF(D23-Config!$B$5&lt;=Config!$B$6,2000-(D23-Config!$B$5),IF(D23-Config!$B$5&lt;=Config!$B$7,1000-(D23-Config!$B$5),500-MIN(D23-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>1997.99977</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="31" t="inlineStr">
         <is>
-          <t>5297049-18.2026.8.26.0015</t>
+          <t>5900991-46.2026.8.26.0469</t>
         </is>
       </c>
       <c r="B24" s="31" t="inlineStr">
         <is>
-          <t>Bistrô 42</t>
+          <t>José Antônio Ribeiro</t>
         </is>
       </c>
       <c r="C24" s="33" t="inlineStr">
@@ -3388,176 +3954,176 @@
         </is>
       </c>
       <c r="D24" s="34">
-        <f>TODAY()+3</f>
-        <v/>
+        <f>TODAY()-4</f>
+        <v>46275.0</v>
       </c>
       <c r="E24" s="33" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="F24" s="33" t="n"/>
-      <c r="G24" s="31" t="n"/>
+      <c r="G24" s="31" t="inlineStr">
+        <is>
+          <t>Laudo recebido; rascunho começado</t>
+        </is>
+      </c>
       <c r="H24" s="28">
         <f>IF(OR(I24="",I24="Feito",I24="Sem data"),"",D24-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I24" s="25">
+        <v>-4</v>
+      </c>
+      <c r="I24" s="25" t="str">
         <f>IF(AND(A24="",C24="",D24=""),"",IF(F24="Sim","Feito",IF(D24="","Sem data",IF(D24&lt;Config!$B$5,"Atrasado",IF(D24=Config!$B$5,"Hoje",IF(D24-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D24-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Atrasado</v>
       </c>
       <c r="J24" s="35">
         <f>IF(OR(I24="",I24="Feito",I24="Sem data"),0,IF(I24="Atrasado",3000+MIN(Config!$B$5-D24,60),IF(I24="Hoje",2500,IF(D24-Config!$B$5&lt;=Config!$B$6,2000-(D24-Config!$B$5),IF(D24-Config!$B$5&lt;=Config!$B$7,1000-(D24-Config!$B$5),500-MIN(D24-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>3003.99976</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="31" t="inlineStr">
         <is>
-          <t>6877173-50.2026.8.26.0467</t>
+          <t>3363714-92.2025.8.26.0592</t>
         </is>
       </c>
       <c r="B25" s="31" t="inlineStr">
         <is>
-          <t>Roberto Almeida</t>
+          <t>Oficina Mecânica Central</t>
         </is>
       </c>
       <c r="C25" s="33" t="inlineStr">
         <is>
-          <t>Réplica</t>
+          <t>Alegações finais</t>
         </is>
       </c>
       <c r="D25" s="34">
-        <f>TODAY()+1</f>
-        <v/>
+        <f>TODAY()+10</f>
+        <v>46289.0</v>
       </c>
       <c r="E25" s="33" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="F25" s="33" t="n"/>
       <c r="G25" s="31" t="n"/>
       <c r="H25" s="28">
         <f>IF(OR(I25="",I25="Feito",I25="Sem data"),"",D25-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I25" s="25">
+        <v>10</v>
+      </c>
+      <c r="I25" s="25" t="str">
         <f>IF(AND(A25="",C25="",D25=""),"",IF(F25="Sim","Feito",IF(D25="","Sem data",IF(D25&lt;Config!$B$5,"Atrasado",IF(D25=Config!$B$5,"Hoje",IF(D25-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D25-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Até 30 dias</v>
       </c>
       <c r="J25" s="35">
         <f>IF(OR(I25="",I25="Feito",I25="Sem data"),0,IF(I25="Atrasado",3000+MIN(Config!$B$5-D25,60),IF(I25="Hoje",2500,IF(D25-Config!$B$5&lt;=Config!$B$6,2000-(D25-Config!$B$5),IF(D25-Config!$B$5&lt;=Config!$B$7,1000-(D25-Config!$B$5),500-MIN(D25-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>989.99975</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="31" t="inlineStr">
         <is>
-          <t>6545676-47.2025.8.26.0126</t>
+          <t>6184138-13.2026.8.26.0378</t>
         </is>
       </c>
       <c r="B26" s="31" t="inlineStr">
         <is>
-          <t>Marcos Vinícius Teles</t>
+          <t>Oficina Mecânica Central</t>
         </is>
       </c>
       <c r="C26" s="33" t="inlineStr">
         <is>
-          <t>Manifestação sobre laudo</t>
+          <t>Audiência de conciliação</t>
         </is>
       </c>
       <c r="D26" s="34">
-        <f>TODAY()-3</f>
-        <v/>
+        <f>TODAY()+12</f>
+        <v>46291.0</v>
       </c>
       <c r="E26" s="33" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="F26" s="33" t="n"/>
-      <c r="G26" s="31" t="inlineStr">
-        <is>
-          <t>Confirmar com o cliente ainda hoje</t>
-        </is>
-      </c>
+      <c r="G26" s="31" t="n"/>
       <c r="H26" s="28">
         <f>IF(OR(I26="",I26="Feito",I26="Sem data"),"",D26-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I26" s="25">
+        <v>12</v>
+      </c>
+      <c r="I26" s="25" t="str">
         <f>IF(AND(A26="",C26="",D26=""),"",IF(F26="Sim","Feito",IF(D26="","Sem data",IF(D26&lt;Config!$B$5,"Atrasado",IF(D26=Config!$B$5,"Hoje",IF(D26-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D26-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Até 30 dias</v>
       </c>
       <c r="J26" s="35">
         <f>IF(OR(I26="",I26="Feito",I26="Sem data"),0,IF(I26="Atrasado",3000+MIN(Config!$B$5-D26,60),IF(I26="Hoje",2500,IF(D26-Config!$B$5&lt;=Config!$B$6,2000-(D26-Config!$B$5),IF(D26-Config!$B$5&lt;=Config!$B$7,1000-(D26-Config!$B$5),500-MIN(D26-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>987.99974</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="31" t="inlineStr">
         <is>
-          <t>1941959-24.2026.8.26.0167</t>
+          <t>7099226-69.2026.8.26.0433</t>
         </is>
       </c>
       <c r="B27" s="31" t="inlineStr">
         <is>
-          <t>Transportadora Rota Sul</t>
+          <t>Luciana Farias</t>
         </is>
       </c>
       <c r="C27" s="33" t="inlineStr">
         <is>
-          <t>Audiência de conciliação</t>
+          <t>Juntada de documentos</t>
         </is>
       </c>
       <c r="D27" s="34">
-        <f>TODAY()+4</f>
-        <v/>
+        <f>TODAY()-6</f>
+        <v>46273.0</v>
       </c>
       <c r="E27" s="33" t="inlineStr">
         <is>
-          <t>Rafael Lima</t>
+          <t>Júlia Prado</t>
         </is>
       </c>
       <c r="F27" s="33" t="n"/>
       <c r="G27" s="31" t="inlineStr">
         <is>
-          <t>Levar via impressa</t>
+          <t>Pedir 2 comprovantes ao cliente</t>
         </is>
       </c>
       <c r="H27" s="28">
         <f>IF(OR(I27="",I27="Feito",I27="Sem data"),"",D27-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I27" s="25">
+        <v>-6</v>
+      </c>
+      <c r="I27" s="25" t="str">
         <f>IF(AND(A27="",C27="",D27=""),"",IF(F27="Sim","Feito",IF(D27="","Sem data",IF(D27&lt;Config!$B$5,"Atrasado",IF(D27=Config!$B$5,"Hoje",IF(D27-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D27-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Atrasado</v>
       </c>
       <c r="J27" s="35">
         <f>IF(OR(I27="",I27="Feito",I27="Sem data"),0,IF(I27="Atrasado",3000+MIN(Config!$B$5-D27,60),IF(I27="Hoje",2500,IF(D27-Config!$B$5&lt;=Config!$B$6,2000-(D27-Config!$B$5),IF(D27-Config!$B$5&lt;=Config!$B$7,1000-(D27-Config!$B$5),500-MIN(D27-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>3005.99973</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="31" t="inlineStr">
         <is>
-          <t>3118925-55.2025.8.26.0426</t>
+          <t>2521428-61.2026.8.26.0600</t>
         </is>
       </c>
       <c r="B28" s="31" t="inlineStr">
         <is>
-          <t>Patrícia Gomes</t>
+          <t>Luciana Farias</t>
         </is>
       </c>
       <c r="C28" s="33" t="inlineStr">
         <is>
-          <t>Cumprimento de sentença</t>
+          <t>Homologação do acordo</t>
         </is>
       </c>
       <c r="D28" s="34">
-        <f>TODAY()-3</f>
-        <v/>
+        <f>TODAY()+18</f>
+        <v>46297.0</v>
       </c>
       <c r="E28" s="33" t="inlineStr">
         <is>
@@ -3567,31 +4133,31 @@
       <c r="F28" s="33" t="n"/>
       <c r="G28" s="31" t="inlineStr">
         <is>
-          <t>Confirmar com o cliente ainda hoje</t>
+          <t>Minuta assinada; aguardando homologação</t>
         </is>
       </c>
       <c r="H28" s="28">
         <f>IF(OR(I28="",I28="Feito",I28="Sem data"),"",D28-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I28" s="25">
+        <v>18</v>
+      </c>
+      <c r="I28" s="25" t="str">
         <f>IF(AND(A28="",C28="",D28=""),"",IF(F28="Sim","Feito",IF(D28="","Sem data",IF(D28&lt;Config!$B$5,"Atrasado",IF(D28=Config!$B$5,"Hoje",IF(D28-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D28-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Até 30 dias</v>
       </c>
       <c r="J28" s="35">
         <f>IF(OR(I28="",I28="Feito",I28="Sem data"),0,IF(I28="Atrasado",3000+MIN(Config!$B$5-D28,60),IF(I28="Hoje",2500,IF(D28-Config!$B$5&lt;=Config!$B$6,2000-(D28-Config!$B$5),IF(D28-Config!$B$5&lt;=Config!$B$7,1000-(D28-Config!$B$5),500-MIN(D28-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>981.99972</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="31" t="inlineStr">
         <is>
-          <t>7658179-42.2026.8.26.0152</t>
+          <t>9362688-24.2025.8.26.0436</t>
         </is>
       </c>
       <c r="B29" s="31" t="inlineStr">
         <is>
-          <t>Escola Aurora</t>
+          <t>Agência Prisma</t>
         </is>
       </c>
       <c r="C29" s="33" t="inlineStr">
@@ -3600,8 +4166,8 @@
         </is>
       </c>
       <c r="D29" s="34">
-        <f>TODAY()-3</f>
-        <v/>
+        <f>TODAY()+27</f>
+        <v>46306.0</v>
       </c>
       <c r="E29" s="33" t="inlineStr">
         <is>
@@ -3609,43 +4175,39 @@
         </is>
       </c>
       <c r="F29" s="33" t="n"/>
-      <c r="G29" s="31" t="inlineStr">
-        <is>
-          <t>Confirmar com o cliente ainda hoje</t>
-        </is>
-      </c>
+      <c r="G29" s="31" t="n"/>
       <c r="H29" s="28">
         <f>IF(OR(I29="",I29="Feito",I29="Sem data"),"",D29-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I29" s="25">
+        <v>27</v>
+      </c>
+      <c r="I29" s="25" t="str">
         <f>IF(AND(A29="",C29="",D29=""),"",IF(F29="Sim","Feito",IF(D29="","Sem data",IF(D29&lt;Config!$B$5,"Atrasado",IF(D29=Config!$B$5,"Hoje",IF(D29-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D29-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Até 30 dias</v>
       </c>
       <c r="J29" s="35">
         <f>IF(OR(I29="",I29="Feito",I29="Sem data"),0,IF(I29="Atrasado",3000+MIN(Config!$B$5-D29,60),IF(I29="Hoje",2500,IF(D29-Config!$B$5&lt;=Config!$B$6,2000-(D29-Config!$B$5),IF(D29-Config!$B$5&lt;=Config!$B$7,1000-(D29-Config!$B$5),500-MIN(D29-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>972.99971</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="31" t="inlineStr">
         <is>
-          <t>1191416-90.2025.8.26.0249</t>
+          <t>CONS-2026-07</t>
         </is>
       </c>
       <c r="B30" s="31" t="inlineStr">
         <is>
-          <t>Oficina Mecânica Central</t>
+          <t>Agência Prisma</t>
         </is>
       </c>
       <c r="C30" s="33" t="inlineStr">
         <is>
-          <t>Contrarrazões</t>
+          <t>Entrega de parecer</t>
         </is>
       </c>
       <c r="D30" s="34">
-        <f>TODAY()-1</f>
-        <v/>
+        <f>TODAY()+16</f>
+        <v>46295.0</v>
       </c>
       <c r="E30" s="33" t="inlineStr">
         <is>
@@ -3655,243 +4217,239 @@
       <c r="F30" s="33" t="n"/>
       <c r="G30" s="31" t="inlineStr">
         <is>
-          <t>Aguardando documentos do cliente</t>
+          <t>Parecer sobre o novo contrato</t>
         </is>
       </c>
       <c r="H30" s="28">
         <f>IF(OR(I30="",I30="Feito",I30="Sem data"),"",D30-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I30" s="25">
+        <v>16</v>
+      </c>
+      <c r="I30" s="25" t="str">
         <f>IF(AND(A30="",C30="",D30=""),"",IF(F30="Sim","Feito",IF(D30="","Sem data",IF(D30&lt;Config!$B$5,"Atrasado",IF(D30=Config!$B$5,"Hoje",IF(D30-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D30-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Até 30 dias</v>
       </c>
       <c r="J30" s="35">
         <f>IF(OR(I30="",I30="Feito",I30="Sem data"),0,IF(I30="Atrasado",3000+MIN(Config!$B$5-D30,60),IF(I30="Hoje",2500,IF(D30-Config!$B$5&lt;=Config!$B$6,2000-(D30-Config!$B$5),IF(D30-Config!$B$5&lt;=Config!$B$7,1000-(D30-Config!$B$5),500-MIN(D30-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>983.9997</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="31" t="inlineStr">
         <is>
-          <t>6710873-21.2025.8.26.0571</t>
+          <t>9495290-86.2025.8.26.0503</t>
         </is>
       </c>
       <c r="B31" s="31" t="inlineStr">
         <is>
-          <t>Construtora Horizonte</t>
+          <t>Helena Duarte</t>
         </is>
       </c>
       <c r="C31" s="33" t="inlineStr">
         <is>
-          <t>Audiência de instrução</t>
+          <t>Cumprimento de sentença</t>
         </is>
       </c>
       <c r="D31" s="34">
-        <f>TODAY()+9</f>
-        <v/>
+        <f>TODAY()+22</f>
+        <v>46301.0</v>
       </c>
       <c r="E31" s="33" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="F31" s="33" t="n"/>
-      <c r="G31" s="31" t="inlineStr">
-        <is>
-          <t>Sala 3, 14h; testemunha avisada</t>
-        </is>
-      </c>
+      <c r="G31" s="31" t="n"/>
       <c r="H31" s="28">
         <f>IF(OR(I31="",I31="Feito",I31="Sem data"),"",D31-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I31" s="25">
+        <v>22</v>
+      </c>
+      <c r="I31" s="25" t="str">
         <f>IF(AND(A31="",C31="",D31=""),"",IF(F31="Sim","Feito",IF(D31="","Sem data",IF(D31&lt;Config!$B$5,"Atrasado",IF(D31=Config!$B$5,"Hoje",IF(D31-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D31-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Até 30 dias</v>
       </c>
       <c r="J31" s="35">
         <f>IF(OR(I31="",I31="Feito",I31="Sem data"),0,IF(I31="Atrasado",3000+MIN(Config!$B$5-D31,60),IF(I31="Hoje",2500,IF(D31-Config!$B$5&lt;=Config!$B$6,2000-(D31-Config!$B$5),IF(D31-Config!$B$5&lt;=Config!$B$7,1000-(D31-Config!$B$5),500-MIN(D31-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>977.99969</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="31" t="inlineStr">
         <is>
-          <t>6258696-95.2026.8.26.0598</t>
+          <t>7679821-77.2026.8.26.0265</t>
         </is>
       </c>
       <c r="B32" s="31" t="inlineStr">
         <is>
-          <t>Escola Aurora</t>
+          <t>Helena Duarte</t>
         </is>
       </c>
       <c r="C32" s="33" t="inlineStr">
         <is>
-          <t>Reunião com cliente</t>
+          <t>Réplica</t>
         </is>
       </c>
       <c r="D32" s="34">
-        <f>TODAY()+5</f>
-        <v/>
+        <f>TODAY()+1</f>
+        <v>46280.0</v>
       </c>
       <c r="E32" s="33" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="F32" s="33" t="n"/>
-      <c r="G32" s="31" t="inlineStr">
-        <is>
-          <t>Alinhar próximos passos</t>
-        </is>
-      </c>
+      <c r="G32" s="31" t="n"/>
       <c r="H32" s="28">
         <f>IF(OR(I32="",I32="Feito",I32="Sem data"),"",D32-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I32" s="25">
+        <v>1</v>
+      </c>
+      <c r="I32" s="25" t="str">
         <f>IF(AND(A32="",C32="",D32=""),"",IF(F32="Sim","Feito",IF(D32="","Sem data",IF(D32&lt;Config!$B$5,"Atrasado",IF(D32=Config!$B$5,"Hoje",IF(D32-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D32-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Até 7 dias</v>
       </c>
       <c r="J32" s="35">
         <f>IF(OR(I32="",I32="Feito",I32="Sem data"),0,IF(I32="Atrasado",3000+MIN(Config!$B$5-D32,60),IF(I32="Hoje",2500,IF(D32-Config!$B$5&lt;=Config!$B$6,2000-(D32-Config!$B$5),IF(D32-Config!$B$5&lt;=Config!$B$7,1000-(D32-Config!$B$5),500-MIN(D32-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>1998.99968</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="31" t="inlineStr">
         <is>
-          <t>9717671-36.2026.8.26.0445</t>
+          <t>8045862-82.2026.8.26.0491</t>
         </is>
       </c>
       <c r="B33" s="31" t="inlineStr">
         <is>
-          <t>Agência Prisma</t>
+          <t>Carlos Eduardo Nunes</t>
         </is>
       </c>
       <c r="C33" s="33" t="inlineStr">
         <is>
-          <t>Juntada de documentos</t>
+          <t>Embargos de declaração</t>
         </is>
       </c>
       <c r="D33" s="34">
-        <f>TODAY()+12</f>
-        <v/>
+        <f>TODAY()+3</f>
+        <v>46282.0</v>
       </c>
       <c r="E33" s="33" t="inlineStr">
         <is>
-          <t>Júlia Prado</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="F33" s="33" t="n"/>
-      <c r="G33" s="31" t="inlineStr">
-        <is>
-          <t>Pedir 2 comprovantes ao cliente</t>
-        </is>
-      </c>
+      <c r="G33" s="31" t="n"/>
       <c r="H33" s="28">
         <f>IF(OR(I33="",I33="Feito",I33="Sem data"),"",D33-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I33" s="25">
+        <v>3</v>
+      </c>
+      <c r="I33" s="25" t="str">
         <f>IF(AND(A33="",C33="",D33=""),"",IF(F33="Sim","Feito",IF(D33="","Sem data",IF(D33&lt;Config!$B$5,"Atrasado",IF(D33=Config!$B$5,"Hoje",IF(D33-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D33-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Até 7 dias</v>
       </c>
       <c r="J33" s="35">
         <f>IF(OR(I33="",I33="Feito",I33="Sem data"),0,IF(I33="Atrasado",3000+MIN(Config!$B$5-D33,60),IF(I33="Hoje",2500,IF(D33-Config!$B$5&lt;=Config!$B$6,2000-(D33-Config!$B$5),IF(D33-Config!$B$5&lt;=Config!$B$7,1000-(D33-Config!$B$5),500-MIN(D33-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>1996.99967</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="31" t="inlineStr">
         <is>
-          <t>5497983-95.2025.8.26.0570</t>
+          <t>9605863-76.2026.8.26.0026</t>
         </is>
       </c>
       <c r="B34" s="31" t="inlineStr">
         <is>
-          <t>Loja Verde Comércio</t>
+          <t>Marcos Vinícius Teles</t>
         </is>
       </c>
       <c r="C34" s="33" t="inlineStr">
         <is>
-          <t>Audiência de conciliação</t>
+          <t>Manifestação sobre o recurso</t>
         </is>
       </c>
       <c r="D34" s="34">
-        <f>TODAY()+20</f>
-        <v/>
+        <f>TODAY()-1</f>
+        <v>46278.0</v>
       </c>
       <c r="E34" s="33" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="F34" s="33" t="n"/>
-      <c r="G34" s="31" t="n"/>
+      <c r="G34" s="31" t="inlineStr">
+        <is>
+          <t>Aguardando documentos do cliente</t>
+        </is>
+      </c>
       <c r="H34" s="28">
         <f>IF(OR(I34="",I34="Feito",I34="Sem data"),"",D34-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I34" s="25">
+        <v>-1</v>
+      </c>
+      <c r="I34" s="25" t="str">
         <f>IF(AND(A34="",C34="",D34=""),"",IF(F34="Sim","Feito",IF(D34="","Sem data",IF(D34&lt;Config!$B$5,"Atrasado",IF(D34=Config!$B$5,"Hoje",IF(D34-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D34-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Atrasado</v>
       </c>
       <c r="J34" s="35">
         <f>IF(OR(I34="",I34="Feito",I34="Sem data"),0,IF(I34="Atrasado",3000+MIN(Config!$B$5-D34,60),IF(I34="Hoje",2500,IF(D34-Config!$B$5&lt;=Config!$B$6,2000-(D34-Config!$B$5),IF(D34-Config!$B$5&lt;=Config!$B$7,1000-(D34-Config!$B$5),500-MIN(D34-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>3000.99966</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="31" t="inlineStr">
         <is>
-          <t>5470559-73.2026.8.26.0380</t>
+          <t>8056747-83.2026.8.26.0561</t>
         </is>
       </c>
       <c r="B35" s="31" t="inlineStr">
         <is>
-          <t>Transportadora Rota Sul</t>
+          <t>Bistrô 42</t>
         </is>
       </c>
       <c r="C35" s="33" t="inlineStr">
         <is>
-          <t>Manifestação sobre laudo</t>
+          <t>Juntada de documentos</t>
         </is>
       </c>
       <c r="D35" s="34">
-        <f>TODAY()+24</f>
-        <v/>
+        <f>TODAY()+5</f>
+        <v>46284.0</v>
       </c>
       <c r="E35" s="33" t="inlineStr">
         <is>
-          <t>Rafael Lima</t>
+          <t>Júlia Prado</t>
         </is>
       </c>
       <c r="F35" s="33" t="n"/>
-      <c r="G35" s="31" t="n"/>
+      <c r="G35" s="31" t="inlineStr">
+        <is>
+          <t>Ata da audiência anterior</t>
+        </is>
+      </c>
       <c r="H35" s="28">
         <f>IF(OR(I35="",I35="Feito",I35="Sem data"),"",D35-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I35" s="25">
+        <v>5</v>
+      </c>
+      <c r="I35" s="25" t="str">
         <f>IF(AND(A35="",C35="",D35=""),"",IF(F35="Sim","Feito",IF(D35="","Sem data",IF(D35&lt;Config!$B$5,"Atrasado",IF(D35=Config!$B$5,"Hoje",IF(D35-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D35-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Até 7 dias</v>
       </c>
       <c r="J35" s="35">
         <f>IF(OR(I35="",I35="Feito",I35="Sem data"),0,IF(I35="Atrasado",3000+MIN(Config!$B$5-D35,60),IF(I35="Hoje",2500,IF(D35-Config!$B$5&lt;=Config!$B$6,2000-(D35-Config!$B$5),IF(D35-Config!$B$5&lt;=Config!$B$7,1000-(D35-Config!$B$5),500-MIN(D35-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>1994.99965</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="31" t="inlineStr">
         <is>
-          <t>6877173-50.2026.8.26.0467</t>
+          <t>3363714-92.2025.8.26.0592</t>
         </is>
       </c>
       <c r="B36" s="31" t="inlineStr">
         <is>
-          <t>Roberto Almeida</t>
+          <t>Oficina Mecânica Central</t>
         </is>
       </c>
       <c r="C36" s="33" t="inlineStr">
@@ -3900,42 +4458,42 @@
         </is>
       </c>
       <c r="D36" s="34">
-        <f>TODAY()+31</f>
-        <v/>
+        <f>TODAY()+12</f>
+        <v>46291.0</v>
       </c>
       <c r="E36" s="33" t="inlineStr">
         <is>
-          <t>Marina Ferraz</t>
+          <t>Rafael Lima</t>
         </is>
       </c>
       <c r="F36" s="33" t="n"/>
       <c r="G36" s="31" t="inlineStr">
         <is>
-          <t>Revisão semestral do contrato</t>
+          <t>Alinhar alegações finais</t>
         </is>
       </c>
       <c r="H36" s="28">
         <f>IF(OR(I36="",I36="Feito",I36="Sem data"),"",D36-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I36" s="25">
+        <v>12</v>
+      </c>
+      <c r="I36" s="25" t="str">
         <f>IF(AND(A36="",C36="",D36=""),"",IF(F36="Sim","Feito",IF(D36="","Sem data",IF(D36&lt;Config!$B$5,"Atrasado",IF(D36=Config!$B$5,"Hoje",IF(D36-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D36-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Até 30 dias</v>
       </c>
       <c r="J36" s="35">
         <f>IF(OR(I36="",I36="Feito",I36="Sem data"),0,IF(I36="Atrasado",3000+MIN(Config!$B$5-D36,60),IF(I36="Hoje",2500,IF(D36-Config!$B$5&lt;=Config!$B$6,2000-(D36-Config!$B$5),IF(D36-Config!$B$5&lt;=Config!$B$7,1000-(D36-Config!$B$5),500-MIN(D36-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>987.99964</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="31" t="inlineStr">
         <is>
-          <t>8735513-64.2025.8.26.0093</t>
+          <t>4526984-60.2026.8.26.0258</t>
         </is>
       </c>
       <c r="B37" s="31" t="inlineStr">
         <is>
-          <t>Carlos Eduardo Nunes</t>
+          <t>Transportadora Rota Sul</t>
         </is>
       </c>
       <c r="C37" s="33" t="inlineStr">
@@ -3944,8 +4502,8 @@
         </is>
       </c>
       <c r="D37" s="34">
-        <f>TODAY()+45</f>
-        <v/>
+        <f>TODAY()+16</f>
+        <v>46295.0</v>
       </c>
       <c r="E37" s="33" t="inlineStr">
         <is>
@@ -3953,77 +4511,77 @@
         </is>
       </c>
       <c r="F37" s="33" t="n"/>
-      <c r="G37" s="31" t="n"/>
+      <c r="G37" s="31" t="inlineStr">
+        <is>
+          <t>Procuração atualizada</t>
+        </is>
+      </c>
       <c r="H37" s="28">
         <f>IF(OR(I37="",I37="Feito",I37="Sem data"),"",D37-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I37" s="25">
+        <v>16</v>
+      </c>
+      <c r="I37" s="25" t="str">
         <f>IF(AND(A37="",C37="",D37=""),"",IF(F37="Sim","Feito",IF(D37="","Sem data",IF(D37&lt;Config!$B$5,"Atrasado",IF(D37=Config!$B$5,"Hoje",IF(D37-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D37-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Até 30 dias</v>
       </c>
       <c r="J37" s="35">
         <f>IF(OR(I37="",I37="Feito",I37="Sem data"),0,IF(I37="Atrasado",3000+MIN(Config!$B$5-D37,60),IF(I37="Hoje",2500,IF(D37-Config!$B$5&lt;=Config!$B$6,2000-(D37-Config!$B$5),IF(D37-Config!$B$5&lt;=Config!$B$7,1000-(D37-Config!$B$5),500-MIN(D37-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>983.99963</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="31" t="inlineStr">
         <is>
-          <t>8986364-51.2026.8.26.0700</t>
+          <t>2998500-50.2026.8.26.0515</t>
         </is>
       </c>
       <c r="B38" s="31" t="inlineStr">
         <is>
-          <t>Luciana Farias</t>
+          <t>Ana Beatriz Moreira</t>
         </is>
       </c>
       <c r="C38" s="33" t="inlineStr">
         <is>
-          <t>Juntada de documentos</t>
+          <t>Prazo interno</t>
         </is>
       </c>
       <c r="D38" s="34">
-        <f>TODAY()-6</f>
-        <v/>
+        <f>TODAY()+1</f>
+        <v>46280.0</v>
       </c>
       <c r="E38" s="33" t="inlineStr">
         <is>
-          <t>Júlia Prado</t>
-        </is>
-      </c>
-      <c r="F38" s="33" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+          <t>Rafael Lima</t>
+        </is>
+      </c>
+      <c r="F38" s="33" t="n"/>
       <c r="G38" s="31" t="inlineStr">
         <is>
-          <t>Entregue no protocolo</t>
+          <t>Preparar o cliente para a audiência</t>
         </is>
       </c>
       <c r="H38" s="28">
         <f>IF(OR(I38="",I38="Feito",I38="Sem data"),"",D38-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I38" s="25">
+        <v>1</v>
+      </c>
+      <c r="I38" s="25" t="str">
         <f>IF(AND(A38="",C38="",D38=""),"",IF(F38="Sim","Feito",IF(D38="","Sem data",IF(D38&lt;Config!$B$5,"Atrasado",IF(D38=Config!$B$5,"Hoje",IF(D38-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D38-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Até 7 dias</v>
       </c>
       <c r="J38" s="35">
         <f>IF(OR(I38="",I38="Feito",I38="Sem data"),0,IF(I38="Atrasado",3000+MIN(Config!$B$5-D38,60),IF(I38="Hoje",2500,IF(D38-Config!$B$5&lt;=Config!$B$6,2000-(D38-Config!$B$5),IF(D38-Config!$B$5&lt;=Config!$B$7,1000-(D38-Config!$B$5),500-MIN(D38-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>1998.99962</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="31" t="inlineStr">
         <is>
-          <t>1808451-67.2026.8.26.0657</t>
+          <t>9362688-24.2025.8.26.0436</t>
         </is>
       </c>
       <c r="B39" s="31" t="inlineStr">
         <is>
-          <t>Helena Duarte</t>
+          <t>Agência Prisma</t>
         </is>
       </c>
       <c r="C39" s="33" t="inlineStr">
@@ -4032,98 +4590,171 @@
         </is>
       </c>
       <c r="D39" s="34">
-        <f>TODAY()-10</f>
-        <v/>
+        <f>TODAY()+31</f>
+        <v>46310.0</v>
       </c>
       <c r="E39" s="33" t="inlineStr">
         <is>
-          <t>Rafael Lima</t>
-        </is>
-      </c>
-      <c r="F39" s="33" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
+          <t>Marina Ferraz</t>
+        </is>
+      </c>
+      <c r="F39" s="33" t="n"/>
       <c r="G39" s="31" t="inlineStr">
         <is>
-          <t>Feita por vídeo</t>
+          <t>Fechar as horas do recurso</t>
         </is>
       </c>
       <c r="H39" s="28">
         <f>IF(OR(I39="",I39="Feito",I39="Sem data"),"",D39-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I39" s="25">
+        <v>31</v>
+      </c>
+      <c r="I39" s="25" t="str">
         <f>IF(AND(A39="",C39="",D39=""),"",IF(F39="Sim","Feito",IF(D39="","Sem data",IF(D39&lt;Config!$B$5,"Atrasado",IF(D39=Config!$B$5,"Hoje",IF(D39-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D39-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Depois</v>
       </c>
       <c r="J39" s="35">
         <f>IF(OR(I39="",I39="Feito",I39="Sem data"),0,IF(I39="Atrasado",3000+MIN(Config!$B$5-D39,60),IF(I39="Hoje",2500,IF(D39-Config!$B$5&lt;=Config!$B$6,2000-(D39-Config!$B$5),IF(D39-Config!$B$5&lt;=Config!$B$7,1000-(D39-Config!$B$5),500-MIN(D39-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>468.99961</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="31" t="n"/>
-      <c r="B40" s="31" t="n"/>
-      <c r="C40" s="33" t="n"/>
-      <c r="D40" s="34" t="n"/>
-      <c r="E40" s="33" t="n"/>
+      <c r="A40" s="31" t="inlineStr">
+        <is>
+          <t>CONS-2025-05</t>
+        </is>
+      </c>
+      <c r="B40" s="31" t="inlineStr">
+        <is>
+          <t>Clínica Bem-Estar</t>
+        </is>
+      </c>
+      <c r="C40" s="33" t="inlineStr">
+        <is>
+          <t>Juntada de documentos</t>
+        </is>
+      </c>
+      <c r="D40" s="34">
+        <f>TODAY()+45</f>
+        <v>46324.0</v>
+      </c>
+      <c r="E40" s="33" t="inlineStr">
+        <is>
+          <t>Júlia Prado</t>
+        </is>
+      </c>
       <c r="F40" s="33" t="n"/>
-      <c r="G40" s="31" t="n"/>
+      <c r="G40" s="31" t="inlineStr">
+        <is>
+          <t>Alteração contratual na junta</t>
+        </is>
+      </c>
       <c r="H40" s="28">
         <f>IF(OR(I40="",I40="Feito",I40="Sem data"),"",D40-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="I40" s="25">
+        <v>45</v>
+      </c>
+      <c r="I40" s="25" t="str">
         <f>IF(AND(A40="",C40="",D40=""),"",IF(F40="Sim","Feito",IF(D40="","Sem data",IF(D40&lt;Config!$B$5,"Atrasado",IF(D40=Config!$B$5,"Hoje",IF(D40-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D40-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Depois</v>
       </c>
       <c r="J40" s="35">
         <f>IF(OR(I40="",I40="Feito",I40="Sem data"),0,IF(I40="Atrasado",3000+MIN(Config!$B$5-D40,60),IF(I40="Hoje",2500,IF(D40-Config!$B$5&lt;=Config!$B$6,2000-(D40-Config!$B$5),IF(D40-Config!$B$5&lt;=Config!$B$7,1000-(D40-Config!$B$5),500-MIN(D40-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>454.9996</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="31" t="n"/>
-      <c r="B41" s="31" t="n"/>
-      <c r="C41" s="33" t="n"/>
-      <c r="D41" s="34" t="n"/>
-      <c r="E41" s="33" t="n"/>
-      <c r="F41" s="33" t="n"/>
-      <c r="G41" s="31" t="n"/>
+      <c r="A41" s="31" t="inlineStr">
+        <is>
+          <t>5025425-10.2025.8.26.0629</t>
+        </is>
+      </c>
+      <c r="B41" s="31" t="inlineStr">
+        <is>
+          <t>Roberto Almeida</t>
+        </is>
+      </c>
+      <c r="C41" s="33" t="inlineStr">
+        <is>
+          <t>Juntada de documentos</t>
+        </is>
+      </c>
+      <c r="D41" s="34">
+        <f>TODAY()-6</f>
+        <v>46273.0</v>
+      </c>
+      <c r="E41" s="33" t="inlineStr">
+        <is>
+          <t>Júlia Prado</t>
+        </is>
+      </c>
+      <c r="F41" s="33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G41" s="31" t="inlineStr">
+        <is>
+          <t>Entregue no protocolo</t>
+        </is>
+      </c>
       <c r="H41" s="28">
         <f>IF(OR(I41="",I41="Feito",I41="Sem data"),"",D41-Config!$B$5)</f>
         <v/>
       </c>
-      <c r="I41" s="25">
+      <c r="I41" s="25" t="str">
         <f>IF(AND(A41="",C41="",D41=""),"",IF(F41="Sim","Feito",IF(D41="","Sem data",IF(D41&lt;Config!$B$5,"Atrasado",IF(D41=Config!$B$5,"Hoje",IF(D41-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D41-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Feito</v>
       </c>
       <c r="J41" s="35">
         <f>IF(OR(I41="",I41="Feito",I41="Sem data"),0,IF(I41="Atrasado",3000+MIN(Config!$B$5-D41,60),IF(I41="Hoje",2500,IF(D41-Config!$B$5&lt;=Config!$B$6,2000-(D41-Config!$B$5),IF(D41-Config!$B$5&lt;=Config!$B$7,1000-(D41-Config!$B$5),500-MIN(D41-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="31" t="n"/>
-      <c r="B42" s="31" t="n"/>
-      <c r="C42" s="33" t="n"/>
-      <c r="D42" s="34" t="n"/>
-      <c r="E42" s="33" t="n"/>
-      <c r="F42" s="33" t="n"/>
-      <c r="G42" s="31" t="n"/>
+      <c r="A42" s="31" t="inlineStr">
+        <is>
+          <t>6832730-55.2026.8.26.0386</t>
+        </is>
+      </c>
+      <c r="B42" s="31" t="inlineStr">
+        <is>
+          <t>Patrícia Gomes</t>
+        </is>
+      </c>
+      <c r="C42" s="33" t="inlineStr">
+        <is>
+          <t>Reunião com cliente</t>
+        </is>
+      </c>
+      <c r="D42" s="34">
+        <f>TODAY()-10</f>
+        <v>46269.0</v>
+      </c>
+      <c r="E42" s="33" t="inlineStr">
+        <is>
+          <t>Marina Ferraz</t>
+        </is>
+      </c>
+      <c r="F42" s="33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="G42" s="31" t="inlineStr">
+        <is>
+          <t>Feita por vídeo</t>
+        </is>
+      </c>
       <c r="H42" s="28">
         <f>IF(OR(I42="",I42="Feito",I42="Sem data"),"",D42-Config!$B$5)</f>
         <v/>
       </c>
-      <c r="I42" s="25">
+      <c r="I42" s="25" t="str">
         <f>IF(AND(A42="",C42="",D42=""),"",IF(F42="Sim","Feito",IF(D42="","Sem data",IF(D42&lt;Config!$B$5,"Atrasado",IF(D42=Config!$B$5,"Hoje",IF(D42-Config!$B$5&lt;=Config!$B$6,"Até "&amp;Config!$B$6&amp;" dias",IF(D42-Config!$B$5&lt;=Config!$B$7,"Até "&amp;Config!$B$7&amp;" dias","Depois")))))))</f>
-        <v/>
+        <v>Feito</v>
       </c>
       <c r="J42" s="35">
         <f>IF(OR(I42="",I42="Feito",I42="Sem data"),0,IF(I42="Atrasado",3000+MIN(Config!$B$5-D42,60),IF(I42="Hoje",2500,IF(D42-Config!$B$5&lt;=Config!$B$6,2000-(D42-Config!$B$5),IF(D42-Config!$B$5&lt;=Config!$B$7,1000-(D42-Config!$B$5),500-MIN(D42-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -4144,7 +4775,7 @@
       </c>
       <c r="J43" s="35">
         <f>IF(OR(I43="",I43="Feito",I43="Sem data"),0,IF(I43="Atrasado",3000+MIN(Config!$B$5-D43,60),IF(I43="Hoje",2500,IF(D43-Config!$B$5&lt;=Config!$B$6,2000-(D43-Config!$B$5),IF(D43-Config!$B$5&lt;=Config!$B$7,1000-(D43-Config!$B$5),500-MIN(D43-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -4165,7 +4796,7 @@
       </c>
       <c r="J44" s="35">
         <f>IF(OR(I44="",I44="Feito",I44="Sem data"),0,IF(I44="Atrasado",3000+MIN(Config!$B$5-D44,60),IF(I44="Hoje",2500,IF(D44-Config!$B$5&lt;=Config!$B$6,2000-(D44-Config!$B$5),IF(D44-Config!$B$5&lt;=Config!$B$7,1000-(D44-Config!$B$5),500-MIN(D44-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4186,7 +4817,7 @@
       </c>
       <c r="J45" s="35">
         <f>IF(OR(I45="",I45="Feito",I45="Sem data"),0,IF(I45="Atrasado",3000+MIN(Config!$B$5-D45,60),IF(I45="Hoje",2500,IF(D45-Config!$B$5&lt;=Config!$B$6,2000-(D45-Config!$B$5),IF(D45-Config!$B$5&lt;=Config!$B$7,1000-(D45-Config!$B$5),500-MIN(D45-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4207,7 +4838,7 @@
       </c>
       <c r="J46" s="35">
         <f>IF(OR(I46="",I46="Feito",I46="Sem data"),0,IF(I46="Atrasado",3000+MIN(Config!$B$5-D46,60),IF(I46="Hoje",2500,IF(D46-Config!$B$5&lt;=Config!$B$6,2000-(D46-Config!$B$5),IF(D46-Config!$B$5&lt;=Config!$B$7,1000-(D46-Config!$B$5),500-MIN(D46-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -4228,7 +4859,7 @@
       </c>
       <c r="J47" s="35">
         <f>IF(OR(I47="",I47="Feito",I47="Sem data"),0,IF(I47="Atrasado",3000+MIN(Config!$B$5-D47,60),IF(I47="Hoje",2500,IF(D47-Config!$B$5&lt;=Config!$B$6,2000-(D47-Config!$B$5),IF(D47-Config!$B$5&lt;=Config!$B$7,1000-(D47-Config!$B$5),500-MIN(D47-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -4249,7 +4880,7 @@
       </c>
       <c r="J48" s="35">
         <f>IF(OR(I48="",I48="Feito",I48="Sem data"),0,IF(I48="Atrasado",3000+MIN(Config!$B$5-D48,60),IF(I48="Hoje",2500,IF(D48-Config!$B$5&lt;=Config!$B$6,2000-(D48-Config!$B$5),IF(D48-Config!$B$5&lt;=Config!$B$7,1000-(D48-Config!$B$5),500-MIN(D48-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -4270,7 +4901,7 @@
       </c>
       <c r="J49" s="35">
         <f>IF(OR(I49="",I49="Feito",I49="Sem data"),0,IF(I49="Atrasado",3000+MIN(Config!$B$5-D49,60),IF(I49="Hoje",2500,IF(D49-Config!$B$5&lt;=Config!$B$6,2000-(D49-Config!$B$5),IF(D49-Config!$B$5&lt;=Config!$B$7,1000-(D49-Config!$B$5),500-MIN(D49-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -4291,7 +4922,7 @@
       </c>
       <c r="J50" s="35">
         <f>IF(OR(I50="",I50="Feito",I50="Sem data"),0,IF(I50="Atrasado",3000+MIN(Config!$B$5-D50,60),IF(I50="Hoje",2500,IF(D50-Config!$B$5&lt;=Config!$B$6,2000-(D50-Config!$B$5),IF(D50-Config!$B$5&lt;=Config!$B$7,1000-(D50-Config!$B$5),500-MIN(D50-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -4312,7 +4943,7 @@
       </c>
       <c r="J51" s="35">
         <f>IF(OR(I51="",I51="Feito",I51="Sem data"),0,IF(I51="Atrasado",3000+MIN(Config!$B$5-D51,60),IF(I51="Hoje",2500,IF(D51-Config!$B$5&lt;=Config!$B$6,2000-(D51-Config!$B$5),IF(D51-Config!$B$5&lt;=Config!$B$7,1000-(D51-Config!$B$5),500-MIN(D51-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -4333,7 +4964,7 @@
       </c>
       <c r="J52" s="35">
         <f>IF(OR(I52="",I52="Feito",I52="Sem data"),0,IF(I52="Atrasado",3000+MIN(Config!$B$5-D52,60),IF(I52="Hoje",2500,IF(D52-Config!$B$5&lt;=Config!$B$6,2000-(D52-Config!$B$5),IF(D52-Config!$B$5&lt;=Config!$B$7,1000-(D52-Config!$B$5),500-MIN(D52-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -4354,7 +4985,7 @@
       </c>
       <c r="J53" s="35">
         <f>IF(OR(I53="",I53="Feito",I53="Sem data"),0,IF(I53="Atrasado",3000+MIN(Config!$B$5-D53,60),IF(I53="Hoje",2500,IF(D53-Config!$B$5&lt;=Config!$B$6,2000-(D53-Config!$B$5),IF(D53-Config!$B$5&lt;=Config!$B$7,1000-(D53-Config!$B$5),500-MIN(D53-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -4375,7 +5006,7 @@
       </c>
       <c r="J54" s="35">
         <f>IF(OR(I54="",I54="Feito",I54="Sem data"),0,IF(I54="Atrasado",3000+MIN(Config!$B$5-D54,60),IF(I54="Hoje",2500,IF(D54-Config!$B$5&lt;=Config!$B$6,2000-(D54-Config!$B$5),IF(D54-Config!$B$5&lt;=Config!$B$7,1000-(D54-Config!$B$5),500-MIN(D54-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -4396,7 +5027,7 @@
       </c>
       <c r="J55" s="35">
         <f>IF(OR(I55="",I55="Feito",I55="Sem data"),0,IF(I55="Atrasado",3000+MIN(Config!$B$5-D55,60),IF(I55="Hoje",2500,IF(D55-Config!$B$5&lt;=Config!$B$6,2000-(D55-Config!$B$5),IF(D55-Config!$B$5&lt;=Config!$B$7,1000-(D55-Config!$B$5),500-MIN(D55-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -4417,7 +5048,7 @@
       </c>
       <c r="J56" s="35">
         <f>IF(OR(I56="",I56="Feito",I56="Sem data"),0,IF(I56="Atrasado",3000+MIN(Config!$B$5-D56,60),IF(I56="Hoje",2500,IF(D56-Config!$B$5&lt;=Config!$B$6,2000-(D56-Config!$B$5),IF(D56-Config!$B$5&lt;=Config!$B$7,1000-(D56-Config!$B$5),500-MIN(D56-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -4438,7 +5069,7 @@
       </c>
       <c r="J57" s="35">
         <f>IF(OR(I57="",I57="Feito",I57="Sem data"),0,IF(I57="Atrasado",3000+MIN(Config!$B$5-D57,60),IF(I57="Hoje",2500,IF(D57-Config!$B$5&lt;=Config!$B$6,2000-(D57-Config!$B$5),IF(D57-Config!$B$5&lt;=Config!$B$7,1000-(D57-Config!$B$5),500-MIN(D57-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -4459,7 +5090,7 @@
       </c>
       <c r="J58" s="35">
         <f>IF(OR(I58="",I58="Feito",I58="Sem data"),0,IF(I58="Atrasado",3000+MIN(Config!$B$5-D58,60),IF(I58="Hoje",2500,IF(D58-Config!$B$5&lt;=Config!$B$6,2000-(D58-Config!$B$5),IF(D58-Config!$B$5&lt;=Config!$B$7,1000-(D58-Config!$B$5),500-MIN(D58-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -4480,7 +5111,7 @@
       </c>
       <c r="J59" s="35">
         <f>IF(OR(I59="",I59="Feito",I59="Sem data"),0,IF(I59="Atrasado",3000+MIN(Config!$B$5-D59,60),IF(I59="Hoje",2500,IF(D59-Config!$B$5&lt;=Config!$B$6,2000-(D59-Config!$B$5),IF(D59-Config!$B$5&lt;=Config!$B$7,1000-(D59-Config!$B$5),500-MIN(D59-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -4501,7 +5132,7 @@
       </c>
       <c r="J60" s="35">
         <f>IF(OR(I60="",I60="Feito",I60="Sem data"),0,IF(I60="Atrasado",3000+MIN(Config!$B$5-D60,60),IF(I60="Hoje",2500,IF(D60-Config!$B$5&lt;=Config!$B$6,2000-(D60-Config!$B$5),IF(D60-Config!$B$5&lt;=Config!$B$7,1000-(D60-Config!$B$5),500-MIN(D60-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -4522,7 +5153,7 @@
       </c>
       <c r="J61" s="35">
         <f>IF(OR(I61="",I61="Feito",I61="Sem data"),0,IF(I61="Atrasado",3000+MIN(Config!$B$5-D61,60),IF(I61="Hoje",2500,IF(D61-Config!$B$5&lt;=Config!$B$6,2000-(D61-Config!$B$5),IF(D61-Config!$B$5&lt;=Config!$B$7,1000-(D61-Config!$B$5),500-MIN(D61-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -4543,7 +5174,7 @@
       </c>
       <c r="J62" s="35">
         <f>IF(OR(I62="",I62="Feito",I62="Sem data"),0,IF(I62="Atrasado",3000+MIN(Config!$B$5-D62,60),IF(I62="Hoje",2500,IF(D62-Config!$B$5&lt;=Config!$B$6,2000-(D62-Config!$B$5),IF(D62-Config!$B$5&lt;=Config!$B$7,1000-(D62-Config!$B$5),500-MIN(D62-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4564,7 +5195,7 @@
       </c>
       <c r="J63" s="35">
         <f>IF(OR(I63="",I63="Feito",I63="Sem data"),0,IF(I63="Atrasado",3000+MIN(Config!$B$5-D63,60),IF(I63="Hoje",2500,IF(D63-Config!$B$5&lt;=Config!$B$6,2000-(D63-Config!$B$5),IF(D63-Config!$B$5&lt;=Config!$B$7,1000-(D63-Config!$B$5),500-MIN(D63-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4585,7 +5216,7 @@
       </c>
       <c r="J64" s="35">
         <f>IF(OR(I64="",I64="Feito",I64="Sem data"),0,IF(I64="Atrasado",3000+MIN(Config!$B$5-D64,60),IF(I64="Hoje",2500,IF(D64-Config!$B$5&lt;=Config!$B$6,2000-(D64-Config!$B$5),IF(D64-Config!$B$5&lt;=Config!$B$7,1000-(D64-Config!$B$5),500-MIN(D64-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4606,7 +5237,7 @@
       </c>
       <c r="J65" s="35">
         <f>IF(OR(I65="",I65="Feito",I65="Sem data"),0,IF(I65="Atrasado",3000+MIN(Config!$B$5-D65,60),IF(I65="Hoje",2500,IF(D65-Config!$B$5&lt;=Config!$B$6,2000-(D65-Config!$B$5),IF(D65-Config!$B$5&lt;=Config!$B$7,1000-(D65-Config!$B$5),500-MIN(D65-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4627,7 +5258,7 @@
       </c>
       <c r="J66" s="35">
         <f>IF(OR(I66="",I66="Feito",I66="Sem data"),0,IF(I66="Atrasado",3000+MIN(Config!$B$5-D66,60),IF(I66="Hoje",2500,IF(D66-Config!$B$5&lt;=Config!$B$6,2000-(D66-Config!$B$5),IF(D66-Config!$B$5&lt;=Config!$B$7,1000-(D66-Config!$B$5),500-MIN(D66-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4648,7 +5279,7 @@
       </c>
       <c r="J67" s="35">
         <f>IF(OR(I67="",I67="Feito",I67="Sem data"),0,IF(I67="Atrasado",3000+MIN(Config!$B$5-D67,60),IF(I67="Hoje",2500,IF(D67-Config!$B$5&lt;=Config!$B$6,2000-(D67-Config!$B$5),IF(D67-Config!$B$5&lt;=Config!$B$7,1000-(D67-Config!$B$5),500-MIN(D67-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4669,7 +5300,7 @@
       </c>
       <c r="J68" s="35">
         <f>IF(OR(I68="",I68="Feito",I68="Sem data"),0,IF(I68="Atrasado",3000+MIN(Config!$B$5-D68,60),IF(I68="Hoje",2500,IF(D68-Config!$B$5&lt;=Config!$B$6,2000-(D68-Config!$B$5),IF(D68-Config!$B$5&lt;=Config!$B$7,1000-(D68-Config!$B$5),500-MIN(D68-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4690,7 +5321,7 @@
       </c>
       <c r="J69" s="35">
         <f>IF(OR(I69="",I69="Feito",I69="Sem data"),0,IF(I69="Atrasado",3000+MIN(Config!$B$5-D69,60),IF(I69="Hoje",2500,IF(D69-Config!$B$5&lt;=Config!$B$6,2000-(D69-Config!$B$5),IF(D69-Config!$B$5&lt;=Config!$B$7,1000-(D69-Config!$B$5),500-MIN(D69-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4711,7 +5342,7 @@
       </c>
       <c r="J70" s="35">
         <f>IF(OR(I70="",I70="Feito",I70="Sem data"),0,IF(I70="Atrasado",3000+MIN(Config!$B$5-D70,60),IF(I70="Hoje",2500,IF(D70-Config!$B$5&lt;=Config!$B$6,2000-(D70-Config!$B$5),IF(D70-Config!$B$5&lt;=Config!$B$7,1000-(D70-Config!$B$5),500-MIN(D70-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4732,7 +5363,7 @@
       </c>
       <c r="J71" s="35">
         <f>IF(OR(I71="",I71="Feito",I71="Sem data"),0,IF(I71="Atrasado",3000+MIN(Config!$B$5-D71,60),IF(I71="Hoje",2500,IF(D71-Config!$B$5&lt;=Config!$B$6,2000-(D71-Config!$B$5),IF(D71-Config!$B$5&lt;=Config!$B$7,1000-(D71-Config!$B$5),500-MIN(D71-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4753,7 +5384,7 @@
       </c>
       <c r="J72" s="35">
         <f>IF(OR(I72="",I72="Feito",I72="Sem data"),0,IF(I72="Atrasado",3000+MIN(Config!$B$5-D72,60),IF(I72="Hoje",2500,IF(D72-Config!$B$5&lt;=Config!$B$6,2000-(D72-Config!$B$5),IF(D72-Config!$B$5&lt;=Config!$B$7,1000-(D72-Config!$B$5),500-MIN(D72-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4774,7 +5405,7 @@
       </c>
       <c r="J73" s="35">
         <f>IF(OR(I73="",I73="Feito",I73="Sem data"),0,IF(I73="Atrasado",3000+MIN(Config!$B$5-D73,60),IF(I73="Hoje",2500,IF(D73-Config!$B$5&lt;=Config!$B$6,2000-(D73-Config!$B$5),IF(D73-Config!$B$5&lt;=Config!$B$7,1000-(D73-Config!$B$5),500-MIN(D73-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4795,7 +5426,7 @@
       </c>
       <c r="J74" s="35">
         <f>IF(OR(I74="",I74="Feito",I74="Sem data"),0,IF(I74="Atrasado",3000+MIN(Config!$B$5-D74,60),IF(I74="Hoje",2500,IF(D74-Config!$B$5&lt;=Config!$B$6,2000-(D74-Config!$B$5),IF(D74-Config!$B$5&lt;=Config!$B$7,1000-(D74-Config!$B$5),500-MIN(D74-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4816,7 +5447,7 @@
       </c>
       <c r="J75" s="35">
         <f>IF(OR(I75="",I75="Feito",I75="Sem data"),0,IF(I75="Atrasado",3000+MIN(Config!$B$5-D75,60),IF(I75="Hoje",2500,IF(D75-Config!$B$5&lt;=Config!$B$6,2000-(D75-Config!$B$5),IF(D75-Config!$B$5&lt;=Config!$B$7,1000-(D75-Config!$B$5),500-MIN(D75-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -4837,7 +5468,7 @@
       </c>
       <c r="J76" s="35">
         <f>IF(OR(I76="",I76="Feito",I76="Sem data"),0,IF(I76="Atrasado",3000+MIN(Config!$B$5-D76,60),IF(I76="Hoje",2500,IF(D76-Config!$B$5&lt;=Config!$B$6,2000-(D76-Config!$B$5),IF(D76-Config!$B$5&lt;=Config!$B$7,1000-(D76-Config!$B$5),500-MIN(D76-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4858,7 +5489,7 @@
       </c>
       <c r="J77" s="35">
         <f>IF(OR(I77="",I77="Feito",I77="Sem data"),0,IF(I77="Atrasado",3000+MIN(Config!$B$5-D77,60),IF(I77="Hoje",2500,IF(D77-Config!$B$5&lt;=Config!$B$6,2000-(D77-Config!$B$5),IF(D77-Config!$B$5&lt;=Config!$B$7,1000-(D77-Config!$B$5),500-MIN(D77-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4879,7 +5510,7 @@
       </c>
       <c r="J78" s="35">
         <f>IF(OR(I78="",I78="Feito",I78="Sem data"),0,IF(I78="Atrasado",3000+MIN(Config!$B$5-D78,60),IF(I78="Hoje",2500,IF(D78-Config!$B$5&lt;=Config!$B$6,2000-(D78-Config!$B$5),IF(D78-Config!$B$5&lt;=Config!$B$7,1000-(D78-Config!$B$5),500-MIN(D78-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4900,7 +5531,7 @@
       </c>
       <c r="J79" s="35">
         <f>IF(OR(I79="",I79="Feito",I79="Sem data"),0,IF(I79="Atrasado",3000+MIN(Config!$B$5-D79,60),IF(I79="Hoje",2500,IF(D79-Config!$B$5&lt;=Config!$B$6,2000-(D79-Config!$B$5),IF(D79-Config!$B$5&lt;=Config!$B$7,1000-(D79-Config!$B$5),500-MIN(D79-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -4921,7 +5552,7 @@
       </c>
       <c r="J80" s="35">
         <f>IF(OR(I80="",I80="Feito",I80="Sem data"),0,IF(I80="Atrasado",3000+MIN(Config!$B$5-D80,60),IF(I80="Hoje",2500,IF(D80-Config!$B$5&lt;=Config!$B$6,2000-(D80-Config!$B$5),IF(D80-Config!$B$5&lt;=Config!$B$7,1000-(D80-Config!$B$5),500-MIN(D80-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -4942,7 +5573,7 @@
       </c>
       <c r="J81" s="35">
         <f>IF(OR(I81="",I81="Feito",I81="Sem data"),0,IF(I81="Atrasado",3000+MIN(Config!$B$5-D81,60),IF(I81="Hoje",2500,IF(D81-Config!$B$5&lt;=Config!$B$6,2000-(D81-Config!$B$5),IF(D81-Config!$B$5&lt;=Config!$B$7,1000-(D81-Config!$B$5),500-MIN(D81-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -4963,7 +5594,7 @@
       </c>
       <c r="J82" s="35">
         <f>IF(OR(I82="",I82="Feito",I82="Sem data"),0,IF(I82="Atrasado",3000+MIN(Config!$B$5-D82,60),IF(I82="Hoje",2500,IF(D82-Config!$B$5&lt;=Config!$B$6,2000-(D82-Config!$B$5),IF(D82-Config!$B$5&lt;=Config!$B$7,1000-(D82-Config!$B$5),500-MIN(D82-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -4984,7 +5615,7 @@
       </c>
       <c r="J83" s="35">
         <f>IF(OR(I83="",I83="Feito",I83="Sem data"),0,IF(I83="Atrasado",3000+MIN(Config!$B$5-D83,60),IF(I83="Hoje",2500,IF(D83-Config!$B$5&lt;=Config!$B$6,2000-(D83-Config!$B$5),IF(D83-Config!$B$5&lt;=Config!$B$7,1000-(D83-Config!$B$5),500-MIN(D83-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -5005,7 +5636,7 @@
       </c>
       <c r="J84" s="35">
         <f>IF(OR(I84="",I84="Feito",I84="Sem data"),0,IF(I84="Atrasado",3000+MIN(Config!$B$5-D84,60),IF(I84="Hoje",2500,IF(D84-Config!$B$5&lt;=Config!$B$6,2000-(D84-Config!$B$5),IF(D84-Config!$B$5&lt;=Config!$B$7,1000-(D84-Config!$B$5),500-MIN(D84-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -5026,7 +5657,7 @@
       </c>
       <c r="J85" s="35">
         <f>IF(OR(I85="",I85="Feito",I85="Sem data"),0,IF(I85="Atrasado",3000+MIN(Config!$B$5-D85,60),IF(I85="Hoje",2500,IF(D85-Config!$B$5&lt;=Config!$B$6,2000-(D85-Config!$B$5),IF(D85-Config!$B$5&lt;=Config!$B$7,1000-(D85-Config!$B$5),500-MIN(D85-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -5047,7 +5678,7 @@
       </c>
       <c r="J86" s="35">
         <f>IF(OR(I86="",I86="Feito",I86="Sem data"),0,IF(I86="Atrasado",3000+MIN(Config!$B$5-D86,60),IF(I86="Hoje",2500,IF(D86-Config!$B$5&lt;=Config!$B$6,2000-(D86-Config!$B$5),IF(D86-Config!$B$5&lt;=Config!$B$7,1000-(D86-Config!$B$5),500-MIN(D86-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -5068,7 +5699,7 @@
       </c>
       <c r="J87" s="35">
         <f>IF(OR(I87="",I87="Feito",I87="Sem data"),0,IF(I87="Atrasado",3000+MIN(Config!$B$5-D87,60),IF(I87="Hoje",2500,IF(D87-Config!$B$5&lt;=Config!$B$6,2000-(D87-Config!$B$5),IF(D87-Config!$B$5&lt;=Config!$B$7,1000-(D87-Config!$B$5),500-MIN(D87-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -5089,7 +5720,7 @@
       </c>
       <c r="J88" s="35">
         <f>IF(OR(I88="",I88="Feito",I88="Sem data"),0,IF(I88="Atrasado",3000+MIN(Config!$B$5-D88,60),IF(I88="Hoje",2500,IF(D88-Config!$B$5&lt;=Config!$B$6,2000-(D88-Config!$B$5),IF(D88-Config!$B$5&lt;=Config!$B$7,1000-(D88-Config!$B$5),500-MIN(D88-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -5110,7 +5741,7 @@
       </c>
       <c r="J89" s="35">
         <f>IF(OR(I89="",I89="Feito",I89="Sem data"),0,IF(I89="Atrasado",3000+MIN(Config!$B$5-D89,60),IF(I89="Hoje",2500,IF(D89-Config!$B$5&lt;=Config!$B$6,2000-(D89-Config!$B$5),IF(D89-Config!$B$5&lt;=Config!$B$7,1000-(D89-Config!$B$5),500-MIN(D89-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -5131,7 +5762,7 @@
       </c>
       <c r="J90" s="35">
         <f>IF(OR(I90="",I90="Feito",I90="Sem data"),0,IF(I90="Atrasado",3000+MIN(Config!$B$5-D90,60),IF(I90="Hoje",2500,IF(D90-Config!$B$5&lt;=Config!$B$6,2000-(D90-Config!$B$5),IF(D90-Config!$B$5&lt;=Config!$B$7,1000-(D90-Config!$B$5),500-MIN(D90-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -5152,7 +5783,7 @@
       </c>
       <c r="J91" s="35">
         <f>IF(OR(I91="",I91="Feito",I91="Sem data"),0,IF(I91="Atrasado",3000+MIN(Config!$B$5-D91,60),IF(I91="Hoje",2500,IF(D91-Config!$B$5&lt;=Config!$B$6,2000-(D91-Config!$B$5),IF(D91-Config!$B$5&lt;=Config!$B$7,1000-(D91-Config!$B$5),500-MIN(D91-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -5173,7 +5804,7 @@
       </c>
       <c r="J92" s="35">
         <f>IF(OR(I92="",I92="Feito",I92="Sem data"),0,IF(I92="Atrasado",3000+MIN(Config!$B$5-D92,60),IF(I92="Hoje",2500,IF(D92-Config!$B$5&lt;=Config!$B$6,2000-(D92-Config!$B$5),IF(D92-Config!$B$5&lt;=Config!$B$7,1000-(D92-Config!$B$5),500-MIN(D92-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -5194,7 +5825,7 @@
       </c>
       <c r="J93" s="35">
         <f>IF(OR(I93="",I93="Feito",I93="Sem data"),0,IF(I93="Atrasado",3000+MIN(Config!$B$5-D93,60),IF(I93="Hoje",2500,IF(D93-Config!$B$5&lt;=Config!$B$6,2000-(D93-Config!$B$5),IF(D93-Config!$B$5&lt;=Config!$B$7,1000-(D93-Config!$B$5),500-MIN(D93-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -5215,7 +5846,7 @@
       </c>
       <c r="J94" s="35">
         <f>IF(OR(I94="",I94="Feito",I94="Sem data"),0,IF(I94="Atrasado",3000+MIN(Config!$B$5-D94,60),IF(I94="Hoje",2500,IF(D94-Config!$B$5&lt;=Config!$B$6,2000-(D94-Config!$B$5),IF(D94-Config!$B$5&lt;=Config!$B$7,1000-(D94-Config!$B$5),500-MIN(D94-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -5236,7 +5867,7 @@
       </c>
       <c r="J95" s="35">
         <f>IF(OR(I95="",I95="Feito",I95="Sem data"),0,IF(I95="Atrasado",3000+MIN(Config!$B$5-D95,60),IF(I95="Hoje",2500,IF(D95-Config!$B$5&lt;=Config!$B$6,2000-(D95-Config!$B$5),IF(D95-Config!$B$5&lt;=Config!$B$7,1000-(D95-Config!$B$5),500-MIN(D95-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -5257,7 +5888,7 @@
       </c>
       <c r="J96" s="35">
         <f>IF(OR(I96="",I96="Feito",I96="Sem data"),0,IF(I96="Atrasado",3000+MIN(Config!$B$5-D96,60),IF(I96="Hoje",2500,IF(D96-Config!$B$5&lt;=Config!$B$6,2000-(D96-Config!$B$5),IF(D96-Config!$B$5&lt;=Config!$B$7,1000-(D96-Config!$B$5),500-MIN(D96-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -5278,7 +5909,7 @@
       </c>
       <c r="J97" s="35">
         <f>IF(OR(I97="",I97="Feito",I97="Sem data"),0,IF(I97="Atrasado",3000+MIN(Config!$B$5-D97,60),IF(I97="Hoje",2500,IF(D97-Config!$B$5&lt;=Config!$B$6,2000-(D97-Config!$B$5),IF(D97-Config!$B$5&lt;=Config!$B$7,1000-(D97-Config!$B$5),500-MIN(D97-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -5299,7 +5930,7 @@
       </c>
       <c r="J98" s="35">
         <f>IF(OR(I98="",I98="Feito",I98="Sem data"),0,IF(I98="Atrasado",3000+MIN(Config!$B$5-D98,60),IF(I98="Hoje",2500,IF(D98-Config!$B$5&lt;=Config!$B$6,2000-(D98-Config!$B$5),IF(D98-Config!$B$5&lt;=Config!$B$7,1000-(D98-Config!$B$5),500-MIN(D98-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -5320,7 +5951,7 @@
       </c>
       <c r="J99" s="35">
         <f>IF(OR(I99="",I99="Feito",I99="Sem data"),0,IF(I99="Atrasado",3000+MIN(Config!$B$5-D99,60),IF(I99="Hoje",2500,IF(D99-Config!$B$5&lt;=Config!$B$6,2000-(D99-Config!$B$5),IF(D99-Config!$B$5&lt;=Config!$B$7,1000-(D99-Config!$B$5),500-MIN(D99-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -5341,7 +5972,7 @@
       </c>
       <c r="J100" s="35">
         <f>IF(OR(I100="",I100="Feito",I100="Sem data"),0,IF(I100="Atrasado",3000+MIN(Config!$B$5-D100,60),IF(I100="Hoje",2500,IF(D100-Config!$B$5&lt;=Config!$B$6,2000-(D100-Config!$B$5),IF(D100-Config!$B$5&lt;=Config!$B$7,1000-(D100-Config!$B$5),500-MIN(D100-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -5362,7 +5993,7 @@
       </c>
       <c r="J101" s="35">
         <f>IF(OR(I101="",I101="Feito",I101="Sem data"),0,IF(I101="Atrasado",3000+MIN(Config!$B$5-D101,60),IF(I101="Hoje",2500,IF(D101-Config!$B$5&lt;=Config!$B$6,2000-(D101-Config!$B$5),IF(D101-Config!$B$5&lt;=Config!$B$7,1000-(D101-Config!$B$5),500-MIN(D101-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -5383,7 +6014,7 @@
       </c>
       <c r="J102" s="35">
         <f>IF(OR(I102="",I102="Feito",I102="Sem data"),0,IF(I102="Atrasado",3000+MIN(Config!$B$5-D102,60),IF(I102="Hoje",2500,IF(D102-Config!$B$5&lt;=Config!$B$6,2000-(D102-Config!$B$5),IF(D102-Config!$B$5&lt;=Config!$B$7,1000-(D102-Config!$B$5),500-MIN(D102-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -5404,7 +6035,7 @@
       </c>
       <c r="J103" s="35">
         <f>IF(OR(I103="",I103="Feito",I103="Sem data"),0,IF(I103="Atrasado",3000+MIN(Config!$B$5-D103,60),IF(I103="Hoje",2500,IF(D103-Config!$B$5&lt;=Config!$B$6,2000-(D103-Config!$B$5),IF(D103-Config!$B$5&lt;=Config!$B$7,1000-(D103-Config!$B$5),500-MIN(D103-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -5425,7 +6056,7 @@
       </c>
       <c r="J104" s="35">
         <f>IF(OR(I104="",I104="Feito",I104="Sem data"),0,IF(I104="Atrasado",3000+MIN(Config!$B$5-D104,60),IF(I104="Hoje",2500,IF(D104-Config!$B$5&lt;=Config!$B$6,2000-(D104-Config!$B$5),IF(D104-Config!$B$5&lt;=Config!$B$7,1000-(D104-Config!$B$5),500-MIN(D104-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -5446,7 +6077,7 @@
       </c>
       <c r="J105" s="35">
         <f>IF(OR(I105="",I105="Feito",I105="Sem data"),0,IF(I105="Atrasado",3000+MIN(Config!$B$5-D105,60),IF(I105="Hoje",2500,IF(D105-Config!$B$5&lt;=Config!$B$6,2000-(D105-Config!$B$5),IF(D105-Config!$B$5&lt;=Config!$B$7,1000-(D105-Config!$B$5),500-MIN(D105-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -5467,7 +6098,7 @@
       </c>
       <c r="J106" s="35">
         <f>IF(OR(I106="",I106="Feito",I106="Sem data"),0,IF(I106="Atrasado",3000+MIN(Config!$B$5-D106,60),IF(I106="Hoje",2500,IF(D106-Config!$B$5&lt;=Config!$B$6,2000-(D106-Config!$B$5),IF(D106-Config!$B$5&lt;=Config!$B$7,1000-(D106-Config!$B$5),500-MIN(D106-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -5488,7 +6119,7 @@
       </c>
       <c r="J107" s="35">
         <f>IF(OR(I107="",I107="Feito",I107="Sem data"),0,IF(I107="Atrasado",3000+MIN(Config!$B$5-D107,60),IF(I107="Hoje",2500,IF(D107-Config!$B$5&lt;=Config!$B$6,2000-(D107-Config!$B$5),IF(D107-Config!$B$5&lt;=Config!$B$7,1000-(D107-Config!$B$5),500-MIN(D107-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -5509,7 +6140,7 @@
       </c>
       <c r="J108" s="35">
         <f>IF(OR(I108="",I108="Feito",I108="Sem data"),0,IF(I108="Atrasado",3000+MIN(Config!$B$5-D108,60),IF(I108="Hoje",2500,IF(D108-Config!$B$5&lt;=Config!$B$6,2000-(D108-Config!$B$5),IF(D108-Config!$B$5&lt;=Config!$B$7,1000-(D108-Config!$B$5),500-MIN(D108-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -5530,7 +6161,7 @@
       </c>
       <c r="J109" s="35">
         <f>IF(OR(I109="",I109="Feito",I109="Sem data"),0,IF(I109="Atrasado",3000+MIN(Config!$B$5-D109,60),IF(I109="Hoje",2500,IF(D109-Config!$B$5&lt;=Config!$B$6,2000-(D109-Config!$B$5),IF(D109-Config!$B$5&lt;=Config!$B$7,1000-(D109-Config!$B$5),500-MIN(D109-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -5551,7 +6182,7 @@
       </c>
       <c r="J110" s="35">
         <f>IF(OR(I110="",I110="Feito",I110="Sem data"),0,IF(I110="Atrasado",3000+MIN(Config!$B$5-D110,60),IF(I110="Hoje",2500,IF(D110-Config!$B$5&lt;=Config!$B$6,2000-(D110-Config!$B$5),IF(D110-Config!$B$5&lt;=Config!$B$7,1000-(D110-Config!$B$5),500-MIN(D110-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -5572,7 +6203,7 @@
       </c>
       <c r="J111" s="35">
         <f>IF(OR(I111="",I111="Feito",I111="Sem data"),0,IF(I111="Atrasado",3000+MIN(Config!$B$5-D111,60),IF(I111="Hoje",2500,IF(D111-Config!$B$5&lt;=Config!$B$6,2000-(D111-Config!$B$5),IF(D111-Config!$B$5&lt;=Config!$B$7,1000-(D111-Config!$B$5),500-MIN(D111-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -5593,7 +6224,7 @@
       </c>
       <c r="J112" s="35">
         <f>IF(OR(I112="",I112="Feito",I112="Sem data"),0,IF(I112="Atrasado",3000+MIN(Config!$B$5-D112,60),IF(I112="Hoje",2500,IF(D112-Config!$B$5&lt;=Config!$B$6,2000-(D112-Config!$B$5),IF(D112-Config!$B$5&lt;=Config!$B$7,1000-(D112-Config!$B$5),500-MIN(D112-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -5614,7 +6245,7 @@
       </c>
       <c r="J113" s="35">
         <f>IF(OR(I113="",I113="Feito",I113="Sem data"),0,IF(I113="Atrasado",3000+MIN(Config!$B$5-D113,60),IF(I113="Hoje",2500,IF(D113-Config!$B$5&lt;=Config!$B$6,2000-(D113-Config!$B$5),IF(D113-Config!$B$5&lt;=Config!$B$7,1000-(D113-Config!$B$5),500-MIN(D113-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -5635,7 +6266,7 @@
       </c>
       <c r="J114" s="35">
         <f>IF(OR(I114="",I114="Feito",I114="Sem data"),0,IF(I114="Atrasado",3000+MIN(Config!$B$5-D114,60),IF(I114="Hoje",2500,IF(D114-Config!$B$5&lt;=Config!$B$6,2000-(D114-Config!$B$5),IF(D114-Config!$B$5&lt;=Config!$B$7,1000-(D114-Config!$B$5),500-MIN(D114-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -5656,7 +6287,7 @@
       </c>
       <c r="J115" s="35">
         <f>IF(OR(I115="",I115="Feito",I115="Sem data"),0,IF(I115="Atrasado",3000+MIN(Config!$B$5-D115,60),IF(I115="Hoje",2500,IF(D115-Config!$B$5&lt;=Config!$B$6,2000-(D115-Config!$B$5),IF(D115-Config!$B$5&lt;=Config!$B$7,1000-(D115-Config!$B$5),500-MIN(D115-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -5677,7 +6308,7 @@
       </c>
       <c r="J116" s="35">
         <f>IF(OR(I116="",I116="Feito",I116="Sem data"),0,IF(I116="Atrasado",3000+MIN(Config!$B$5-D116,60),IF(I116="Hoje",2500,IF(D116-Config!$B$5&lt;=Config!$B$6,2000-(D116-Config!$B$5),IF(D116-Config!$B$5&lt;=Config!$B$7,1000-(D116-Config!$B$5),500-MIN(D116-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -5698,7 +6329,7 @@
       </c>
       <c r="J117" s="35">
         <f>IF(OR(I117="",I117="Feito",I117="Sem data"),0,IF(I117="Atrasado",3000+MIN(Config!$B$5-D117,60),IF(I117="Hoje",2500,IF(D117-Config!$B$5&lt;=Config!$B$6,2000-(D117-Config!$B$5),IF(D117-Config!$B$5&lt;=Config!$B$7,1000-(D117-Config!$B$5),500-MIN(D117-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -5719,7 +6350,7 @@
       </c>
       <c r="J118" s="35">
         <f>IF(OR(I118="",I118="Feito",I118="Sem data"),0,IF(I118="Atrasado",3000+MIN(Config!$B$5-D118,60),IF(I118="Hoje",2500,IF(D118-Config!$B$5&lt;=Config!$B$6,2000-(D118-Config!$B$5),IF(D118-Config!$B$5&lt;=Config!$B$7,1000-(D118-Config!$B$5),500-MIN(D118-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -5740,7 +6371,7 @@
       </c>
       <c r="J119" s="35">
         <f>IF(OR(I119="",I119="Feito",I119="Sem data"),0,IF(I119="Atrasado",3000+MIN(Config!$B$5-D119,60),IF(I119="Hoje",2500,IF(D119-Config!$B$5&lt;=Config!$B$6,2000-(D119-Config!$B$5),IF(D119-Config!$B$5&lt;=Config!$B$7,1000-(D119-Config!$B$5),500-MIN(D119-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -5761,7 +6392,7 @@
       </c>
       <c r="J120" s="35">
         <f>IF(OR(I120="",I120="Feito",I120="Sem data"),0,IF(I120="Atrasado",3000+MIN(Config!$B$5-D120,60),IF(I120="Hoje",2500,IF(D120-Config!$B$5&lt;=Config!$B$6,2000-(D120-Config!$B$5),IF(D120-Config!$B$5&lt;=Config!$B$7,1000-(D120-Config!$B$5),500-MIN(D120-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -5782,7 +6413,7 @@
       </c>
       <c r="J121" s="35">
         <f>IF(OR(I121="",I121="Feito",I121="Sem data"),0,IF(I121="Atrasado",3000+MIN(Config!$B$5-D121,60),IF(I121="Hoje",2500,IF(D121-Config!$B$5&lt;=Config!$B$6,2000-(D121-Config!$B$5),IF(D121-Config!$B$5&lt;=Config!$B$7,1000-(D121-Config!$B$5),500-MIN(D121-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -5803,7 +6434,7 @@
       </c>
       <c r="J122" s="35">
         <f>IF(OR(I122="",I122="Feito",I122="Sem data"),0,IF(I122="Atrasado",3000+MIN(Config!$B$5-D122,60),IF(I122="Hoje",2500,IF(D122-Config!$B$5&lt;=Config!$B$6,2000-(D122-Config!$B$5),IF(D122-Config!$B$5&lt;=Config!$B$7,1000-(D122-Config!$B$5),500-MIN(D122-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -5824,7 +6455,7 @@
       </c>
       <c r="J123" s="35">
         <f>IF(OR(I123="",I123="Feito",I123="Sem data"),0,IF(I123="Atrasado",3000+MIN(Config!$B$5-D123,60),IF(I123="Hoje",2500,IF(D123-Config!$B$5&lt;=Config!$B$6,2000-(D123-Config!$B$5),IF(D123-Config!$B$5&lt;=Config!$B$7,1000-(D123-Config!$B$5),500-MIN(D123-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -5845,7 +6476,7 @@
       </c>
       <c r="J124" s="35">
         <f>IF(OR(I124="",I124="Feito",I124="Sem data"),0,IF(I124="Atrasado",3000+MIN(Config!$B$5-D124,60),IF(I124="Hoje",2500,IF(D124-Config!$B$5&lt;=Config!$B$6,2000-(D124-Config!$B$5),IF(D124-Config!$B$5&lt;=Config!$B$7,1000-(D124-Config!$B$5),500-MIN(D124-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -5866,7 +6497,7 @@
       </c>
       <c r="J125" s="35">
         <f>IF(OR(I125="",I125="Feito",I125="Sem data"),0,IF(I125="Atrasado",3000+MIN(Config!$B$5-D125,60),IF(I125="Hoje",2500,IF(D125-Config!$B$5&lt;=Config!$B$6,2000-(D125-Config!$B$5),IF(D125-Config!$B$5&lt;=Config!$B$7,1000-(D125-Config!$B$5),500-MIN(D125-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -5887,7 +6518,7 @@
       </c>
       <c r="J126" s="35">
         <f>IF(OR(I126="",I126="Feito",I126="Sem data"),0,IF(I126="Atrasado",3000+MIN(Config!$B$5-D126,60),IF(I126="Hoje",2500,IF(D126-Config!$B$5&lt;=Config!$B$6,2000-(D126-Config!$B$5),IF(D126-Config!$B$5&lt;=Config!$B$7,1000-(D126-Config!$B$5),500-MIN(D126-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -5908,7 +6539,7 @@
       </c>
       <c r="J127" s="35">
         <f>IF(OR(I127="",I127="Feito",I127="Sem data"),0,IF(I127="Atrasado",3000+MIN(Config!$B$5-D127,60),IF(I127="Hoje",2500,IF(D127-Config!$B$5&lt;=Config!$B$6,2000-(D127-Config!$B$5),IF(D127-Config!$B$5&lt;=Config!$B$7,1000-(D127-Config!$B$5),500-MIN(D127-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -5929,7 +6560,7 @@
       </c>
       <c r="J128" s="35">
         <f>IF(OR(I128="",I128="Feito",I128="Sem data"),0,IF(I128="Atrasado",3000+MIN(Config!$B$5-D128,60),IF(I128="Hoje",2500,IF(D128-Config!$B$5&lt;=Config!$B$6,2000-(D128-Config!$B$5),IF(D128-Config!$B$5&lt;=Config!$B$7,1000-(D128-Config!$B$5),500-MIN(D128-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -5950,7 +6581,7 @@
       </c>
       <c r="J129" s="35">
         <f>IF(OR(I129="",I129="Feito",I129="Sem data"),0,IF(I129="Atrasado",3000+MIN(Config!$B$5-D129,60),IF(I129="Hoje",2500,IF(D129-Config!$B$5&lt;=Config!$B$6,2000-(D129-Config!$B$5),IF(D129-Config!$B$5&lt;=Config!$B$7,1000-(D129-Config!$B$5),500-MIN(D129-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -5971,7 +6602,7 @@
       </c>
       <c r="J130" s="35">
         <f>IF(OR(I130="",I130="Feito",I130="Sem data"),0,IF(I130="Atrasado",3000+MIN(Config!$B$5-D130,60),IF(I130="Hoje",2500,IF(D130-Config!$B$5&lt;=Config!$B$6,2000-(D130-Config!$B$5),IF(D130-Config!$B$5&lt;=Config!$B$7,1000-(D130-Config!$B$5),500-MIN(D130-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -5992,7 +6623,7 @@
       </c>
       <c r="J131" s="35">
         <f>IF(OR(I131="",I131="Feito",I131="Sem data"),0,IF(I131="Atrasado",3000+MIN(Config!$B$5-D131,60),IF(I131="Hoje",2500,IF(D131-Config!$B$5&lt;=Config!$B$6,2000-(D131-Config!$B$5),IF(D131-Config!$B$5&lt;=Config!$B$7,1000-(D131-Config!$B$5),500-MIN(D131-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -6013,7 +6644,7 @@
       </c>
       <c r="J132" s="35">
         <f>IF(OR(I132="",I132="Feito",I132="Sem data"),0,IF(I132="Atrasado",3000+MIN(Config!$B$5-D132,60),IF(I132="Hoje",2500,IF(D132-Config!$B$5&lt;=Config!$B$6,2000-(D132-Config!$B$5),IF(D132-Config!$B$5&lt;=Config!$B$7,1000-(D132-Config!$B$5),500-MIN(D132-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -6034,7 +6665,7 @@
       </c>
       <c r="J133" s="35">
         <f>IF(OR(I133="",I133="Feito",I133="Sem data"),0,IF(I133="Atrasado",3000+MIN(Config!$B$5-D133,60),IF(I133="Hoje",2500,IF(D133-Config!$B$5&lt;=Config!$B$6,2000-(D133-Config!$B$5),IF(D133-Config!$B$5&lt;=Config!$B$7,1000-(D133-Config!$B$5),500-MIN(D133-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -6055,7 +6686,7 @@
       </c>
       <c r="J134" s="35">
         <f>IF(OR(I134="",I134="Feito",I134="Sem data"),0,IF(I134="Atrasado",3000+MIN(Config!$B$5-D134,60),IF(I134="Hoje",2500,IF(D134-Config!$B$5&lt;=Config!$B$6,2000-(D134-Config!$B$5),IF(D134-Config!$B$5&lt;=Config!$B$7,1000-(D134-Config!$B$5),500-MIN(D134-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -6076,7 +6707,7 @@
       </c>
       <c r="J135" s="35">
         <f>IF(OR(I135="",I135="Feito",I135="Sem data"),0,IF(I135="Atrasado",3000+MIN(Config!$B$5-D135,60),IF(I135="Hoje",2500,IF(D135-Config!$B$5&lt;=Config!$B$6,2000-(D135-Config!$B$5),IF(D135-Config!$B$5&lt;=Config!$B$7,1000-(D135-Config!$B$5),500-MIN(D135-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -6097,7 +6728,7 @@
       </c>
       <c r="J136" s="35">
         <f>IF(OR(I136="",I136="Feito",I136="Sem data"),0,IF(I136="Atrasado",3000+MIN(Config!$B$5-D136,60),IF(I136="Hoje",2500,IF(D136-Config!$B$5&lt;=Config!$B$6,2000-(D136-Config!$B$5),IF(D136-Config!$B$5&lt;=Config!$B$7,1000-(D136-Config!$B$5),500-MIN(D136-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -6118,7 +6749,7 @@
       </c>
       <c r="J137" s="35">
         <f>IF(OR(I137="",I137="Feito",I137="Sem data"),0,IF(I137="Atrasado",3000+MIN(Config!$B$5-D137,60),IF(I137="Hoje",2500,IF(D137-Config!$B$5&lt;=Config!$B$6,2000-(D137-Config!$B$5),IF(D137-Config!$B$5&lt;=Config!$B$7,1000-(D137-Config!$B$5),500-MIN(D137-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -6139,7 +6770,7 @@
       </c>
       <c r="J138" s="35">
         <f>IF(OR(I138="",I138="Feito",I138="Sem data"),0,IF(I138="Atrasado",3000+MIN(Config!$B$5-D138,60),IF(I138="Hoje",2500,IF(D138-Config!$B$5&lt;=Config!$B$6,2000-(D138-Config!$B$5),IF(D138-Config!$B$5&lt;=Config!$B$7,1000-(D138-Config!$B$5),500-MIN(D138-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -6160,7 +6791,7 @@
       </c>
       <c r="J139" s="35">
         <f>IF(OR(I139="",I139="Feito",I139="Sem data"),0,IF(I139="Atrasado",3000+MIN(Config!$B$5-D139,60),IF(I139="Hoje",2500,IF(D139-Config!$B$5&lt;=Config!$B$6,2000-(D139-Config!$B$5),IF(D139-Config!$B$5&lt;=Config!$B$7,1000-(D139-Config!$B$5),500-MIN(D139-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -6181,7 +6812,7 @@
       </c>
       <c r="J140" s="35">
         <f>IF(OR(I140="",I140="Feito",I140="Sem data"),0,IF(I140="Atrasado",3000+MIN(Config!$B$5-D140,60),IF(I140="Hoje",2500,IF(D140-Config!$B$5&lt;=Config!$B$6,2000-(D140-Config!$B$5),IF(D140-Config!$B$5&lt;=Config!$B$7,1000-(D140-Config!$B$5),500-MIN(D140-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -6202,7 +6833,7 @@
       </c>
       <c r="J141" s="35">
         <f>IF(OR(I141="",I141="Feito",I141="Sem data"),0,IF(I141="Atrasado",3000+MIN(Config!$B$5-D141,60),IF(I141="Hoje",2500,IF(D141-Config!$B$5&lt;=Config!$B$6,2000-(D141-Config!$B$5),IF(D141-Config!$B$5&lt;=Config!$B$7,1000-(D141-Config!$B$5),500-MIN(D141-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -6223,7 +6854,7 @@
       </c>
       <c r="J142" s="35">
         <f>IF(OR(I142="",I142="Feito",I142="Sem data"),0,IF(I142="Atrasado",3000+MIN(Config!$B$5-D142,60),IF(I142="Hoje",2500,IF(D142-Config!$B$5&lt;=Config!$B$6,2000-(D142-Config!$B$5),IF(D142-Config!$B$5&lt;=Config!$B$7,1000-(D142-Config!$B$5),500-MIN(D142-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -6244,7 +6875,7 @@
       </c>
       <c r="J143" s="35">
         <f>IF(OR(I143="",I143="Feito",I143="Sem data"),0,IF(I143="Atrasado",3000+MIN(Config!$B$5-D143,60),IF(I143="Hoje",2500,IF(D143-Config!$B$5&lt;=Config!$B$6,2000-(D143-Config!$B$5),IF(D143-Config!$B$5&lt;=Config!$B$7,1000-(D143-Config!$B$5),500-MIN(D143-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -6265,7 +6896,7 @@
       </c>
       <c r="J144" s="35">
         <f>IF(OR(I144="",I144="Feito",I144="Sem data"),0,IF(I144="Atrasado",3000+MIN(Config!$B$5-D144,60),IF(I144="Hoje",2500,IF(D144-Config!$B$5&lt;=Config!$B$6,2000-(D144-Config!$B$5),IF(D144-Config!$B$5&lt;=Config!$B$7,1000-(D144-Config!$B$5),500-MIN(D144-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -6286,7 +6917,7 @@
       </c>
       <c r="J145" s="35">
         <f>IF(OR(I145="",I145="Feito",I145="Sem data"),0,IF(I145="Atrasado",3000+MIN(Config!$B$5-D145,60),IF(I145="Hoje",2500,IF(D145-Config!$B$5&lt;=Config!$B$6,2000-(D145-Config!$B$5),IF(D145-Config!$B$5&lt;=Config!$B$7,1000-(D145-Config!$B$5),500-MIN(D145-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -6307,7 +6938,7 @@
       </c>
       <c r="J146" s="35">
         <f>IF(OR(I146="",I146="Feito",I146="Sem data"),0,IF(I146="Atrasado",3000+MIN(Config!$B$5-D146,60),IF(I146="Hoje",2500,IF(D146-Config!$B$5&lt;=Config!$B$6,2000-(D146-Config!$B$5),IF(D146-Config!$B$5&lt;=Config!$B$7,1000-(D146-Config!$B$5),500-MIN(D146-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -6328,7 +6959,7 @@
       </c>
       <c r="J147" s="35">
         <f>IF(OR(I147="",I147="Feito",I147="Sem data"),0,IF(I147="Atrasado",3000+MIN(Config!$B$5-D147,60),IF(I147="Hoje",2500,IF(D147-Config!$B$5&lt;=Config!$B$6,2000-(D147-Config!$B$5),IF(D147-Config!$B$5&lt;=Config!$B$7,1000-(D147-Config!$B$5),500-MIN(D147-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -6349,7 +6980,7 @@
       </c>
       <c r="J148" s="35">
         <f>IF(OR(I148="",I148="Feito",I148="Sem data"),0,IF(I148="Atrasado",3000+MIN(Config!$B$5-D148,60),IF(I148="Hoje",2500,IF(D148-Config!$B$5&lt;=Config!$B$6,2000-(D148-Config!$B$5),IF(D148-Config!$B$5&lt;=Config!$B$7,1000-(D148-Config!$B$5),500-MIN(D148-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -6370,7 +7001,7 @@
       </c>
       <c r="J149" s="35">
         <f>IF(OR(I149="",I149="Feito",I149="Sem data"),0,IF(I149="Atrasado",3000+MIN(Config!$B$5-D149,60),IF(I149="Hoje",2500,IF(D149-Config!$B$5&lt;=Config!$B$6,2000-(D149-Config!$B$5),IF(D149-Config!$B$5&lt;=Config!$B$7,1000-(D149-Config!$B$5),500-MIN(D149-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -6391,7 +7022,7 @@
       </c>
       <c r="J150" s="35">
         <f>IF(OR(I150="",I150="Feito",I150="Sem data"),0,IF(I150="Atrasado",3000+MIN(Config!$B$5-D150,60),IF(I150="Hoje",2500,IF(D150-Config!$B$5&lt;=Config!$B$6,2000-(D150-Config!$B$5),IF(D150-Config!$B$5&lt;=Config!$B$7,1000-(D150-Config!$B$5),500-MIN(D150-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -6412,7 +7043,7 @@
       </c>
       <c r="J151" s="35">
         <f>IF(OR(I151="",I151="Feito",I151="Sem data"),0,IF(I151="Atrasado",3000+MIN(Config!$B$5-D151,60),IF(I151="Hoje",2500,IF(D151-Config!$B$5&lt;=Config!$B$6,2000-(D151-Config!$B$5),IF(D151-Config!$B$5&lt;=Config!$B$7,1000-(D151-Config!$B$5),500-MIN(D151-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -6433,7 +7064,7 @@
       </c>
       <c r="J152" s="35">
         <f>IF(OR(I152="",I152="Feito",I152="Sem data"),0,IF(I152="Atrasado",3000+MIN(Config!$B$5-D152,60),IF(I152="Hoje",2500,IF(D152-Config!$B$5&lt;=Config!$B$6,2000-(D152-Config!$B$5),IF(D152-Config!$B$5&lt;=Config!$B$7,1000-(D152-Config!$B$5),500-MIN(D152-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -6454,7 +7085,7 @@
       </c>
       <c r="J153" s="35">
         <f>IF(OR(I153="",I153="Feito",I153="Sem data"),0,IF(I153="Atrasado",3000+MIN(Config!$B$5-D153,60),IF(I153="Hoje",2500,IF(D153-Config!$B$5&lt;=Config!$B$6,2000-(D153-Config!$B$5),IF(D153-Config!$B$5&lt;=Config!$B$7,1000-(D153-Config!$B$5),500-MIN(D153-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -6475,7 +7106,7 @@
       </c>
       <c r="J154" s="35">
         <f>IF(OR(I154="",I154="Feito",I154="Sem data"),0,IF(I154="Atrasado",3000+MIN(Config!$B$5-D154,60),IF(I154="Hoje",2500,IF(D154-Config!$B$5&lt;=Config!$B$6,2000-(D154-Config!$B$5),IF(D154-Config!$B$5&lt;=Config!$B$7,1000-(D154-Config!$B$5),500-MIN(D154-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -6496,7 +7127,7 @@
       </c>
       <c r="J155" s="35">
         <f>IF(OR(I155="",I155="Feito",I155="Sem data"),0,IF(I155="Atrasado",3000+MIN(Config!$B$5-D155,60),IF(I155="Hoje",2500,IF(D155-Config!$B$5&lt;=Config!$B$6,2000-(D155-Config!$B$5),IF(D155-Config!$B$5&lt;=Config!$B$7,1000-(D155-Config!$B$5),500-MIN(D155-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -6517,7 +7148,7 @@
       </c>
       <c r="J156" s="35">
         <f>IF(OR(I156="",I156="Feito",I156="Sem data"),0,IF(I156="Atrasado",3000+MIN(Config!$B$5-D156,60),IF(I156="Hoje",2500,IF(D156-Config!$B$5&lt;=Config!$B$6,2000-(D156-Config!$B$5),IF(D156-Config!$B$5&lt;=Config!$B$7,1000-(D156-Config!$B$5),500-MIN(D156-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -6538,7 +7169,7 @@
       </c>
       <c r="J157" s="35">
         <f>IF(OR(I157="",I157="Feito",I157="Sem data"),0,IF(I157="Atrasado",3000+MIN(Config!$B$5-D157,60),IF(I157="Hoje",2500,IF(D157-Config!$B$5&lt;=Config!$B$6,2000-(D157-Config!$B$5),IF(D157-Config!$B$5&lt;=Config!$B$7,1000-(D157-Config!$B$5),500-MIN(D157-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -6559,7 +7190,7 @@
       </c>
       <c r="J158" s="35">
         <f>IF(OR(I158="",I158="Feito",I158="Sem data"),0,IF(I158="Atrasado",3000+MIN(Config!$B$5-D158,60),IF(I158="Hoje",2500,IF(D158-Config!$B$5&lt;=Config!$B$6,2000-(D158-Config!$B$5),IF(D158-Config!$B$5&lt;=Config!$B$7,1000-(D158-Config!$B$5),500-MIN(D158-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -6580,7 +7211,7 @@
       </c>
       <c r="J159" s="35">
         <f>IF(OR(I159="",I159="Feito",I159="Sem data"),0,IF(I159="Atrasado",3000+MIN(Config!$B$5-D159,60),IF(I159="Hoje",2500,IF(D159-Config!$B$5&lt;=Config!$B$6,2000-(D159-Config!$B$5),IF(D159-Config!$B$5&lt;=Config!$B$7,1000-(D159-Config!$B$5),500-MIN(D159-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -6601,7 +7232,7 @@
       </c>
       <c r="J160" s="35">
         <f>IF(OR(I160="",I160="Feito",I160="Sem data"),0,IF(I160="Atrasado",3000+MIN(Config!$B$5-D160,60),IF(I160="Hoje",2500,IF(D160-Config!$B$5&lt;=Config!$B$6,2000-(D160-Config!$B$5),IF(D160-Config!$B$5&lt;=Config!$B$7,1000-(D160-Config!$B$5),500-MIN(D160-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -6622,7 +7253,7 @@
       </c>
       <c r="J161" s="35">
         <f>IF(OR(I161="",I161="Feito",I161="Sem data"),0,IF(I161="Atrasado",3000+MIN(Config!$B$5-D161,60),IF(I161="Hoje",2500,IF(D161-Config!$B$5&lt;=Config!$B$6,2000-(D161-Config!$B$5),IF(D161-Config!$B$5&lt;=Config!$B$7,1000-(D161-Config!$B$5),500-MIN(D161-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -6643,7 +7274,7 @@
       </c>
       <c r="J162" s="35">
         <f>IF(OR(I162="",I162="Feito",I162="Sem data"),0,IF(I162="Atrasado",3000+MIN(Config!$B$5-D162,60),IF(I162="Hoje",2500,IF(D162-Config!$B$5&lt;=Config!$B$6,2000-(D162-Config!$B$5),IF(D162-Config!$B$5&lt;=Config!$B$7,1000-(D162-Config!$B$5),500-MIN(D162-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -6664,7 +7295,7 @@
       </c>
       <c r="J163" s="35">
         <f>IF(OR(I163="",I163="Feito",I163="Sem data"),0,IF(I163="Atrasado",3000+MIN(Config!$B$5-D163,60),IF(I163="Hoje",2500,IF(D163-Config!$B$5&lt;=Config!$B$6,2000-(D163-Config!$B$5),IF(D163-Config!$B$5&lt;=Config!$B$7,1000-(D163-Config!$B$5),500-MIN(D163-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -6685,7 +7316,7 @@
       </c>
       <c r="J164" s="35">
         <f>IF(OR(I164="",I164="Feito",I164="Sem data"),0,IF(I164="Atrasado",3000+MIN(Config!$B$5-D164,60),IF(I164="Hoje",2500,IF(D164-Config!$B$5&lt;=Config!$B$6,2000-(D164-Config!$B$5),IF(D164-Config!$B$5&lt;=Config!$B$7,1000-(D164-Config!$B$5),500-MIN(D164-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -6706,7 +7337,7 @@
       </c>
       <c r="J165" s="35">
         <f>IF(OR(I165="",I165="Feito",I165="Sem data"),0,IF(I165="Atrasado",3000+MIN(Config!$B$5-D165,60),IF(I165="Hoje",2500,IF(D165-Config!$B$5&lt;=Config!$B$6,2000-(D165-Config!$B$5),IF(D165-Config!$B$5&lt;=Config!$B$7,1000-(D165-Config!$B$5),500-MIN(D165-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -6727,7 +7358,7 @@
       </c>
       <c r="J166" s="35">
         <f>IF(OR(I166="",I166="Feito",I166="Sem data"),0,IF(I166="Atrasado",3000+MIN(Config!$B$5-D166,60),IF(I166="Hoje",2500,IF(D166-Config!$B$5&lt;=Config!$B$6,2000-(D166-Config!$B$5),IF(D166-Config!$B$5&lt;=Config!$B$7,1000-(D166-Config!$B$5),500-MIN(D166-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -6748,7 +7379,7 @@
       </c>
       <c r="J167" s="35">
         <f>IF(OR(I167="",I167="Feito",I167="Sem data"),0,IF(I167="Atrasado",3000+MIN(Config!$B$5-D167,60),IF(I167="Hoje",2500,IF(D167-Config!$B$5&lt;=Config!$B$6,2000-(D167-Config!$B$5),IF(D167-Config!$B$5&lt;=Config!$B$7,1000-(D167-Config!$B$5),500-MIN(D167-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -6769,7 +7400,7 @@
       </c>
       <c r="J168" s="35">
         <f>IF(OR(I168="",I168="Feito",I168="Sem data"),0,IF(I168="Atrasado",3000+MIN(Config!$B$5-D168,60),IF(I168="Hoje",2500,IF(D168-Config!$B$5&lt;=Config!$B$6,2000-(D168-Config!$B$5),IF(D168-Config!$B$5&lt;=Config!$B$7,1000-(D168-Config!$B$5),500-MIN(D168-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -6790,7 +7421,7 @@
       </c>
       <c r="J169" s="35">
         <f>IF(OR(I169="",I169="Feito",I169="Sem data"),0,IF(I169="Atrasado",3000+MIN(Config!$B$5-D169,60),IF(I169="Hoje",2500,IF(D169-Config!$B$5&lt;=Config!$B$6,2000-(D169-Config!$B$5),IF(D169-Config!$B$5&lt;=Config!$B$7,1000-(D169-Config!$B$5),500-MIN(D169-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -6811,7 +7442,7 @@
       </c>
       <c r="J170" s="35">
         <f>IF(OR(I170="",I170="Feito",I170="Sem data"),0,IF(I170="Atrasado",3000+MIN(Config!$B$5-D170,60),IF(I170="Hoje",2500,IF(D170-Config!$B$5&lt;=Config!$B$6,2000-(D170-Config!$B$5),IF(D170-Config!$B$5&lt;=Config!$B$7,1000-(D170-Config!$B$5),500-MIN(D170-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -6832,7 +7463,7 @@
       </c>
       <c r="J171" s="35">
         <f>IF(OR(I171="",I171="Feito",I171="Sem data"),0,IF(I171="Atrasado",3000+MIN(Config!$B$5-D171,60),IF(I171="Hoje",2500,IF(D171-Config!$B$5&lt;=Config!$B$6,2000-(D171-Config!$B$5),IF(D171-Config!$B$5&lt;=Config!$B$7,1000-(D171-Config!$B$5),500-MIN(D171-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -6853,7 +7484,7 @@
       </c>
       <c r="J172" s="35">
         <f>IF(OR(I172="",I172="Feito",I172="Sem data"),0,IF(I172="Atrasado",3000+MIN(Config!$B$5-D172,60),IF(I172="Hoje",2500,IF(D172-Config!$B$5&lt;=Config!$B$6,2000-(D172-Config!$B$5),IF(D172-Config!$B$5&lt;=Config!$B$7,1000-(D172-Config!$B$5),500-MIN(D172-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -6874,7 +7505,7 @@
       </c>
       <c r="J173" s="35">
         <f>IF(OR(I173="",I173="Feito",I173="Sem data"),0,IF(I173="Atrasado",3000+MIN(Config!$B$5-D173,60),IF(I173="Hoje",2500,IF(D173-Config!$B$5&lt;=Config!$B$6,2000-(D173-Config!$B$5),IF(D173-Config!$B$5&lt;=Config!$B$7,1000-(D173-Config!$B$5),500-MIN(D173-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -6895,7 +7526,7 @@
       </c>
       <c r="J174" s="35">
         <f>IF(OR(I174="",I174="Feito",I174="Sem data"),0,IF(I174="Atrasado",3000+MIN(Config!$B$5-D174,60),IF(I174="Hoje",2500,IF(D174-Config!$B$5&lt;=Config!$B$6,2000-(D174-Config!$B$5),IF(D174-Config!$B$5&lt;=Config!$B$7,1000-(D174-Config!$B$5),500-MIN(D174-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -6916,7 +7547,7 @@
       </c>
       <c r="J175" s="35">
         <f>IF(OR(I175="",I175="Feito",I175="Sem data"),0,IF(I175="Atrasado",3000+MIN(Config!$B$5-D175,60),IF(I175="Hoje",2500,IF(D175-Config!$B$5&lt;=Config!$B$6,2000-(D175-Config!$B$5),IF(D175-Config!$B$5&lt;=Config!$B$7,1000-(D175-Config!$B$5),500-MIN(D175-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -6937,7 +7568,7 @@
       </c>
       <c r="J176" s="35">
         <f>IF(OR(I176="",I176="Feito",I176="Sem data"),0,IF(I176="Atrasado",3000+MIN(Config!$B$5-D176,60),IF(I176="Hoje",2500,IF(D176-Config!$B$5&lt;=Config!$B$6,2000-(D176-Config!$B$5),IF(D176-Config!$B$5&lt;=Config!$B$7,1000-(D176-Config!$B$5),500-MIN(D176-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -6958,7 +7589,7 @@
       </c>
       <c r="J177" s="35">
         <f>IF(OR(I177="",I177="Feito",I177="Sem data"),0,IF(I177="Atrasado",3000+MIN(Config!$B$5-D177,60),IF(I177="Hoje",2500,IF(D177-Config!$B$5&lt;=Config!$B$6,2000-(D177-Config!$B$5),IF(D177-Config!$B$5&lt;=Config!$B$7,1000-(D177-Config!$B$5),500-MIN(D177-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -6979,7 +7610,7 @@
       </c>
       <c r="J178" s="35">
         <f>IF(OR(I178="",I178="Feito",I178="Sem data"),0,IF(I178="Atrasado",3000+MIN(Config!$B$5-D178,60),IF(I178="Hoje",2500,IF(D178-Config!$B$5&lt;=Config!$B$6,2000-(D178-Config!$B$5),IF(D178-Config!$B$5&lt;=Config!$B$7,1000-(D178-Config!$B$5),500-MIN(D178-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -7000,7 +7631,7 @@
       </c>
       <c r="J179" s="35">
         <f>IF(OR(I179="",I179="Feito",I179="Sem data"),0,IF(I179="Atrasado",3000+MIN(Config!$B$5-D179,60),IF(I179="Hoje",2500,IF(D179-Config!$B$5&lt;=Config!$B$6,2000-(D179-Config!$B$5),IF(D179-Config!$B$5&lt;=Config!$B$7,1000-(D179-Config!$B$5),500-MIN(D179-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -7021,7 +7652,7 @@
       </c>
       <c r="J180" s="35">
         <f>IF(OR(I180="",I180="Feito",I180="Sem data"),0,IF(I180="Atrasado",3000+MIN(Config!$B$5-D180,60),IF(I180="Hoje",2500,IF(D180-Config!$B$5&lt;=Config!$B$6,2000-(D180-Config!$B$5),IF(D180-Config!$B$5&lt;=Config!$B$7,1000-(D180-Config!$B$5),500-MIN(D180-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -7042,7 +7673,7 @@
       </c>
       <c r="J181" s="35">
         <f>IF(OR(I181="",I181="Feito",I181="Sem data"),0,IF(I181="Atrasado",3000+MIN(Config!$B$5-D181,60),IF(I181="Hoje",2500,IF(D181-Config!$B$5&lt;=Config!$B$6,2000-(D181-Config!$B$5),IF(D181-Config!$B$5&lt;=Config!$B$7,1000-(D181-Config!$B$5),500-MIN(D181-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -7063,7 +7694,7 @@
       </c>
       <c r="J182" s="35">
         <f>IF(OR(I182="",I182="Feito",I182="Sem data"),0,IF(I182="Atrasado",3000+MIN(Config!$B$5-D182,60),IF(I182="Hoje",2500,IF(D182-Config!$B$5&lt;=Config!$B$6,2000-(D182-Config!$B$5),IF(D182-Config!$B$5&lt;=Config!$B$7,1000-(D182-Config!$B$5),500-MIN(D182-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -7084,7 +7715,7 @@
       </c>
       <c r="J183" s="35">
         <f>IF(OR(I183="",I183="Feito",I183="Sem data"),0,IF(I183="Atrasado",3000+MIN(Config!$B$5-D183,60),IF(I183="Hoje",2500,IF(D183-Config!$B$5&lt;=Config!$B$6,2000-(D183-Config!$B$5),IF(D183-Config!$B$5&lt;=Config!$B$7,1000-(D183-Config!$B$5),500-MIN(D183-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -7105,7 +7736,7 @@
       </c>
       <c r="J184" s="35">
         <f>IF(OR(I184="",I184="Feito",I184="Sem data"),0,IF(I184="Atrasado",3000+MIN(Config!$B$5-D184,60),IF(I184="Hoje",2500,IF(D184-Config!$B$5&lt;=Config!$B$6,2000-(D184-Config!$B$5),IF(D184-Config!$B$5&lt;=Config!$B$7,1000-(D184-Config!$B$5),500-MIN(D184-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -7126,7 +7757,7 @@
       </c>
       <c r="J185" s="35">
         <f>IF(OR(I185="",I185="Feito",I185="Sem data"),0,IF(I185="Atrasado",3000+MIN(Config!$B$5-D185,60),IF(I185="Hoje",2500,IF(D185-Config!$B$5&lt;=Config!$B$6,2000-(D185-Config!$B$5),IF(D185-Config!$B$5&lt;=Config!$B$7,1000-(D185-Config!$B$5),500-MIN(D185-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -7147,7 +7778,7 @@
       </c>
       <c r="J186" s="35">
         <f>IF(OR(I186="",I186="Feito",I186="Sem data"),0,IF(I186="Atrasado",3000+MIN(Config!$B$5-D186,60),IF(I186="Hoje",2500,IF(D186-Config!$B$5&lt;=Config!$B$6,2000-(D186-Config!$B$5),IF(D186-Config!$B$5&lt;=Config!$B$7,1000-(D186-Config!$B$5),500-MIN(D186-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -7168,7 +7799,7 @@
       </c>
       <c r="J187" s="35">
         <f>IF(OR(I187="",I187="Feito",I187="Sem data"),0,IF(I187="Atrasado",3000+MIN(Config!$B$5-D187,60),IF(I187="Hoje",2500,IF(D187-Config!$B$5&lt;=Config!$B$6,2000-(D187-Config!$B$5),IF(D187-Config!$B$5&lt;=Config!$B$7,1000-(D187-Config!$B$5),500-MIN(D187-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
@@ -7189,7 +7820,7 @@
       </c>
       <c r="J188" s="35">
         <f>IF(OR(I188="",I188="Feito",I188="Sem data"),0,IF(I188="Atrasado",3000+MIN(Config!$B$5-D188,60),IF(I188="Hoje",2500,IF(D188-Config!$B$5&lt;=Config!$B$6,2000-(D188-Config!$B$5),IF(D188-Config!$B$5&lt;=Config!$B$7,1000-(D188-Config!$B$5),500-MIN(D188-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -7210,7 +7841,7 @@
       </c>
       <c r="J189" s="35">
         <f>IF(OR(I189="",I189="Feito",I189="Sem data"),0,IF(I189="Atrasado",3000+MIN(Config!$B$5-D189,60),IF(I189="Hoje",2500,IF(D189-Config!$B$5&lt;=Config!$B$6,2000-(D189-Config!$B$5),IF(D189-Config!$B$5&lt;=Config!$B$7,1000-(D189-Config!$B$5),500-MIN(D189-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -7231,7 +7862,7 @@
       </c>
       <c r="J190" s="35">
         <f>IF(OR(I190="",I190="Feito",I190="Sem data"),0,IF(I190="Atrasado",3000+MIN(Config!$B$5-D190,60),IF(I190="Hoje",2500,IF(D190-Config!$B$5&lt;=Config!$B$6,2000-(D190-Config!$B$5),IF(D190-Config!$B$5&lt;=Config!$B$7,1000-(D190-Config!$B$5),500-MIN(D190-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -7252,7 +7883,7 @@
       </c>
       <c r="J191" s="35">
         <f>IF(OR(I191="",I191="Feito",I191="Sem data"),0,IF(I191="Atrasado",3000+MIN(Config!$B$5-D191,60),IF(I191="Hoje",2500,IF(D191-Config!$B$5&lt;=Config!$B$6,2000-(D191-Config!$B$5),IF(D191-Config!$B$5&lt;=Config!$B$7,1000-(D191-Config!$B$5),500-MIN(D191-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -7273,7 +7904,7 @@
       </c>
       <c r="J192" s="35">
         <f>IF(OR(I192="",I192="Feito",I192="Sem data"),0,IF(I192="Atrasado",3000+MIN(Config!$B$5-D192,60),IF(I192="Hoje",2500,IF(D192-Config!$B$5&lt;=Config!$B$6,2000-(D192-Config!$B$5),IF(D192-Config!$B$5&lt;=Config!$B$7,1000-(D192-Config!$B$5),500-MIN(D192-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -7294,7 +7925,7 @@
       </c>
       <c r="J193" s="35">
         <f>IF(OR(I193="",I193="Feito",I193="Sem data"),0,IF(I193="Atrasado",3000+MIN(Config!$B$5-D193,60),IF(I193="Hoje",2500,IF(D193-Config!$B$5&lt;=Config!$B$6,2000-(D193-Config!$B$5),IF(D193-Config!$B$5&lt;=Config!$B$7,1000-(D193-Config!$B$5),500-MIN(D193-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -7315,7 +7946,7 @@
       </c>
       <c r="J194" s="35">
         <f>IF(OR(I194="",I194="Feito",I194="Sem data"),0,IF(I194="Atrasado",3000+MIN(Config!$B$5-D194,60),IF(I194="Hoje",2500,IF(D194-Config!$B$5&lt;=Config!$B$6,2000-(D194-Config!$B$5),IF(D194-Config!$B$5&lt;=Config!$B$7,1000-(D194-Config!$B$5),500-MIN(D194-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -7336,7 +7967,7 @@
       </c>
       <c r="J195" s="35">
         <f>IF(OR(I195="",I195="Feito",I195="Sem data"),0,IF(I195="Atrasado",3000+MIN(Config!$B$5-D195,60),IF(I195="Hoje",2500,IF(D195-Config!$B$5&lt;=Config!$B$6,2000-(D195-Config!$B$5),IF(D195-Config!$B$5&lt;=Config!$B$7,1000-(D195-Config!$B$5),500-MIN(D195-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -7357,7 +7988,7 @@
       </c>
       <c r="J196" s="35">
         <f>IF(OR(I196="",I196="Feito",I196="Sem data"),0,IF(I196="Atrasado",3000+MIN(Config!$B$5-D196,60),IF(I196="Hoje",2500,IF(D196-Config!$B$5&lt;=Config!$B$6,2000-(D196-Config!$B$5),IF(D196-Config!$B$5&lt;=Config!$B$7,1000-(D196-Config!$B$5),500-MIN(D196-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -7378,7 +8009,7 @@
       </c>
       <c r="J197" s="35">
         <f>IF(OR(I197="",I197="Feito",I197="Sem data"),0,IF(I197="Atrasado",3000+MIN(Config!$B$5-D197,60),IF(I197="Hoje",2500,IF(D197-Config!$B$5&lt;=Config!$B$6,2000-(D197-Config!$B$5),IF(D197-Config!$B$5&lt;=Config!$B$7,1000-(D197-Config!$B$5),500-MIN(D197-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -7399,7 +8030,7 @@
       </c>
       <c r="J198" s="35">
         <f>IF(OR(I198="",I198="Feito",I198="Sem data"),0,IF(I198="Atrasado",3000+MIN(Config!$B$5-D198,60),IF(I198="Hoje",2500,IF(D198-Config!$B$5&lt;=Config!$B$6,2000-(D198-Config!$B$5),IF(D198-Config!$B$5&lt;=Config!$B$7,1000-(D198-Config!$B$5),500-MIN(D198-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -7420,7 +8051,7 @@
       </c>
       <c r="J199" s="35">
         <f>IF(OR(I199="",I199="Feito",I199="Sem data"),0,IF(I199="Atrasado",3000+MIN(Config!$B$5-D199,60),IF(I199="Hoje",2500,IF(D199-Config!$B$5&lt;=Config!$B$6,2000-(D199-Config!$B$5),IF(D199-Config!$B$5&lt;=Config!$B$7,1000-(D199-Config!$B$5),500-MIN(D199-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -7441,7 +8072,7 @@
       </c>
       <c r="J200" s="35">
         <f>IF(OR(I200="",I200="Feito",I200="Sem data"),0,IF(I200="Atrasado",3000+MIN(Config!$B$5-D200,60),IF(I200="Hoje",2500,IF(D200-Config!$B$5&lt;=Config!$B$6,2000-(D200-Config!$B$5),IF(D200-Config!$B$5&lt;=Config!$B$7,1000-(D200-Config!$B$5),500-MIN(D200-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
@@ -7462,7 +8093,7 @@
       </c>
       <c r="J201" s="35">
         <f>IF(OR(I201="",I201="Feito",I201="Sem data"),0,IF(I201="Atrasado",3000+MIN(Config!$B$5-D201,60),IF(I201="Hoje",2500,IF(D201-Config!$B$5&lt;=Config!$B$6,2000-(D201-Config!$B$5),IF(D201-Config!$B$5&lt;=Config!$B$7,1000-(D201-Config!$B$5),500-MIN(D201-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="202">
@@ -7483,7 +8114,7 @@
       </c>
       <c r="J202" s="35">
         <f>IF(OR(I202="",I202="Feito",I202="Sem data"),0,IF(I202="Atrasado",3000+MIN(Config!$B$5-D202,60),IF(I202="Hoje",2500,IF(D202-Config!$B$5&lt;=Config!$B$6,2000-(D202-Config!$B$5),IF(D202-Config!$B$5&lt;=Config!$B$7,1000-(D202-Config!$B$5),500-MIN(D202-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -7504,7 +8135,7 @@
       </c>
       <c r="J203" s="35">
         <f>IF(OR(I203="",I203="Feito",I203="Sem data"),0,IF(I203="Atrasado",3000+MIN(Config!$B$5-D203,60),IF(I203="Hoje",2500,IF(D203-Config!$B$5&lt;=Config!$B$6,2000-(D203-Config!$B$5),IF(D203-Config!$B$5&lt;=Config!$B$7,1000-(D203-Config!$B$5),500-MIN(D203-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="204">
@@ -7525,7 +8156,7 @@
       </c>
       <c r="J204" s="35">
         <f>IF(OR(I204="",I204="Feito",I204="Sem data"),0,IF(I204="Atrasado",3000+MIN(Config!$B$5-D204,60),IF(I204="Hoje",2500,IF(D204-Config!$B$5&lt;=Config!$B$6,2000-(D204-Config!$B$5),IF(D204-Config!$B$5&lt;=Config!$B$7,1000-(D204-Config!$B$5),500-MIN(D204-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
@@ -7546,7 +8177,7 @@
       </c>
       <c r="J205" s="35">
         <f>IF(OR(I205="",I205="Feito",I205="Sem data"),0,IF(I205="Atrasado",3000+MIN(Config!$B$5-D205,60),IF(I205="Hoje",2500,IF(D205-Config!$B$5&lt;=Config!$B$6,2000-(D205-Config!$B$5),IF(D205-Config!$B$5&lt;=Config!$B$7,1000-(D205-Config!$B$5),500-MIN(D205-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -7567,7 +8198,7 @@
       </c>
       <c r="J206" s="35">
         <f>IF(OR(I206="",I206="Feito",I206="Sem data"),0,IF(I206="Atrasado",3000+MIN(Config!$B$5-D206,60),IF(I206="Hoje",2500,IF(D206-Config!$B$5&lt;=Config!$B$6,2000-(D206-Config!$B$5),IF(D206-Config!$B$5&lt;=Config!$B$7,1000-(D206-Config!$B$5),500-MIN(D206-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -7588,7 +8219,7 @@
       </c>
       <c r="J207" s="35">
         <f>IF(OR(I207="",I207="Feito",I207="Sem data"),0,IF(I207="Atrasado",3000+MIN(Config!$B$5-D207,60),IF(I207="Hoje",2500,IF(D207-Config!$B$5&lt;=Config!$B$6,2000-(D207-Config!$B$5),IF(D207-Config!$B$5&lt;=Config!$B$7,1000-(D207-Config!$B$5),500-MIN(D207-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -7609,7 +8240,7 @@
       </c>
       <c r="J208" s="35">
         <f>IF(OR(I208="",I208="Feito",I208="Sem data"),0,IF(I208="Atrasado",3000+MIN(Config!$B$5-D208,60),IF(I208="Hoje",2500,IF(D208-Config!$B$5&lt;=Config!$B$6,2000-(D208-Config!$B$5),IF(D208-Config!$B$5&lt;=Config!$B$7,1000-(D208-Config!$B$5),500-MIN(D208-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="209">
@@ -7630,7 +8261,7 @@
       </c>
       <c r="J209" s="35">
         <f>IF(OR(I209="",I209="Feito",I209="Sem data"),0,IF(I209="Atrasado",3000+MIN(Config!$B$5-D209,60),IF(I209="Hoje",2500,IF(D209-Config!$B$5&lt;=Config!$B$6,2000-(D209-Config!$B$5),IF(D209-Config!$B$5&lt;=Config!$B$7,1000-(D209-Config!$B$5),500-MIN(D209-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="210">
@@ -7651,7 +8282,7 @@
       </c>
       <c r="J210" s="35">
         <f>IF(OR(I210="",I210="Feito",I210="Sem data"),0,IF(I210="Atrasado",3000+MIN(Config!$B$5-D210,60),IF(I210="Hoje",2500,IF(D210-Config!$B$5&lt;=Config!$B$6,2000-(D210-Config!$B$5),IF(D210-Config!$B$5&lt;=Config!$B$7,1000-(D210-Config!$B$5),500-MIN(D210-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
@@ -7672,7 +8303,7 @@
       </c>
       <c r="J211" s="35">
         <f>IF(OR(I211="",I211="Feito",I211="Sem data"),0,IF(I211="Atrasado",3000+MIN(Config!$B$5-D211,60),IF(I211="Hoje",2500,IF(D211-Config!$B$5&lt;=Config!$B$6,2000-(D211-Config!$B$5),IF(D211-Config!$B$5&lt;=Config!$B$7,1000-(D211-Config!$B$5),500-MIN(D211-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="212">
@@ -7693,7 +8324,7 @@
       </c>
       <c r="J212" s="35">
         <f>IF(OR(I212="",I212="Feito",I212="Sem data"),0,IF(I212="Atrasado",3000+MIN(Config!$B$5-D212,60),IF(I212="Hoje",2500,IF(D212-Config!$B$5&lt;=Config!$B$6,2000-(D212-Config!$B$5),IF(D212-Config!$B$5&lt;=Config!$B$7,1000-(D212-Config!$B$5),500-MIN(D212-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="213">
@@ -7714,7 +8345,7 @@
       </c>
       <c r="J213" s="35">
         <f>IF(OR(I213="",I213="Feito",I213="Sem data"),0,IF(I213="Atrasado",3000+MIN(Config!$B$5-D213,60),IF(I213="Hoje",2500,IF(D213-Config!$B$5&lt;=Config!$B$6,2000-(D213-Config!$B$5),IF(D213-Config!$B$5&lt;=Config!$B$7,1000-(D213-Config!$B$5),500-MIN(D213-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -7735,7 +8366,7 @@
       </c>
       <c r="J214" s="35">
         <f>IF(OR(I214="",I214="Feito",I214="Sem data"),0,IF(I214="Atrasado",3000+MIN(Config!$B$5-D214,60),IF(I214="Hoje",2500,IF(D214-Config!$B$5&lt;=Config!$B$6,2000-(D214-Config!$B$5),IF(D214-Config!$B$5&lt;=Config!$B$7,1000-(D214-Config!$B$5),500-MIN(D214-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -7756,7 +8387,7 @@
       </c>
       <c r="J215" s="35">
         <f>IF(OR(I215="",I215="Feito",I215="Sem data"),0,IF(I215="Atrasado",3000+MIN(Config!$B$5-D215,60),IF(I215="Hoje",2500,IF(D215-Config!$B$5&lt;=Config!$B$6,2000-(D215-Config!$B$5),IF(D215-Config!$B$5&lt;=Config!$B$7,1000-(D215-Config!$B$5),500-MIN(D215-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -7777,7 +8408,7 @@
       </c>
       <c r="J216" s="35">
         <f>IF(OR(I216="",I216="Feito",I216="Sem data"),0,IF(I216="Atrasado",3000+MIN(Config!$B$5-D216,60),IF(I216="Hoje",2500,IF(D216-Config!$B$5&lt;=Config!$B$6,2000-(D216-Config!$B$5),IF(D216-Config!$B$5&lt;=Config!$B$7,1000-(D216-Config!$B$5),500-MIN(D216-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -7798,7 +8429,7 @@
       </c>
       <c r="J217" s="35">
         <f>IF(OR(I217="",I217="Feito",I217="Sem data"),0,IF(I217="Atrasado",3000+MIN(Config!$B$5-D217,60),IF(I217="Hoje",2500,IF(D217-Config!$B$5&lt;=Config!$B$6,2000-(D217-Config!$B$5),IF(D217-Config!$B$5&lt;=Config!$B$7,1000-(D217-Config!$B$5),500-MIN(D217-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -7819,7 +8450,7 @@
       </c>
       <c r="J218" s="35">
         <f>IF(OR(I218="",I218="Feito",I218="Sem data"),0,IF(I218="Atrasado",3000+MIN(Config!$B$5-D218,60),IF(I218="Hoje",2500,IF(D218-Config!$B$5&lt;=Config!$B$6,2000-(D218-Config!$B$5),IF(D218-Config!$B$5&lt;=Config!$B$7,1000-(D218-Config!$B$5),500-MIN(D218-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -7840,7 +8471,7 @@
       </c>
       <c r="J219" s="35">
         <f>IF(OR(I219="",I219="Feito",I219="Sem data"),0,IF(I219="Atrasado",3000+MIN(Config!$B$5-D219,60),IF(I219="Hoje",2500,IF(D219-Config!$B$5&lt;=Config!$B$6,2000-(D219-Config!$B$5),IF(D219-Config!$B$5&lt;=Config!$B$7,1000-(D219-Config!$B$5),500-MIN(D219-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="220">
@@ -7861,7 +8492,7 @@
       </c>
       <c r="J220" s="35">
         <f>IF(OR(I220="",I220="Feito",I220="Sem data"),0,IF(I220="Atrasado",3000+MIN(Config!$B$5-D220,60),IF(I220="Hoje",2500,IF(D220-Config!$B$5&lt;=Config!$B$6,2000-(D220-Config!$B$5),IF(D220-Config!$B$5&lt;=Config!$B$7,1000-(D220-Config!$B$5),500-MIN(D220-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -7882,7 +8513,7 @@
       </c>
       <c r="J221" s="35">
         <f>IF(OR(I221="",I221="Feito",I221="Sem data"),0,IF(I221="Atrasado",3000+MIN(Config!$B$5-D221,60),IF(I221="Hoje",2500,IF(D221-Config!$B$5&lt;=Config!$B$6,2000-(D221-Config!$B$5),IF(D221-Config!$B$5&lt;=Config!$B$7,1000-(D221-Config!$B$5),500-MIN(D221-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -7903,7 +8534,7 @@
       </c>
       <c r="J222" s="35">
         <f>IF(OR(I222="",I222="Feito",I222="Sem data"),0,IF(I222="Atrasado",3000+MIN(Config!$B$5-D222,60),IF(I222="Hoje",2500,IF(D222-Config!$B$5&lt;=Config!$B$6,2000-(D222-Config!$B$5),IF(D222-Config!$B$5&lt;=Config!$B$7,1000-(D222-Config!$B$5),500-MIN(D222-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
@@ -7924,7 +8555,7 @@
       </c>
       <c r="J223" s="35">
         <f>IF(OR(I223="",I223="Feito",I223="Sem data"),0,IF(I223="Atrasado",3000+MIN(Config!$B$5-D223,60),IF(I223="Hoje",2500,IF(D223-Config!$B$5&lt;=Config!$B$6,2000-(D223-Config!$B$5),IF(D223-Config!$B$5&lt;=Config!$B$7,1000-(D223-Config!$B$5),500-MIN(D223-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -7945,7 +8576,7 @@
       </c>
       <c r="J224" s="35">
         <f>IF(OR(I224="",I224="Feito",I224="Sem data"),0,IF(I224="Atrasado",3000+MIN(Config!$B$5-D224,60),IF(I224="Hoje",2500,IF(D224-Config!$B$5&lt;=Config!$B$6,2000-(D224-Config!$B$5),IF(D224-Config!$B$5&lt;=Config!$B$7,1000-(D224-Config!$B$5),500-MIN(D224-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="225">
@@ -7966,7 +8597,7 @@
       </c>
       <c r="J225" s="35">
         <f>IF(OR(I225="",I225="Feito",I225="Sem data"),0,IF(I225="Atrasado",3000+MIN(Config!$B$5-D225,60),IF(I225="Hoje",2500,IF(D225-Config!$B$5&lt;=Config!$B$6,2000-(D225-Config!$B$5),IF(D225-Config!$B$5&lt;=Config!$B$7,1000-(D225-Config!$B$5),500-MIN(D225-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
@@ -7987,7 +8618,7 @@
       </c>
       <c r="J226" s="35">
         <f>IF(OR(I226="",I226="Feito",I226="Sem data"),0,IF(I226="Atrasado",3000+MIN(Config!$B$5-D226,60),IF(I226="Hoje",2500,IF(D226-Config!$B$5&lt;=Config!$B$6,2000-(D226-Config!$B$5),IF(D226-Config!$B$5&lt;=Config!$B$7,1000-(D226-Config!$B$5),500-MIN(D226-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="227">
@@ -8008,7 +8639,7 @@
       </c>
       <c r="J227" s="35">
         <f>IF(OR(I227="",I227="Feito",I227="Sem data"),0,IF(I227="Atrasado",3000+MIN(Config!$B$5-D227,60),IF(I227="Hoje",2500,IF(D227-Config!$B$5&lt;=Config!$B$6,2000-(D227-Config!$B$5),IF(D227-Config!$B$5&lt;=Config!$B$7,1000-(D227-Config!$B$5),500-MIN(D227-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
@@ -8029,7 +8660,7 @@
       </c>
       <c r="J228" s="35">
         <f>IF(OR(I228="",I228="Feito",I228="Sem data"),0,IF(I228="Atrasado",3000+MIN(Config!$B$5-D228,60),IF(I228="Hoje",2500,IF(D228-Config!$B$5&lt;=Config!$B$6,2000-(D228-Config!$B$5),IF(D228-Config!$B$5&lt;=Config!$B$7,1000-(D228-Config!$B$5),500-MIN(D228-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="229">
@@ -8050,7 +8681,7 @@
       </c>
       <c r="J229" s="35">
         <f>IF(OR(I229="",I229="Feito",I229="Sem data"),0,IF(I229="Atrasado",3000+MIN(Config!$B$5-D229,60),IF(I229="Hoje",2500,IF(D229-Config!$B$5&lt;=Config!$B$6,2000-(D229-Config!$B$5),IF(D229-Config!$B$5&lt;=Config!$B$7,1000-(D229-Config!$B$5),500-MIN(D229-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
@@ -8071,7 +8702,7 @@
       </c>
       <c r="J230" s="35">
         <f>IF(OR(I230="",I230="Feito",I230="Sem data"),0,IF(I230="Atrasado",3000+MIN(Config!$B$5-D230,60),IF(I230="Hoje",2500,IF(D230-Config!$B$5&lt;=Config!$B$6,2000-(D230-Config!$B$5),IF(D230-Config!$B$5&lt;=Config!$B$7,1000-(D230-Config!$B$5),500-MIN(D230-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="231">
@@ -8092,7 +8723,7 @@
       </c>
       <c r="J231" s="35">
         <f>IF(OR(I231="",I231="Feito",I231="Sem data"),0,IF(I231="Atrasado",3000+MIN(Config!$B$5-D231,60),IF(I231="Hoje",2500,IF(D231-Config!$B$5&lt;=Config!$B$6,2000-(D231-Config!$B$5),IF(D231-Config!$B$5&lt;=Config!$B$7,1000-(D231-Config!$B$5),500-MIN(D231-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="232">
@@ -8113,7 +8744,7 @@
       </c>
       <c r="J232" s="35">
         <f>IF(OR(I232="",I232="Feito",I232="Sem data"),0,IF(I232="Atrasado",3000+MIN(Config!$B$5-D232,60),IF(I232="Hoje",2500,IF(D232-Config!$B$5&lt;=Config!$B$6,2000-(D232-Config!$B$5),IF(D232-Config!$B$5&lt;=Config!$B$7,1000-(D232-Config!$B$5),500-MIN(D232-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
@@ -8134,7 +8765,7 @@
       </c>
       <c r="J233" s="35">
         <f>IF(OR(I233="",I233="Feito",I233="Sem data"),0,IF(I233="Atrasado",3000+MIN(Config!$B$5-D233,60),IF(I233="Hoje",2500,IF(D233-Config!$B$5&lt;=Config!$B$6,2000-(D233-Config!$B$5),IF(D233-Config!$B$5&lt;=Config!$B$7,1000-(D233-Config!$B$5),500-MIN(D233-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -8155,7 +8786,7 @@
       </c>
       <c r="J234" s="35">
         <f>IF(OR(I234="",I234="Feito",I234="Sem data"),0,IF(I234="Atrasado",3000+MIN(Config!$B$5-D234,60),IF(I234="Hoje",2500,IF(D234-Config!$B$5&lt;=Config!$B$6,2000-(D234-Config!$B$5),IF(D234-Config!$B$5&lt;=Config!$B$7,1000-(D234-Config!$B$5),500-MIN(D234-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="235">
@@ -8176,7 +8807,7 @@
       </c>
       <c r="J235" s="35">
         <f>IF(OR(I235="",I235="Feito",I235="Sem data"),0,IF(I235="Atrasado",3000+MIN(Config!$B$5-D235,60),IF(I235="Hoje",2500,IF(D235-Config!$B$5&lt;=Config!$B$6,2000-(D235-Config!$B$5),IF(D235-Config!$B$5&lt;=Config!$B$7,1000-(D235-Config!$B$5),500-MIN(D235-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
@@ -8197,7 +8828,7 @@
       </c>
       <c r="J236" s="35">
         <f>IF(OR(I236="",I236="Feito",I236="Sem data"),0,IF(I236="Atrasado",3000+MIN(Config!$B$5-D236,60),IF(I236="Hoje",2500,IF(D236-Config!$B$5&lt;=Config!$B$6,2000-(D236-Config!$B$5),IF(D236-Config!$B$5&lt;=Config!$B$7,1000-(D236-Config!$B$5),500-MIN(D236-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
@@ -8218,7 +8849,7 @@
       </c>
       <c r="J237" s="35">
         <f>IF(OR(I237="",I237="Feito",I237="Sem data"),0,IF(I237="Atrasado",3000+MIN(Config!$B$5-D237,60),IF(I237="Hoje",2500,IF(D237-Config!$B$5&lt;=Config!$B$6,2000-(D237-Config!$B$5),IF(D237-Config!$B$5&lt;=Config!$B$7,1000-(D237-Config!$B$5),500-MIN(D237-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
@@ -8239,7 +8870,7 @@
       </c>
       <c r="J238" s="35">
         <f>IF(OR(I238="",I238="Feito",I238="Sem data"),0,IF(I238="Atrasado",3000+MIN(Config!$B$5-D238,60),IF(I238="Hoje",2500,IF(D238-Config!$B$5&lt;=Config!$B$6,2000-(D238-Config!$B$5),IF(D238-Config!$B$5&lt;=Config!$B$7,1000-(D238-Config!$B$5),500-MIN(D238-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
@@ -8260,7 +8891,7 @@
       </c>
       <c r="J239" s="35">
         <f>IF(OR(I239="",I239="Feito",I239="Sem data"),0,IF(I239="Atrasado",3000+MIN(Config!$B$5-D239,60),IF(I239="Hoje",2500,IF(D239-Config!$B$5&lt;=Config!$B$6,2000-(D239-Config!$B$5),IF(D239-Config!$B$5&lt;=Config!$B$7,1000-(D239-Config!$B$5),500-MIN(D239-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -8281,7 +8912,7 @@
       </c>
       <c r="J240" s="35">
         <f>IF(OR(I240="",I240="Feito",I240="Sem data"),0,IF(I240="Atrasado",3000+MIN(Config!$B$5-D240,60),IF(I240="Hoje",2500,IF(D240-Config!$B$5&lt;=Config!$B$6,2000-(D240-Config!$B$5),IF(D240-Config!$B$5&lt;=Config!$B$7,1000-(D240-Config!$B$5),500-MIN(D240-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
@@ -8302,7 +8933,7 @@
       </c>
       <c r="J241" s="35">
         <f>IF(OR(I241="",I241="Feito",I241="Sem data"),0,IF(I241="Atrasado",3000+MIN(Config!$B$5-D241,60),IF(I241="Hoje",2500,IF(D241-Config!$B$5&lt;=Config!$B$6,2000-(D241-Config!$B$5),IF(D241-Config!$B$5&lt;=Config!$B$7,1000-(D241-Config!$B$5),500-MIN(D241-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
@@ -8323,7 +8954,7 @@
       </c>
       <c r="J242" s="35">
         <f>IF(OR(I242="",I242="Feito",I242="Sem data"),0,IF(I242="Atrasado",3000+MIN(Config!$B$5-D242,60),IF(I242="Hoje",2500,IF(D242-Config!$B$5&lt;=Config!$B$6,2000-(D242-Config!$B$5),IF(D242-Config!$B$5&lt;=Config!$B$7,1000-(D242-Config!$B$5),500-MIN(D242-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -8344,7 +8975,7 @@
       </c>
       <c r="J243" s="35">
         <f>IF(OR(I243="",I243="Feito",I243="Sem data"),0,IF(I243="Atrasado",3000+MIN(Config!$B$5-D243,60),IF(I243="Hoje",2500,IF(D243-Config!$B$5&lt;=Config!$B$6,2000-(D243-Config!$B$5),IF(D243-Config!$B$5&lt;=Config!$B$7,1000-(D243-Config!$B$5),500-MIN(D243-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
@@ -8365,7 +8996,7 @@
       </c>
       <c r="J244" s="35">
         <f>IF(OR(I244="",I244="Feito",I244="Sem data"),0,IF(I244="Atrasado",3000+MIN(Config!$B$5-D244,60),IF(I244="Hoje",2500,IF(D244-Config!$B$5&lt;=Config!$B$6,2000-(D244-Config!$B$5),IF(D244-Config!$B$5&lt;=Config!$B$7,1000-(D244-Config!$B$5),500-MIN(D244-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
@@ -8386,7 +9017,7 @@
       </c>
       <c r="J245" s="35">
         <f>IF(OR(I245="",I245="Feito",I245="Sem data"),0,IF(I245="Atrasado",3000+MIN(Config!$B$5-D245,60),IF(I245="Hoje",2500,IF(D245-Config!$B$5&lt;=Config!$B$6,2000-(D245-Config!$B$5),IF(D245-Config!$B$5&lt;=Config!$B$7,1000-(D245-Config!$B$5),500-MIN(D245-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
@@ -8407,7 +9038,7 @@
       </c>
       <c r="J246" s="35">
         <f>IF(OR(I246="",I246="Feito",I246="Sem data"),0,IF(I246="Atrasado",3000+MIN(Config!$B$5-D246,60),IF(I246="Hoje",2500,IF(D246-Config!$B$5&lt;=Config!$B$6,2000-(D246-Config!$B$5),IF(D246-Config!$B$5&lt;=Config!$B$7,1000-(D246-Config!$B$5),500-MIN(D246-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -8428,7 +9059,7 @@
       </c>
       <c r="J247" s="35">
         <f>IF(OR(I247="",I247="Feito",I247="Sem data"),0,IF(I247="Atrasado",3000+MIN(Config!$B$5-D247,60),IF(I247="Hoje",2500,IF(D247-Config!$B$5&lt;=Config!$B$6,2000-(D247-Config!$B$5),IF(D247-Config!$B$5&lt;=Config!$B$7,1000-(D247-Config!$B$5),500-MIN(D247-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -8449,7 +9080,7 @@
       </c>
       <c r="J248" s="35">
         <f>IF(OR(I248="",I248="Feito",I248="Sem data"),0,IF(I248="Atrasado",3000+MIN(Config!$B$5-D248,60),IF(I248="Hoje",2500,IF(D248-Config!$B$5&lt;=Config!$B$6,2000-(D248-Config!$B$5),IF(D248-Config!$B$5&lt;=Config!$B$7,1000-(D248-Config!$B$5),500-MIN(D248-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -8470,7 +9101,7 @@
       </c>
       <c r="J249" s="35">
         <f>IF(OR(I249="",I249="Feito",I249="Sem data"),0,IF(I249="Atrasado",3000+MIN(Config!$B$5-D249,60),IF(I249="Hoje",2500,IF(D249-Config!$B$5&lt;=Config!$B$6,2000-(D249-Config!$B$5),IF(D249-Config!$B$5&lt;=Config!$B$7,1000-(D249-Config!$B$5),500-MIN(D249-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
@@ -8491,7 +9122,7 @@
       </c>
       <c r="J250" s="35">
         <f>IF(OR(I250="",I250="Feito",I250="Sem data"),0,IF(I250="Atrasado",3000+MIN(Config!$B$5-D250,60),IF(I250="Hoje",2500,IF(D250-Config!$B$5&lt;=Config!$B$6,2000-(D250-Config!$B$5),IF(D250-Config!$B$5&lt;=Config!$B$7,1000-(D250-Config!$B$5),500-MIN(D250-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
@@ -8512,7 +9143,7 @@
       </c>
       <c r="J251" s="35">
         <f>IF(OR(I251="",I251="Feito",I251="Sem data"),0,IF(I251="Atrasado",3000+MIN(Config!$B$5-D251,60),IF(I251="Hoje",2500,IF(D251-Config!$B$5&lt;=Config!$B$6,2000-(D251-Config!$B$5),IF(D251-Config!$B$5&lt;=Config!$B$7,1000-(D251-Config!$B$5),500-MIN(D251-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
@@ -8533,7 +9164,7 @@
       </c>
       <c r="J252" s="35">
         <f>IF(OR(I252="",I252="Feito",I252="Sem data"),0,IF(I252="Atrasado",3000+MIN(Config!$B$5-D252,60),IF(I252="Hoje",2500,IF(D252-Config!$B$5&lt;=Config!$B$6,2000-(D252-Config!$B$5),IF(D252-Config!$B$5&lt;=Config!$B$7,1000-(D252-Config!$B$5),500-MIN(D252-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
@@ -8554,7 +9185,7 @@
       </c>
       <c r="J253" s="35">
         <f>IF(OR(I253="",I253="Feito",I253="Sem data"),0,IF(I253="Atrasado",3000+MIN(Config!$B$5-D253,60),IF(I253="Hoje",2500,IF(D253-Config!$B$5&lt;=Config!$B$6,2000-(D253-Config!$B$5),IF(D253-Config!$B$5&lt;=Config!$B$7,1000-(D253-Config!$B$5),500-MIN(D253-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
@@ -8575,7 +9206,7 @@
       </c>
       <c r="J254" s="35">
         <f>IF(OR(I254="",I254="Feito",I254="Sem data"),0,IF(I254="Atrasado",3000+MIN(Config!$B$5-D254,60),IF(I254="Hoje",2500,IF(D254-Config!$B$5&lt;=Config!$B$6,2000-(D254-Config!$B$5),IF(D254-Config!$B$5&lt;=Config!$B$7,1000-(D254-Config!$B$5),500-MIN(D254-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
@@ -8596,7 +9227,7 @@
       </c>
       <c r="J255" s="35">
         <f>IF(OR(I255="",I255="Feito",I255="Sem data"),0,IF(I255="Atrasado",3000+MIN(Config!$B$5-D255,60),IF(I255="Hoje",2500,IF(D255-Config!$B$5&lt;=Config!$B$6,2000-(D255-Config!$B$5),IF(D255-Config!$B$5&lt;=Config!$B$7,1000-(D255-Config!$B$5),500-MIN(D255-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="256">
@@ -8617,7 +9248,7 @@
       </c>
       <c r="J256" s="35">
         <f>IF(OR(I256="",I256="Feito",I256="Sem data"),0,IF(I256="Atrasado",3000+MIN(Config!$B$5-D256,60),IF(I256="Hoje",2500,IF(D256-Config!$B$5&lt;=Config!$B$6,2000-(D256-Config!$B$5),IF(D256-Config!$B$5&lt;=Config!$B$7,1000-(D256-Config!$B$5),500-MIN(D256-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
@@ -8638,7 +9269,7 @@
       </c>
       <c r="J257" s="35">
         <f>IF(OR(I257="",I257="Feito",I257="Sem data"),0,IF(I257="Atrasado",3000+MIN(Config!$B$5-D257,60),IF(I257="Hoje",2500,IF(D257-Config!$B$5&lt;=Config!$B$6,2000-(D257-Config!$B$5),IF(D257-Config!$B$5&lt;=Config!$B$7,1000-(D257-Config!$B$5),500-MIN(D257-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
@@ -8659,7 +9290,7 @@
       </c>
       <c r="J258" s="35">
         <f>IF(OR(I258="",I258="Feito",I258="Sem data"),0,IF(I258="Atrasado",3000+MIN(Config!$B$5-D258,60),IF(I258="Hoje",2500,IF(D258-Config!$B$5&lt;=Config!$B$6,2000-(D258-Config!$B$5),IF(D258-Config!$B$5&lt;=Config!$B$7,1000-(D258-Config!$B$5),500-MIN(D258-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
@@ -8680,7 +9311,7 @@
       </c>
       <c r="J259" s="35">
         <f>IF(OR(I259="",I259="Feito",I259="Sem data"),0,IF(I259="Atrasado",3000+MIN(Config!$B$5-D259,60),IF(I259="Hoje",2500,IF(D259-Config!$B$5&lt;=Config!$B$6,2000-(D259-Config!$B$5),IF(D259-Config!$B$5&lt;=Config!$B$7,1000-(D259-Config!$B$5),500-MIN(D259-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
@@ -8701,7 +9332,7 @@
       </c>
       <c r="J260" s="35">
         <f>IF(OR(I260="",I260="Feito",I260="Sem data"),0,IF(I260="Atrasado",3000+MIN(Config!$B$5-D260,60),IF(I260="Hoje",2500,IF(D260-Config!$B$5&lt;=Config!$B$6,2000-(D260-Config!$B$5),IF(D260-Config!$B$5&lt;=Config!$B$7,1000-(D260-Config!$B$5),500-MIN(D260-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="261">
@@ -8722,7 +9353,7 @@
       </c>
       <c r="J261" s="35">
         <f>IF(OR(I261="",I261="Feito",I261="Sem data"),0,IF(I261="Atrasado",3000+MIN(Config!$B$5-D261,60),IF(I261="Hoje",2500,IF(D261-Config!$B$5&lt;=Config!$B$6,2000-(D261-Config!$B$5),IF(D261-Config!$B$5&lt;=Config!$B$7,1000-(D261-Config!$B$5),500-MIN(D261-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="262">
@@ -8743,7 +9374,7 @@
       </c>
       <c r="J262" s="35">
         <f>IF(OR(I262="",I262="Feito",I262="Sem data"),0,IF(I262="Atrasado",3000+MIN(Config!$B$5-D262,60),IF(I262="Hoje",2500,IF(D262-Config!$B$5&lt;=Config!$B$6,2000-(D262-Config!$B$5),IF(D262-Config!$B$5&lt;=Config!$B$7,1000-(D262-Config!$B$5),500-MIN(D262-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="263">
@@ -8764,7 +9395,7 @@
       </c>
       <c r="J263" s="35">
         <f>IF(OR(I263="",I263="Feito",I263="Sem data"),0,IF(I263="Atrasado",3000+MIN(Config!$B$5-D263,60),IF(I263="Hoje",2500,IF(D263-Config!$B$5&lt;=Config!$B$6,2000-(D263-Config!$B$5),IF(D263-Config!$B$5&lt;=Config!$B$7,1000-(D263-Config!$B$5),500-MIN(D263-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="264">
@@ -8785,7 +9416,7 @@
       </c>
       <c r="J264" s="35">
         <f>IF(OR(I264="",I264="Feito",I264="Sem data"),0,IF(I264="Atrasado",3000+MIN(Config!$B$5-D264,60),IF(I264="Hoje",2500,IF(D264-Config!$B$5&lt;=Config!$B$6,2000-(D264-Config!$B$5),IF(D264-Config!$B$5&lt;=Config!$B$7,1000-(D264-Config!$B$5),500-MIN(D264-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="265">
@@ -8806,7 +9437,7 @@
       </c>
       <c r="J265" s="35">
         <f>IF(OR(I265="",I265="Feito",I265="Sem data"),0,IF(I265="Atrasado",3000+MIN(Config!$B$5-D265,60),IF(I265="Hoje",2500,IF(D265-Config!$B$5&lt;=Config!$B$6,2000-(D265-Config!$B$5),IF(D265-Config!$B$5&lt;=Config!$B$7,1000-(D265-Config!$B$5),500-MIN(D265-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="266">
@@ -8827,7 +9458,7 @@
       </c>
       <c r="J266" s="35">
         <f>IF(OR(I266="",I266="Feito",I266="Sem data"),0,IF(I266="Atrasado",3000+MIN(Config!$B$5-D266,60),IF(I266="Hoje",2500,IF(D266-Config!$B$5&lt;=Config!$B$6,2000-(D266-Config!$B$5),IF(D266-Config!$B$5&lt;=Config!$B$7,1000-(D266-Config!$B$5),500-MIN(D266-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="267">
@@ -8848,7 +9479,7 @@
       </c>
       <c r="J267" s="35">
         <f>IF(OR(I267="",I267="Feito",I267="Sem data"),0,IF(I267="Atrasado",3000+MIN(Config!$B$5-D267,60),IF(I267="Hoje",2500,IF(D267-Config!$B$5&lt;=Config!$B$6,2000-(D267-Config!$B$5),IF(D267-Config!$B$5&lt;=Config!$B$7,1000-(D267-Config!$B$5),500-MIN(D267-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="268">
@@ -8869,7 +9500,7 @@
       </c>
       <c r="J268" s="35">
         <f>IF(OR(I268="",I268="Feito",I268="Sem data"),0,IF(I268="Atrasado",3000+MIN(Config!$B$5-D268,60),IF(I268="Hoje",2500,IF(D268-Config!$B$5&lt;=Config!$B$6,2000-(D268-Config!$B$5),IF(D268-Config!$B$5&lt;=Config!$B$7,1000-(D268-Config!$B$5),500-MIN(D268-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="269">
@@ -8890,7 +9521,7 @@
       </c>
       <c r="J269" s="35">
         <f>IF(OR(I269="",I269="Feito",I269="Sem data"),0,IF(I269="Atrasado",3000+MIN(Config!$B$5-D269,60),IF(I269="Hoje",2500,IF(D269-Config!$B$5&lt;=Config!$B$6,2000-(D269-Config!$B$5),IF(D269-Config!$B$5&lt;=Config!$B$7,1000-(D269-Config!$B$5),500-MIN(D269-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="270">
@@ -8911,7 +9542,7 @@
       </c>
       <c r="J270" s="35">
         <f>IF(OR(I270="",I270="Feito",I270="Sem data"),0,IF(I270="Atrasado",3000+MIN(Config!$B$5-D270,60),IF(I270="Hoje",2500,IF(D270-Config!$B$5&lt;=Config!$B$6,2000-(D270-Config!$B$5),IF(D270-Config!$B$5&lt;=Config!$B$7,1000-(D270-Config!$B$5),500-MIN(D270-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="271">
@@ -8932,7 +9563,7 @@
       </c>
       <c r="J271" s="35">
         <f>IF(OR(I271="",I271="Feito",I271="Sem data"),0,IF(I271="Atrasado",3000+MIN(Config!$B$5-D271,60),IF(I271="Hoje",2500,IF(D271-Config!$B$5&lt;=Config!$B$6,2000-(D271-Config!$B$5),IF(D271-Config!$B$5&lt;=Config!$B$7,1000-(D271-Config!$B$5),500-MIN(D271-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="272">
@@ -8953,7 +9584,7 @@
       </c>
       <c r="J272" s="35">
         <f>IF(OR(I272="",I272="Feito",I272="Sem data"),0,IF(I272="Atrasado",3000+MIN(Config!$B$5-D272,60),IF(I272="Hoje",2500,IF(D272-Config!$B$5&lt;=Config!$B$6,2000-(D272-Config!$B$5),IF(D272-Config!$B$5&lt;=Config!$B$7,1000-(D272-Config!$B$5),500-MIN(D272-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -8974,7 +9605,7 @@
       </c>
       <c r="J273" s="35">
         <f>IF(OR(I273="",I273="Feito",I273="Sem data"),0,IF(I273="Atrasado",3000+MIN(Config!$B$5-D273,60),IF(I273="Hoje",2500,IF(D273-Config!$B$5&lt;=Config!$B$6,2000-(D273-Config!$B$5),IF(D273-Config!$B$5&lt;=Config!$B$7,1000-(D273-Config!$B$5),500-MIN(D273-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
@@ -8995,7 +9626,7 @@
       </c>
       <c r="J274" s="35">
         <f>IF(OR(I274="",I274="Feito",I274="Sem data"),0,IF(I274="Atrasado",3000+MIN(Config!$B$5-D274,60),IF(I274="Hoje",2500,IF(D274-Config!$B$5&lt;=Config!$B$6,2000-(D274-Config!$B$5),IF(D274-Config!$B$5&lt;=Config!$B$7,1000-(D274-Config!$B$5),500-MIN(D274-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -9016,7 +9647,7 @@
       </c>
       <c r="J275" s="35">
         <f>IF(OR(I275="",I275="Feito",I275="Sem data"),0,IF(I275="Atrasado",3000+MIN(Config!$B$5-D275,60),IF(I275="Hoje",2500,IF(D275-Config!$B$5&lt;=Config!$B$6,2000-(D275-Config!$B$5),IF(D275-Config!$B$5&lt;=Config!$B$7,1000-(D275-Config!$B$5),500-MIN(D275-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="276">
@@ -9037,7 +9668,7 @@
       </c>
       <c r="J276" s="35">
         <f>IF(OR(I276="",I276="Feito",I276="Sem data"),0,IF(I276="Atrasado",3000+MIN(Config!$B$5-D276,60),IF(I276="Hoje",2500,IF(D276-Config!$B$5&lt;=Config!$B$6,2000-(D276-Config!$B$5),IF(D276-Config!$B$5&lt;=Config!$B$7,1000-(D276-Config!$B$5),500-MIN(D276-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="277">
@@ -9058,7 +9689,7 @@
       </c>
       <c r="J277" s="35">
         <f>IF(OR(I277="",I277="Feito",I277="Sem data"),0,IF(I277="Atrasado",3000+MIN(Config!$B$5-D277,60),IF(I277="Hoje",2500,IF(D277-Config!$B$5&lt;=Config!$B$6,2000-(D277-Config!$B$5),IF(D277-Config!$B$5&lt;=Config!$B$7,1000-(D277-Config!$B$5),500-MIN(D277-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="278">
@@ -9079,7 +9710,7 @@
       </c>
       <c r="J278" s="35">
         <f>IF(OR(I278="",I278="Feito",I278="Sem data"),0,IF(I278="Atrasado",3000+MIN(Config!$B$5-D278,60),IF(I278="Hoje",2500,IF(D278-Config!$B$5&lt;=Config!$B$6,2000-(D278-Config!$B$5),IF(D278-Config!$B$5&lt;=Config!$B$7,1000-(D278-Config!$B$5),500-MIN(D278-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="279">
@@ -9100,7 +9731,7 @@
       </c>
       <c r="J279" s="35">
         <f>IF(OR(I279="",I279="Feito",I279="Sem data"),0,IF(I279="Atrasado",3000+MIN(Config!$B$5-D279,60),IF(I279="Hoje",2500,IF(D279-Config!$B$5&lt;=Config!$B$6,2000-(D279-Config!$B$5),IF(D279-Config!$B$5&lt;=Config!$B$7,1000-(D279-Config!$B$5),500-MIN(D279-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="280">
@@ -9121,7 +9752,7 @@
       </c>
       <c r="J280" s="35">
         <f>IF(OR(I280="",I280="Feito",I280="Sem data"),0,IF(I280="Atrasado",3000+MIN(Config!$B$5-D280,60),IF(I280="Hoje",2500,IF(D280-Config!$B$5&lt;=Config!$B$6,2000-(D280-Config!$B$5),IF(D280-Config!$B$5&lt;=Config!$B$7,1000-(D280-Config!$B$5),500-MIN(D280-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="281">
@@ -9142,7 +9773,7 @@
       </c>
       <c r="J281" s="35">
         <f>IF(OR(I281="",I281="Feito",I281="Sem data"),0,IF(I281="Atrasado",3000+MIN(Config!$B$5-D281,60),IF(I281="Hoje",2500,IF(D281-Config!$B$5&lt;=Config!$B$6,2000-(D281-Config!$B$5),IF(D281-Config!$B$5&lt;=Config!$B$7,1000-(D281-Config!$B$5),500-MIN(D281-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="282">
@@ -9163,7 +9794,7 @@
       </c>
       <c r="J282" s="35">
         <f>IF(OR(I282="",I282="Feito",I282="Sem data"),0,IF(I282="Atrasado",3000+MIN(Config!$B$5-D282,60),IF(I282="Hoje",2500,IF(D282-Config!$B$5&lt;=Config!$B$6,2000-(D282-Config!$B$5),IF(D282-Config!$B$5&lt;=Config!$B$7,1000-(D282-Config!$B$5),500-MIN(D282-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="283">
@@ -9184,7 +9815,7 @@
       </c>
       <c r="J283" s="35">
         <f>IF(OR(I283="",I283="Feito",I283="Sem data"),0,IF(I283="Atrasado",3000+MIN(Config!$B$5-D283,60),IF(I283="Hoje",2500,IF(D283-Config!$B$5&lt;=Config!$B$6,2000-(D283-Config!$B$5),IF(D283-Config!$B$5&lt;=Config!$B$7,1000-(D283-Config!$B$5),500-MIN(D283-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="284">
@@ -9205,7 +9836,7 @@
       </c>
       <c r="J284" s="35">
         <f>IF(OR(I284="",I284="Feito",I284="Sem data"),0,IF(I284="Atrasado",3000+MIN(Config!$B$5-D284,60),IF(I284="Hoje",2500,IF(D284-Config!$B$5&lt;=Config!$B$6,2000-(D284-Config!$B$5),IF(D284-Config!$B$5&lt;=Config!$B$7,1000-(D284-Config!$B$5),500-MIN(D284-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="285">
@@ -9226,7 +9857,7 @@
       </c>
       <c r="J285" s="35">
         <f>IF(OR(I285="",I285="Feito",I285="Sem data"),0,IF(I285="Atrasado",3000+MIN(Config!$B$5-D285,60),IF(I285="Hoje",2500,IF(D285-Config!$B$5&lt;=Config!$B$6,2000-(D285-Config!$B$5),IF(D285-Config!$B$5&lt;=Config!$B$7,1000-(D285-Config!$B$5),500-MIN(D285-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="286">
@@ -9247,7 +9878,7 @@
       </c>
       <c r="J286" s="35">
         <f>IF(OR(I286="",I286="Feito",I286="Sem data"),0,IF(I286="Atrasado",3000+MIN(Config!$B$5-D286,60),IF(I286="Hoje",2500,IF(D286-Config!$B$5&lt;=Config!$B$6,2000-(D286-Config!$B$5),IF(D286-Config!$B$5&lt;=Config!$B$7,1000-(D286-Config!$B$5),500-MIN(D286-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="287">
@@ -9268,7 +9899,7 @@
       </c>
       <c r="J287" s="35">
         <f>IF(OR(I287="",I287="Feito",I287="Sem data"),0,IF(I287="Atrasado",3000+MIN(Config!$B$5-D287,60),IF(I287="Hoje",2500,IF(D287-Config!$B$5&lt;=Config!$B$6,2000-(D287-Config!$B$5),IF(D287-Config!$B$5&lt;=Config!$B$7,1000-(D287-Config!$B$5),500-MIN(D287-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="288">
@@ -9289,7 +9920,7 @@
       </c>
       <c r="J288" s="35">
         <f>IF(OR(I288="",I288="Feito",I288="Sem data"),0,IF(I288="Atrasado",3000+MIN(Config!$B$5-D288,60),IF(I288="Hoje",2500,IF(D288-Config!$B$5&lt;=Config!$B$6,2000-(D288-Config!$B$5),IF(D288-Config!$B$5&lt;=Config!$B$7,1000-(D288-Config!$B$5),500-MIN(D288-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="289">
@@ -9310,7 +9941,7 @@
       </c>
       <c r="J289" s="35">
         <f>IF(OR(I289="",I289="Feito",I289="Sem data"),0,IF(I289="Atrasado",3000+MIN(Config!$B$5-D289,60),IF(I289="Hoje",2500,IF(D289-Config!$B$5&lt;=Config!$B$6,2000-(D289-Config!$B$5),IF(D289-Config!$B$5&lt;=Config!$B$7,1000-(D289-Config!$B$5),500-MIN(D289-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="290">
@@ -9331,7 +9962,7 @@
       </c>
       <c r="J290" s="35">
         <f>IF(OR(I290="",I290="Feito",I290="Sem data"),0,IF(I290="Atrasado",3000+MIN(Config!$B$5-D290,60),IF(I290="Hoje",2500,IF(D290-Config!$B$5&lt;=Config!$B$6,2000-(D290-Config!$B$5),IF(D290-Config!$B$5&lt;=Config!$B$7,1000-(D290-Config!$B$5),500-MIN(D290-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="291">
@@ -9352,7 +9983,7 @@
       </c>
       <c r="J291" s="35">
         <f>IF(OR(I291="",I291="Feito",I291="Sem data"),0,IF(I291="Atrasado",3000+MIN(Config!$B$5-D291,60),IF(I291="Hoje",2500,IF(D291-Config!$B$5&lt;=Config!$B$6,2000-(D291-Config!$B$5),IF(D291-Config!$B$5&lt;=Config!$B$7,1000-(D291-Config!$B$5),500-MIN(D291-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="292">
@@ -9373,7 +10004,7 @@
       </c>
       <c r="J292" s="35">
         <f>IF(OR(I292="",I292="Feito",I292="Sem data"),0,IF(I292="Atrasado",3000+MIN(Config!$B$5-D292,60),IF(I292="Hoje",2500,IF(D292-Config!$B$5&lt;=Config!$B$6,2000-(D292-Config!$B$5),IF(D292-Config!$B$5&lt;=Config!$B$7,1000-(D292-Config!$B$5),500-MIN(D292-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="293">
@@ -9394,7 +10025,7 @@
       </c>
       <c r="J293" s="35">
         <f>IF(OR(I293="",I293="Feito",I293="Sem data"),0,IF(I293="Atrasado",3000+MIN(Config!$B$5-D293,60),IF(I293="Hoje",2500,IF(D293-Config!$B$5&lt;=Config!$B$6,2000-(D293-Config!$B$5),IF(D293-Config!$B$5&lt;=Config!$B$7,1000-(D293-Config!$B$5),500-MIN(D293-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="294">
@@ -9415,7 +10046,7 @@
       </c>
       <c r="J294" s="35">
         <f>IF(OR(I294="",I294="Feito",I294="Sem data"),0,IF(I294="Atrasado",3000+MIN(Config!$B$5-D294,60),IF(I294="Hoje",2500,IF(D294-Config!$B$5&lt;=Config!$B$6,2000-(D294-Config!$B$5),IF(D294-Config!$B$5&lt;=Config!$B$7,1000-(D294-Config!$B$5),500-MIN(D294-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="295">
@@ -9436,7 +10067,7 @@
       </c>
       <c r="J295" s="35">
         <f>IF(OR(I295="",I295="Feito",I295="Sem data"),0,IF(I295="Atrasado",3000+MIN(Config!$B$5-D295,60),IF(I295="Hoje",2500,IF(D295-Config!$B$5&lt;=Config!$B$6,2000-(D295-Config!$B$5),IF(D295-Config!$B$5&lt;=Config!$B$7,1000-(D295-Config!$B$5),500-MIN(D295-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="296">
@@ -9457,7 +10088,7 @@
       </c>
       <c r="J296" s="35">
         <f>IF(OR(I296="",I296="Feito",I296="Sem data"),0,IF(I296="Atrasado",3000+MIN(Config!$B$5-D296,60),IF(I296="Hoje",2500,IF(D296-Config!$B$5&lt;=Config!$B$6,2000-(D296-Config!$B$5),IF(D296-Config!$B$5&lt;=Config!$B$7,1000-(D296-Config!$B$5),500-MIN(D296-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
@@ -9478,7 +10109,7 @@
       </c>
       <c r="J297" s="35">
         <f>IF(OR(I297="",I297="Feito",I297="Sem data"),0,IF(I297="Atrasado",3000+MIN(Config!$B$5-D297,60),IF(I297="Hoje",2500,IF(D297-Config!$B$5&lt;=Config!$B$6,2000-(D297-Config!$B$5),IF(D297-Config!$B$5&lt;=Config!$B$7,1000-(D297-Config!$B$5),500-MIN(D297-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="298">
@@ -9499,7 +10130,7 @@
       </c>
       <c r="J298" s="35">
         <f>IF(OR(I298="",I298="Feito",I298="Sem data"),0,IF(I298="Atrasado",3000+MIN(Config!$B$5-D298,60),IF(I298="Hoje",2500,IF(D298-Config!$B$5&lt;=Config!$B$6,2000-(D298-Config!$B$5),IF(D298-Config!$B$5&lt;=Config!$B$7,1000-(D298-Config!$B$5),500-MIN(D298-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="299">
@@ -9520,7 +10151,7 @@
       </c>
       <c r="J299" s="35">
         <f>IF(OR(I299="",I299="Feito",I299="Sem data"),0,IF(I299="Atrasado",3000+MIN(Config!$B$5-D299,60),IF(I299="Hoje",2500,IF(D299-Config!$B$5&lt;=Config!$B$6,2000-(D299-Config!$B$5),IF(D299-Config!$B$5&lt;=Config!$B$7,1000-(D299-Config!$B$5),500-MIN(D299-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="300">
@@ -9541,7 +10172,7 @@
       </c>
       <c r="J300" s="35">
         <f>IF(OR(I300="",I300="Feito",I300="Sem data"),0,IF(I300="Atrasado",3000+MIN(Config!$B$5-D300,60),IF(I300="Hoje",2500,IF(D300-Config!$B$5&lt;=Config!$B$6,2000-(D300-Config!$B$5),IF(D300-Config!$B$5&lt;=Config!$B$7,1000-(D300-Config!$B$5),500-MIN(D300-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="301">
@@ -9562,7 +10193,7 @@
       </c>
       <c r="J301" s="35">
         <f>IF(OR(I301="",I301="Feito",I301="Sem data"),0,IF(I301="Atrasado",3000+MIN(Config!$B$5-D301,60),IF(I301="Hoje",2500,IF(D301-Config!$B$5&lt;=Config!$B$6,2000-(D301-Config!$B$5),IF(D301-Config!$B$5&lt;=Config!$B$7,1000-(D301-Config!$B$5),500-MIN(D301-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="302">
@@ -9583,7 +10214,7 @@
       </c>
       <c r="J302" s="35">
         <f>IF(OR(I302="",I302="Feito",I302="Sem data"),0,IF(I302="Atrasado",3000+MIN(Config!$B$5-D302,60),IF(I302="Hoje",2500,IF(D302-Config!$B$5&lt;=Config!$B$6,2000-(D302-Config!$B$5),IF(D302-Config!$B$5&lt;=Config!$B$7,1000-(D302-Config!$B$5),500-MIN(D302-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
@@ -9604,7 +10235,7 @@
       </c>
       <c r="J303" s="35">
         <f>IF(OR(I303="",I303="Feito",I303="Sem data"),0,IF(I303="Atrasado",3000+MIN(Config!$B$5-D303,60),IF(I303="Hoje",2500,IF(D303-Config!$B$5&lt;=Config!$B$6,2000-(D303-Config!$B$5),IF(D303-Config!$B$5&lt;=Config!$B$7,1000-(D303-Config!$B$5),500-MIN(D303-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="304">
@@ -9625,7 +10256,7 @@
       </c>
       <c r="J304" s="35">
         <f>IF(OR(I304="",I304="Feito",I304="Sem data"),0,IF(I304="Atrasado",3000+MIN(Config!$B$5-D304,60),IF(I304="Hoje",2500,IF(D304-Config!$B$5&lt;=Config!$B$6,2000-(D304-Config!$B$5),IF(D304-Config!$B$5&lt;=Config!$B$7,1000-(D304-Config!$B$5),500-MIN(D304-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="305">
@@ -9646,7 +10277,7 @@
       </c>
       <c r="J305" s="35">
         <f>IF(OR(I305="",I305="Feito",I305="Sem data"),0,IF(I305="Atrasado",3000+MIN(Config!$B$5-D305,60),IF(I305="Hoje",2500,IF(D305-Config!$B$5&lt;=Config!$B$6,2000-(D305-Config!$B$5),IF(D305-Config!$B$5&lt;=Config!$B$7,1000-(D305-Config!$B$5),500-MIN(D305-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="306">
@@ -9667,7 +10298,7 @@
       </c>
       <c r="J306" s="35">
         <f>IF(OR(I306="",I306="Feito",I306="Sem data"),0,IF(I306="Atrasado",3000+MIN(Config!$B$5-D306,60),IF(I306="Hoje",2500,IF(D306-Config!$B$5&lt;=Config!$B$6,2000-(D306-Config!$B$5),IF(D306-Config!$B$5&lt;=Config!$B$7,1000-(D306-Config!$B$5),500-MIN(D306-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="307">
@@ -9688,7 +10319,7 @@
       </c>
       <c r="J307" s="35">
         <f>IF(OR(I307="",I307="Feito",I307="Sem data"),0,IF(I307="Atrasado",3000+MIN(Config!$B$5-D307,60),IF(I307="Hoje",2500,IF(D307-Config!$B$5&lt;=Config!$B$6,2000-(D307-Config!$B$5),IF(D307-Config!$B$5&lt;=Config!$B$7,1000-(D307-Config!$B$5),500-MIN(D307-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="308">
@@ -9709,7 +10340,7 @@
       </c>
       <c r="J308" s="35">
         <f>IF(OR(I308="",I308="Feito",I308="Sem data"),0,IF(I308="Atrasado",3000+MIN(Config!$B$5-D308,60),IF(I308="Hoje",2500,IF(D308-Config!$B$5&lt;=Config!$B$6,2000-(D308-Config!$B$5),IF(D308-Config!$B$5&lt;=Config!$B$7,1000-(D308-Config!$B$5),500-MIN(D308-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="309">
@@ -9730,7 +10361,7 @@
       </c>
       <c r="J309" s="35">
         <f>IF(OR(I309="",I309="Feito",I309="Sem data"),0,IF(I309="Atrasado",3000+MIN(Config!$B$5-D309,60),IF(I309="Hoje",2500,IF(D309-Config!$B$5&lt;=Config!$B$6,2000-(D309-Config!$B$5),IF(D309-Config!$B$5&lt;=Config!$B$7,1000-(D309-Config!$B$5),500-MIN(D309-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="310">
@@ -9751,7 +10382,7 @@
       </c>
       <c r="J310" s="35">
         <f>IF(OR(I310="",I310="Feito",I310="Sem data"),0,IF(I310="Atrasado",3000+MIN(Config!$B$5-D310,60),IF(I310="Hoje",2500,IF(D310-Config!$B$5&lt;=Config!$B$6,2000-(D310-Config!$B$5),IF(D310-Config!$B$5&lt;=Config!$B$7,1000-(D310-Config!$B$5),500-MIN(D310-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="311">
@@ -9772,7 +10403,7 @@
       </c>
       <c r="J311" s="35">
         <f>IF(OR(I311="",I311="Feito",I311="Sem data"),0,IF(I311="Atrasado",3000+MIN(Config!$B$5-D311,60),IF(I311="Hoje",2500,IF(D311-Config!$B$5&lt;=Config!$B$6,2000-(D311-Config!$B$5),IF(D311-Config!$B$5&lt;=Config!$B$7,1000-(D311-Config!$B$5),500-MIN(D311-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="312">
@@ -9793,7 +10424,7 @@
       </c>
       <c r="J312" s="35">
         <f>IF(OR(I312="",I312="Feito",I312="Sem data"),0,IF(I312="Atrasado",3000+MIN(Config!$B$5-D312,60),IF(I312="Hoje",2500,IF(D312-Config!$B$5&lt;=Config!$B$6,2000-(D312-Config!$B$5),IF(D312-Config!$B$5&lt;=Config!$B$7,1000-(D312-Config!$B$5),500-MIN(D312-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="313">
@@ -9814,7 +10445,7 @@
       </c>
       <c r="J313" s="35">
         <f>IF(OR(I313="",I313="Feito",I313="Sem data"),0,IF(I313="Atrasado",3000+MIN(Config!$B$5-D313,60),IF(I313="Hoje",2500,IF(D313-Config!$B$5&lt;=Config!$B$6,2000-(D313-Config!$B$5),IF(D313-Config!$B$5&lt;=Config!$B$7,1000-(D313-Config!$B$5),500-MIN(D313-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="314">
@@ -9835,7 +10466,7 @@
       </c>
       <c r="J314" s="35">
         <f>IF(OR(I314="",I314="Feito",I314="Sem data"),0,IF(I314="Atrasado",3000+MIN(Config!$B$5-D314,60),IF(I314="Hoje",2500,IF(D314-Config!$B$5&lt;=Config!$B$6,2000-(D314-Config!$B$5),IF(D314-Config!$B$5&lt;=Config!$B$7,1000-(D314-Config!$B$5),500-MIN(D314-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="315">
@@ -9856,7 +10487,7 @@
       </c>
       <c r="J315" s="35">
         <f>IF(OR(I315="",I315="Feito",I315="Sem data"),0,IF(I315="Atrasado",3000+MIN(Config!$B$5-D315,60),IF(I315="Hoje",2500,IF(D315-Config!$B$5&lt;=Config!$B$6,2000-(D315-Config!$B$5),IF(D315-Config!$B$5&lt;=Config!$B$7,1000-(D315-Config!$B$5),500-MIN(D315-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="316">
@@ -9877,7 +10508,7 @@
       </c>
       <c r="J316" s="35">
         <f>IF(OR(I316="",I316="Feito",I316="Sem data"),0,IF(I316="Atrasado",3000+MIN(Config!$B$5-D316,60),IF(I316="Hoje",2500,IF(D316-Config!$B$5&lt;=Config!$B$6,2000-(D316-Config!$B$5),IF(D316-Config!$B$5&lt;=Config!$B$7,1000-(D316-Config!$B$5),500-MIN(D316-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="317">
@@ -9898,7 +10529,7 @@
       </c>
       <c r="J317" s="35">
         <f>IF(OR(I317="",I317="Feito",I317="Sem data"),0,IF(I317="Atrasado",3000+MIN(Config!$B$5-D317,60),IF(I317="Hoje",2500,IF(D317-Config!$B$5&lt;=Config!$B$6,2000-(D317-Config!$B$5),IF(D317-Config!$B$5&lt;=Config!$B$7,1000-(D317-Config!$B$5),500-MIN(D317-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="318">
@@ -9919,7 +10550,7 @@
       </c>
       <c r="J318" s="35">
         <f>IF(OR(I318="",I318="Feito",I318="Sem data"),0,IF(I318="Atrasado",3000+MIN(Config!$B$5-D318,60),IF(I318="Hoje",2500,IF(D318-Config!$B$5&lt;=Config!$B$6,2000-(D318-Config!$B$5),IF(D318-Config!$B$5&lt;=Config!$B$7,1000-(D318-Config!$B$5),500-MIN(D318-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="319">
@@ -9940,7 +10571,7 @@
       </c>
       <c r="J319" s="35">
         <f>IF(OR(I319="",I319="Feito",I319="Sem data"),0,IF(I319="Atrasado",3000+MIN(Config!$B$5-D319,60),IF(I319="Hoje",2500,IF(D319-Config!$B$5&lt;=Config!$B$6,2000-(D319-Config!$B$5),IF(D319-Config!$B$5&lt;=Config!$B$7,1000-(D319-Config!$B$5),500-MIN(D319-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="320">
@@ -9961,7 +10592,7 @@
       </c>
       <c r="J320" s="35">
         <f>IF(OR(I320="",I320="Feito",I320="Sem data"),0,IF(I320="Atrasado",3000+MIN(Config!$B$5-D320,60),IF(I320="Hoje",2500,IF(D320-Config!$B$5&lt;=Config!$B$6,2000-(D320-Config!$B$5),IF(D320-Config!$B$5&lt;=Config!$B$7,1000-(D320-Config!$B$5),500-MIN(D320-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="321">
@@ -9982,7 +10613,7 @@
       </c>
       <c r="J321" s="35">
         <f>IF(OR(I321="",I321="Feito",I321="Sem data"),0,IF(I321="Atrasado",3000+MIN(Config!$B$5-D321,60),IF(I321="Hoje",2500,IF(D321-Config!$B$5&lt;=Config!$B$6,2000-(D321-Config!$B$5),IF(D321-Config!$B$5&lt;=Config!$B$7,1000-(D321-Config!$B$5),500-MIN(D321-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="322">
@@ -10003,7 +10634,7 @@
       </c>
       <c r="J322" s="35">
         <f>IF(OR(I322="",I322="Feito",I322="Sem data"),0,IF(I322="Atrasado",3000+MIN(Config!$B$5-D322,60),IF(I322="Hoje",2500,IF(D322-Config!$B$5&lt;=Config!$B$6,2000-(D322-Config!$B$5),IF(D322-Config!$B$5&lt;=Config!$B$7,1000-(D322-Config!$B$5),500-MIN(D322-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="323">
@@ -10024,7 +10655,7 @@
       </c>
       <c r="J323" s="35">
         <f>IF(OR(I323="",I323="Feito",I323="Sem data"),0,IF(I323="Atrasado",3000+MIN(Config!$B$5-D323,60),IF(I323="Hoje",2500,IF(D323-Config!$B$5&lt;=Config!$B$6,2000-(D323-Config!$B$5),IF(D323-Config!$B$5&lt;=Config!$B$7,1000-(D323-Config!$B$5),500-MIN(D323-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="324">
@@ -10045,7 +10676,7 @@
       </c>
       <c r="J324" s="35">
         <f>IF(OR(I324="",I324="Feito",I324="Sem data"),0,IF(I324="Atrasado",3000+MIN(Config!$B$5-D324,60),IF(I324="Hoje",2500,IF(D324-Config!$B$5&lt;=Config!$B$6,2000-(D324-Config!$B$5),IF(D324-Config!$B$5&lt;=Config!$B$7,1000-(D324-Config!$B$5),500-MIN(D324-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="325">
@@ -10066,7 +10697,7 @@
       </c>
       <c r="J325" s="35">
         <f>IF(OR(I325="",I325="Feito",I325="Sem data"),0,IF(I325="Atrasado",3000+MIN(Config!$B$5-D325,60),IF(I325="Hoje",2500,IF(D325-Config!$B$5&lt;=Config!$B$6,2000-(D325-Config!$B$5),IF(D325-Config!$B$5&lt;=Config!$B$7,1000-(D325-Config!$B$5),500-MIN(D325-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="326">
@@ -10087,7 +10718,7 @@
       </c>
       <c r="J326" s="35">
         <f>IF(OR(I326="",I326="Feito",I326="Sem data"),0,IF(I326="Atrasado",3000+MIN(Config!$B$5-D326,60),IF(I326="Hoje",2500,IF(D326-Config!$B$5&lt;=Config!$B$6,2000-(D326-Config!$B$5),IF(D326-Config!$B$5&lt;=Config!$B$7,1000-(D326-Config!$B$5),500-MIN(D326-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="327">
@@ -10108,7 +10739,7 @@
       </c>
       <c r="J327" s="35">
         <f>IF(OR(I327="",I327="Feito",I327="Sem data"),0,IF(I327="Atrasado",3000+MIN(Config!$B$5-D327,60),IF(I327="Hoje",2500,IF(D327-Config!$B$5&lt;=Config!$B$6,2000-(D327-Config!$B$5),IF(D327-Config!$B$5&lt;=Config!$B$7,1000-(D327-Config!$B$5),500-MIN(D327-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="328">
@@ -10129,7 +10760,7 @@
       </c>
       <c r="J328" s="35">
         <f>IF(OR(I328="",I328="Feito",I328="Sem data"),0,IF(I328="Atrasado",3000+MIN(Config!$B$5-D328,60),IF(I328="Hoje",2500,IF(D328-Config!$B$5&lt;=Config!$B$6,2000-(D328-Config!$B$5),IF(D328-Config!$B$5&lt;=Config!$B$7,1000-(D328-Config!$B$5),500-MIN(D328-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="329">
@@ -10150,7 +10781,7 @@
       </c>
       <c r="J329" s="35">
         <f>IF(OR(I329="",I329="Feito",I329="Sem data"),0,IF(I329="Atrasado",3000+MIN(Config!$B$5-D329,60),IF(I329="Hoje",2500,IF(D329-Config!$B$5&lt;=Config!$B$6,2000-(D329-Config!$B$5),IF(D329-Config!$B$5&lt;=Config!$B$7,1000-(D329-Config!$B$5),500-MIN(D329-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="330">
@@ -10171,7 +10802,7 @@
       </c>
       <c r="J330" s="35">
         <f>IF(OR(I330="",I330="Feito",I330="Sem data"),0,IF(I330="Atrasado",3000+MIN(Config!$B$5-D330,60),IF(I330="Hoje",2500,IF(D330-Config!$B$5&lt;=Config!$B$6,2000-(D330-Config!$B$5),IF(D330-Config!$B$5&lt;=Config!$B$7,1000-(D330-Config!$B$5),500-MIN(D330-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="331">
@@ -10192,7 +10823,7 @@
       </c>
       <c r="J331" s="35">
         <f>IF(OR(I331="",I331="Feito",I331="Sem data"),0,IF(I331="Atrasado",3000+MIN(Config!$B$5-D331,60),IF(I331="Hoje",2500,IF(D331-Config!$B$5&lt;=Config!$B$6,2000-(D331-Config!$B$5),IF(D331-Config!$B$5&lt;=Config!$B$7,1000-(D331-Config!$B$5),500-MIN(D331-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="332">
@@ -10213,7 +10844,7 @@
       </c>
       <c r="J332" s="35">
         <f>IF(OR(I332="",I332="Feito",I332="Sem data"),0,IF(I332="Atrasado",3000+MIN(Config!$B$5-D332,60),IF(I332="Hoje",2500,IF(D332-Config!$B$5&lt;=Config!$B$6,2000-(D332-Config!$B$5),IF(D332-Config!$B$5&lt;=Config!$B$7,1000-(D332-Config!$B$5),500-MIN(D332-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="333">
@@ -10234,7 +10865,7 @@
       </c>
       <c r="J333" s="35">
         <f>IF(OR(I333="",I333="Feito",I333="Sem data"),0,IF(I333="Atrasado",3000+MIN(Config!$B$5-D333,60),IF(I333="Hoje",2500,IF(D333-Config!$B$5&lt;=Config!$B$6,2000-(D333-Config!$B$5),IF(D333-Config!$B$5&lt;=Config!$B$7,1000-(D333-Config!$B$5),500-MIN(D333-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="334">
@@ -10255,7 +10886,7 @@
       </c>
       <c r="J334" s="35">
         <f>IF(OR(I334="",I334="Feito",I334="Sem data"),0,IF(I334="Atrasado",3000+MIN(Config!$B$5-D334,60),IF(I334="Hoje",2500,IF(D334-Config!$B$5&lt;=Config!$B$6,2000-(D334-Config!$B$5),IF(D334-Config!$B$5&lt;=Config!$B$7,1000-(D334-Config!$B$5),500-MIN(D334-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="335">
@@ -10276,7 +10907,7 @@
       </c>
       <c r="J335" s="35">
         <f>IF(OR(I335="",I335="Feito",I335="Sem data"),0,IF(I335="Atrasado",3000+MIN(Config!$B$5-D335,60),IF(I335="Hoje",2500,IF(D335-Config!$B$5&lt;=Config!$B$6,2000-(D335-Config!$B$5),IF(D335-Config!$B$5&lt;=Config!$B$7,1000-(D335-Config!$B$5),500-MIN(D335-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="336">
@@ -10297,7 +10928,7 @@
       </c>
       <c r="J336" s="35">
         <f>IF(OR(I336="",I336="Feito",I336="Sem data"),0,IF(I336="Atrasado",3000+MIN(Config!$B$5-D336,60),IF(I336="Hoje",2500,IF(D336-Config!$B$5&lt;=Config!$B$6,2000-(D336-Config!$B$5),IF(D336-Config!$B$5&lt;=Config!$B$7,1000-(D336-Config!$B$5),500-MIN(D336-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="337">
@@ -10318,7 +10949,7 @@
       </c>
       <c r="J337" s="35">
         <f>IF(OR(I337="",I337="Feito",I337="Sem data"),0,IF(I337="Atrasado",3000+MIN(Config!$B$5-D337,60),IF(I337="Hoje",2500,IF(D337-Config!$B$5&lt;=Config!$B$6,2000-(D337-Config!$B$5),IF(D337-Config!$B$5&lt;=Config!$B$7,1000-(D337-Config!$B$5),500-MIN(D337-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="338">
@@ -10339,7 +10970,7 @@
       </c>
       <c r="J338" s="35">
         <f>IF(OR(I338="",I338="Feito",I338="Sem data"),0,IF(I338="Atrasado",3000+MIN(Config!$B$5-D338,60),IF(I338="Hoje",2500,IF(D338-Config!$B$5&lt;=Config!$B$6,2000-(D338-Config!$B$5),IF(D338-Config!$B$5&lt;=Config!$B$7,1000-(D338-Config!$B$5),500-MIN(D338-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="339">
@@ -10360,7 +10991,7 @@
       </c>
       <c r="J339" s="35">
         <f>IF(OR(I339="",I339="Feito",I339="Sem data"),0,IF(I339="Atrasado",3000+MIN(Config!$B$5-D339,60),IF(I339="Hoje",2500,IF(D339-Config!$B$5&lt;=Config!$B$6,2000-(D339-Config!$B$5),IF(D339-Config!$B$5&lt;=Config!$B$7,1000-(D339-Config!$B$5),500-MIN(D339-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="340">
@@ -10381,7 +11012,7 @@
       </c>
       <c r="J340" s="35">
         <f>IF(OR(I340="",I340="Feito",I340="Sem data"),0,IF(I340="Atrasado",3000+MIN(Config!$B$5-D340,60),IF(I340="Hoje",2500,IF(D340-Config!$B$5&lt;=Config!$B$6,2000-(D340-Config!$B$5),IF(D340-Config!$B$5&lt;=Config!$B$7,1000-(D340-Config!$B$5),500-MIN(D340-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="341">
@@ -10402,7 +11033,7 @@
       </c>
       <c r="J341" s="35">
         <f>IF(OR(I341="",I341="Feito",I341="Sem data"),0,IF(I341="Atrasado",3000+MIN(Config!$B$5-D341,60),IF(I341="Hoje",2500,IF(D341-Config!$B$5&lt;=Config!$B$6,2000-(D341-Config!$B$5),IF(D341-Config!$B$5&lt;=Config!$B$7,1000-(D341-Config!$B$5),500-MIN(D341-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="342">
@@ -10423,7 +11054,7 @@
       </c>
       <c r="J342" s="35">
         <f>IF(OR(I342="",I342="Feito",I342="Sem data"),0,IF(I342="Atrasado",3000+MIN(Config!$B$5-D342,60),IF(I342="Hoje",2500,IF(D342-Config!$B$5&lt;=Config!$B$6,2000-(D342-Config!$B$5),IF(D342-Config!$B$5&lt;=Config!$B$7,1000-(D342-Config!$B$5),500-MIN(D342-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="343">
@@ -10444,7 +11075,7 @@
       </c>
       <c r="J343" s="35">
         <f>IF(OR(I343="",I343="Feito",I343="Sem data"),0,IF(I343="Atrasado",3000+MIN(Config!$B$5-D343,60),IF(I343="Hoje",2500,IF(D343-Config!$B$5&lt;=Config!$B$6,2000-(D343-Config!$B$5),IF(D343-Config!$B$5&lt;=Config!$B$7,1000-(D343-Config!$B$5),500-MIN(D343-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="344">
@@ -10465,7 +11096,7 @@
       </c>
       <c r="J344" s="35">
         <f>IF(OR(I344="",I344="Feito",I344="Sem data"),0,IF(I344="Atrasado",3000+MIN(Config!$B$5-D344,60),IF(I344="Hoje",2500,IF(D344-Config!$B$5&lt;=Config!$B$6,2000-(D344-Config!$B$5),IF(D344-Config!$B$5&lt;=Config!$B$7,1000-(D344-Config!$B$5),500-MIN(D344-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="345">
@@ -10486,7 +11117,7 @@
       </c>
       <c r="J345" s="35">
         <f>IF(OR(I345="",I345="Feito",I345="Sem data"),0,IF(I345="Atrasado",3000+MIN(Config!$B$5-D345,60),IF(I345="Hoje",2500,IF(D345-Config!$B$5&lt;=Config!$B$6,2000-(D345-Config!$B$5),IF(D345-Config!$B$5&lt;=Config!$B$7,1000-(D345-Config!$B$5),500-MIN(D345-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="346">
@@ -10507,7 +11138,7 @@
       </c>
       <c r="J346" s="35">
         <f>IF(OR(I346="",I346="Feito",I346="Sem data"),0,IF(I346="Atrasado",3000+MIN(Config!$B$5-D346,60),IF(I346="Hoje",2500,IF(D346-Config!$B$5&lt;=Config!$B$6,2000-(D346-Config!$B$5),IF(D346-Config!$B$5&lt;=Config!$B$7,1000-(D346-Config!$B$5),500-MIN(D346-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="347">
@@ -10528,7 +11159,7 @@
       </c>
       <c r="J347" s="35">
         <f>IF(OR(I347="",I347="Feito",I347="Sem data"),0,IF(I347="Atrasado",3000+MIN(Config!$B$5-D347,60),IF(I347="Hoje",2500,IF(D347-Config!$B$5&lt;=Config!$B$6,2000-(D347-Config!$B$5),IF(D347-Config!$B$5&lt;=Config!$B$7,1000-(D347-Config!$B$5),500-MIN(D347-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="348">
@@ -10549,7 +11180,7 @@
       </c>
       <c r="J348" s="35">
         <f>IF(OR(I348="",I348="Feito",I348="Sem data"),0,IF(I348="Atrasado",3000+MIN(Config!$B$5-D348,60),IF(I348="Hoje",2500,IF(D348-Config!$B$5&lt;=Config!$B$6,2000-(D348-Config!$B$5),IF(D348-Config!$B$5&lt;=Config!$B$7,1000-(D348-Config!$B$5),500-MIN(D348-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="349">
@@ -10570,7 +11201,7 @@
       </c>
       <c r="J349" s="35">
         <f>IF(OR(I349="",I349="Feito",I349="Sem data"),0,IF(I349="Atrasado",3000+MIN(Config!$B$5-D349,60),IF(I349="Hoje",2500,IF(D349-Config!$B$5&lt;=Config!$B$6,2000-(D349-Config!$B$5),IF(D349-Config!$B$5&lt;=Config!$B$7,1000-(D349-Config!$B$5),500-MIN(D349-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="350">
@@ -10591,7 +11222,7 @@
       </c>
       <c r="J350" s="35">
         <f>IF(OR(I350="",I350="Feito",I350="Sem data"),0,IF(I350="Atrasado",3000+MIN(Config!$B$5-D350,60),IF(I350="Hoje",2500,IF(D350-Config!$B$5&lt;=Config!$B$6,2000-(D350-Config!$B$5),IF(D350-Config!$B$5&lt;=Config!$B$7,1000-(D350-Config!$B$5),500-MIN(D350-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="351">
@@ -10612,7 +11243,7 @@
       </c>
       <c r="J351" s="35">
         <f>IF(OR(I351="",I351="Feito",I351="Sem data"),0,IF(I351="Atrasado",3000+MIN(Config!$B$5-D351,60),IF(I351="Hoje",2500,IF(D351-Config!$B$5&lt;=Config!$B$6,2000-(D351-Config!$B$5),IF(D351-Config!$B$5&lt;=Config!$B$7,1000-(D351-Config!$B$5),500-MIN(D351-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="352">
@@ -10633,7 +11264,7 @@
       </c>
       <c r="J352" s="35">
         <f>IF(OR(I352="",I352="Feito",I352="Sem data"),0,IF(I352="Atrasado",3000+MIN(Config!$B$5-D352,60),IF(I352="Hoje",2500,IF(D352-Config!$B$5&lt;=Config!$B$6,2000-(D352-Config!$B$5),IF(D352-Config!$B$5&lt;=Config!$B$7,1000-(D352-Config!$B$5),500-MIN(D352-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="353">
@@ -10654,7 +11285,7 @@
       </c>
       <c r="J353" s="35">
         <f>IF(OR(I353="",I353="Feito",I353="Sem data"),0,IF(I353="Atrasado",3000+MIN(Config!$B$5-D353,60),IF(I353="Hoje",2500,IF(D353-Config!$B$5&lt;=Config!$B$6,2000-(D353-Config!$B$5),IF(D353-Config!$B$5&lt;=Config!$B$7,1000-(D353-Config!$B$5),500-MIN(D353-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="354">
@@ -10675,7 +11306,7 @@
       </c>
       <c r="J354" s="35">
         <f>IF(OR(I354="",I354="Feito",I354="Sem data"),0,IF(I354="Atrasado",3000+MIN(Config!$B$5-D354,60),IF(I354="Hoje",2500,IF(D354-Config!$B$5&lt;=Config!$B$6,2000-(D354-Config!$B$5),IF(D354-Config!$B$5&lt;=Config!$B$7,1000-(D354-Config!$B$5),500-MIN(D354-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="355">
@@ -10696,7 +11327,7 @@
       </c>
       <c r="J355" s="35">
         <f>IF(OR(I355="",I355="Feito",I355="Sem data"),0,IF(I355="Atrasado",3000+MIN(Config!$B$5-D355,60),IF(I355="Hoje",2500,IF(D355-Config!$B$5&lt;=Config!$B$6,2000-(D355-Config!$B$5),IF(D355-Config!$B$5&lt;=Config!$B$7,1000-(D355-Config!$B$5),500-MIN(D355-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="356">
@@ -10717,7 +11348,7 @@
       </c>
       <c r="J356" s="35">
         <f>IF(OR(I356="",I356="Feito",I356="Sem data"),0,IF(I356="Atrasado",3000+MIN(Config!$B$5-D356,60),IF(I356="Hoje",2500,IF(D356-Config!$B$5&lt;=Config!$B$6,2000-(D356-Config!$B$5),IF(D356-Config!$B$5&lt;=Config!$B$7,1000-(D356-Config!$B$5),500-MIN(D356-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="357">
@@ -10738,7 +11369,7 @@
       </c>
       <c r="J357" s="35">
         <f>IF(OR(I357="",I357="Feito",I357="Sem data"),0,IF(I357="Atrasado",3000+MIN(Config!$B$5-D357,60),IF(I357="Hoje",2500,IF(D357-Config!$B$5&lt;=Config!$B$6,2000-(D357-Config!$B$5),IF(D357-Config!$B$5&lt;=Config!$B$7,1000-(D357-Config!$B$5),500-MIN(D357-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="358">
@@ -10759,7 +11390,7 @@
       </c>
       <c r="J358" s="35">
         <f>IF(OR(I358="",I358="Feito",I358="Sem data"),0,IF(I358="Atrasado",3000+MIN(Config!$B$5-D358,60),IF(I358="Hoje",2500,IF(D358-Config!$B$5&lt;=Config!$B$6,2000-(D358-Config!$B$5),IF(D358-Config!$B$5&lt;=Config!$B$7,1000-(D358-Config!$B$5),500-MIN(D358-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="359">
@@ -10780,7 +11411,7 @@
       </c>
       <c r="J359" s="35">
         <f>IF(OR(I359="",I359="Feito",I359="Sem data"),0,IF(I359="Atrasado",3000+MIN(Config!$B$5-D359,60),IF(I359="Hoje",2500,IF(D359-Config!$B$5&lt;=Config!$B$6,2000-(D359-Config!$B$5),IF(D359-Config!$B$5&lt;=Config!$B$7,1000-(D359-Config!$B$5),500-MIN(D359-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="360">
@@ -10801,7 +11432,7 @@
       </c>
       <c r="J360" s="35">
         <f>IF(OR(I360="",I360="Feito",I360="Sem data"),0,IF(I360="Atrasado",3000+MIN(Config!$B$5-D360,60),IF(I360="Hoje",2500,IF(D360-Config!$B$5&lt;=Config!$B$6,2000-(D360-Config!$B$5),IF(D360-Config!$B$5&lt;=Config!$B$7,1000-(D360-Config!$B$5),500-MIN(D360-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="361">
@@ -10822,7 +11453,7 @@
       </c>
       <c r="J361" s="35">
         <f>IF(OR(I361="",I361="Feito",I361="Sem data"),0,IF(I361="Atrasado",3000+MIN(Config!$B$5-D361,60),IF(I361="Hoje",2500,IF(D361-Config!$B$5&lt;=Config!$B$6,2000-(D361-Config!$B$5),IF(D361-Config!$B$5&lt;=Config!$B$7,1000-(D361-Config!$B$5),500-MIN(D361-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="362">
@@ -10843,7 +11474,7 @@
       </c>
       <c r="J362" s="35">
         <f>IF(OR(I362="",I362="Feito",I362="Sem data"),0,IF(I362="Atrasado",3000+MIN(Config!$B$5-D362,60),IF(I362="Hoje",2500,IF(D362-Config!$B$5&lt;=Config!$B$6,2000-(D362-Config!$B$5),IF(D362-Config!$B$5&lt;=Config!$B$7,1000-(D362-Config!$B$5),500-MIN(D362-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="363">
@@ -10864,7 +11495,7 @@
       </c>
       <c r="J363" s="35">
         <f>IF(OR(I363="",I363="Feito",I363="Sem data"),0,IF(I363="Atrasado",3000+MIN(Config!$B$5-D363,60),IF(I363="Hoje",2500,IF(D363-Config!$B$5&lt;=Config!$B$6,2000-(D363-Config!$B$5),IF(D363-Config!$B$5&lt;=Config!$B$7,1000-(D363-Config!$B$5),500-MIN(D363-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="364">
@@ -10885,7 +11516,7 @@
       </c>
       <c r="J364" s="35">
         <f>IF(OR(I364="",I364="Feito",I364="Sem data"),0,IF(I364="Atrasado",3000+MIN(Config!$B$5-D364,60),IF(I364="Hoje",2500,IF(D364-Config!$B$5&lt;=Config!$B$6,2000-(D364-Config!$B$5),IF(D364-Config!$B$5&lt;=Config!$B$7,1000-(D364-Config!$B$5),500-MIN(D364-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="365">
@@ -10906,7 +11537,7 @@
       </c>
       <c r="J365" s="35">
         <f>IF(OR(I365="",I365="Feito",I365="Sem data"),0,IF(I365="Atrasado",3000+MIN(Config!$B$5-D365,60),IF(I365="Hoje",2500,IF(D365-Config!$B$5&lt;=Config!$B$6,2000-(D365-Config!$B$5),IF(D365-Config!$B$5&lt;=Config!$B$7,1000-(D365-Config!$B$5),500-MIN(D365-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="366">
@@ -10927,7 +11558,7 @@
       </c>
       <c r="J366" s="35">
         <f>IF(OR(I366="",I366="Feito",I366="Sem data"),0,IF(I366="Atrasado",3000+MIN(Config!$B$5-D366,60),IF(I366="Hoje",2500,IF(D366-Config!$B$5&lt;=Config!$B$6,2000-(D366-Config!$B$5),IF(D366-Config!$B$5&lt;=Config!$B$7,1000-(D366-Config!$B$5),500-MIN(D366-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="367">
@@ -10948,7 +11579,7 @@
       </c>
       <c r="J367" s="35">
         <f>IF(OR(I367="",I367="Feito",I367="Sem data"),0,IF(I367="Atrasado",3000+MIN(Config!$B$5-D367,60),IF(I367="Hoje",2500,IF(D367-Config!$B$5&lt;=Config!$B$6,2000-(D367-Config!$B$5),IF(D367-Config!$B$5&lt;=Config!$B$7,1000-(D367-Config!$B$5),500-MIN(D367-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="368">
@@ -10969,7 +11600,7 @@
       </c>
       <c r="J368" s="35">
         <f>IF(OR(I368="",I368="Feito",I368="Sem data"),0,IF(I368="Atrasado",3000+MIN(Config!$B$5-D368,60),IF(I368="Hoje",2500,IF(D368-Config!$B$5&lt;=Config!$B$6,2000-(D368-Config!$B$5),IF(D368-Config!$B$5&lt;=Config!$B$7,1000-(D368-Config!$B$5),500-MIN(D368-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="369">
@@ -10990,7 +11621,7 @@
       </c>
       <c r="J369" s="35">
         <f>IF(OR(I369="",I369="Feito",I369="Sem data"),0,IF(I369="Atrasado",3000+MIN(Config!$B$5-D369,60),IF(I369="Hoje",2500,IF(D369-Config!$B$5&lt;=Config!$B$6,2000-(D369-Config!$B$5),IF(D369-Config!$B$5&lt;=Config!$B$7,1000-(D369-Config!$B$5),500-MIN(D369-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="370">
@@ -11011,7 +11642,7 @@
       </c>
       <c r="J370" s="35">
         <f>IF(OR(I370="",I370="Feito",I370="Sem data"),0,IF(I370="Atrasado",3000+MIN(Config!$B$5-D370,60),IF(I370="Hoje",2500,IF(D370-Config!$B$5&lt;=Config!$B$6,2000-(D370-Config!$B$5),IF(D370-Config!$B$5&lt;=Config!$B$7,1000-(D370-Config!$B$5),500-MIN(D370-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="371">
@@ -11032,7 +11663,7 @@
       </c>
       <c r="J371" s="35">
         <f>IF(OR(I371="",I371="Feito",I371="Sem data"),0,IF(I371="Atrasado",3000+MIN(Config!$B$5-D371,60),IF(I371="Hoje",2500,IF(D371-Config!$B$5&lt;=Config!$B$6,2000-(D371-Config!$B$5),IF(D371-Config!$B$5&lt;=Config!$B$7,1000-(D371-Config!$B$5),500-MIN(D371-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="372">
@@ -11053,7 +11684,7 @@
       </c>
       <c r="J372" s="35">
         <f>IF(OR(I372="",I372="Feito",I372="Sem data"),0,IF(I372="Atrasado",3000+MIN(Config!$B$5-D372,60),IF(I372="Hoje",2500,IF(D372-Config!$B$5&lt;=Config!$B$6,2000-(D372-Config!$B$5),IF(D372-Config!$B$5&lt;=Config!$B$7,1000-(D372-Config!$B$5),500-MIN(D372-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="373">
@@ -11074,7 +11705,7 @@
       </c>
       <c r="J373" s="35">
         <f>IF(OR(I373="",I373="Feito",I373="Sem data"),0,IF(I373="Atrasado",3000+MIN(Config!$B$5-D373,60),IF(I373="Hoje",2500,IF(D373-Config!$B$5&lt;=Config!$B$6,2000-(D373-Config!$B$5),IF(D373-Config!$B$5&lt;=Config!$B$7,1000-(D373-Config!$B$5),500-MIN(D373-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="374">
@@ -11095,7 +11726,7 @@
       </c>
       <c r="J374" s="35">
         <f>IF(OR(I374="",I374="Feito",I374="Sem data"),0,IF(I374="Atrasado",3000+MIN(Config!$B$5-D374,60),IF(I374="Hoje",2500,IF(D374-Config!$B$5&lt;=Config!$B$6,2000-(D374-Config!$B$5),IF(D374-Config!$B$5&lt;=Config!$B$7,1000-(D374-Config!$B$5),500-MIN(D374-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="375">
@@ -11116,7 +11747,7 @@
       </c>
       <c r="J375" s="35">
         <f>IF(OR(I375="",I375="Feito",I375="Sem data"),0,IF(I375="Atrasado",3000+MIN(Config!$B$5-D375,60),IF(I375="Hoje",2500,IF(D375-Config!$B$5&lt;=Config!$B$6,2000-(D375-Config!$B$5),IF(D375-Config!$B$5&lt;=Config!$B$7,1000-(D375-Config!$B$5),500-MIN(D375-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="376">
@@ -11137,7 +11768,7 @@
       </c>
       <c r="J376" s="35">
         <f>IF(OR(I376="",I376="Feito",I376="Sem data"),0,IF(I376="Atrasado",3000+MIN(Config!$B$5-D376,60),IF(I376="Hoje",2500,IF(D376-Config!$B$5&lt;=Config!$B$6,2000-(D376-Config!$B$5),IF(D376-Config!$B$5&lt;=Config!$B$7,1000-(D376-Config!$B$5),500-MIN(D376-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="377">
@@ -11158,7 +11789,7 @@
       </c>
       <c r="J377" s="35">
         <f>IF(OR(I377="",I377="Feito",I377="Sem data"),0,IF(I377="Atrasado",3000+MIN(Config!$B$5-D377,60),IF(I377="Hoje",2500,IF(D377-Config!$B$5&lt;=Config!$B$6,2000-(D377-Config!$B$5),IF(D377-Config!$B$5&lt;=Config!$B$7,1000-(D377-Config!$B$5),500-MIN(D377-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="378">
@@ -11179,7 +11810,7 @@
       </c>
       <c r="J378" s="35">
         <f>IF(OR(I378="",I378="Feito",I378="Sem data"),0,IF(I378="Atrasado",3000+MIN(Config!$B$5-D378,60),IF(I378="Hoje",2500,IF(D378-Config!$B$5&lt;=Config!$B$6,2000-(D378-Config!$B$5),IF(D378-Config!$B$5&lt;=Config!$B$7,1000-(D378-Config!$B$5),500-MIN(D378-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="379">
@@ -11200,7 +11831,7 @@
       </c>
       <c r="J379" s="35">
         <f>IF(OR(I379="",I379="Feito",I379="Sem data"),0,IF(I379="Atrasado",3000+MIN(Config!$B$5-D379,60),IF(I379="Hoje",2500,IF(D379-Config!$B$5&lt;=Config!$B$6,2000-(D379-Config!$B$5),IF(D379-Config!$B$5&lt;=Config!$B$7,1000-(D379-Config!$B$5),500-MIN(D379-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="380">
@@ -11221,7 +11852,7 @@
       </c>
       <c r="J380" s="35">
         <f>IF(OR(I380="",I380="Feito",I380="Sem data"),0,IF(I380="Atrasado",3000+MIN(Config!$B$5-D380,60),IF(I380="Hoje",2500,IF(D380-Config!$B$5&lt;=Config!$B$6,2000-(D380-Config!$B$5),IF(D380-Config!$B$5&lt;=Config!$B$7,1000-(D380-Config!$B$5),500-MIN(D380-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="381">
@@ -11242,7 +11873,7 @@
       </c>
       <c r="J381" s="35">
         <f>IF(OR(I381="",I381="Feito",I381="Sem data"),0,IF(I381="Atrasado",3000+MIN(Config!$B$5-D381,60),IF(I381="Hoje",2500,IF(D381-Config!$B$5&lt;=Config!$B$6,2000-(D381-Config!$B$5),IF(D381-Config!$B$5&lt;=Config!$B$7,1000-(D381-Config!$B$5),500-MIN(D381-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="382">
@@ -11263,7 +11894,7 @@
       </c>
       <c r="J382" s="35">
         <f>IF(OR(I382="",I382="Feito",I382="Sem data"),0,IF(I382="Atrasado",3000+MIN(Config!$B$5-D382,60),IF(I382="Hoje",2500,IF(D382-Config!$B$5&lt;=Config!$B$6,2000-(D382-Config!$B$5),IF(D382-Config!$B$5&lt;=Config!$B$7,1000-(D382-Config!$B$5),500-MIN(D382-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="383">
@@ -11284,7 +11915,7 @@
       </c>
       <c r="J383" s="35">
         <f>IF(OR(I383="",I383="Feito",I383="Sem data"),0,IF(I383="Atrasado",3000+MIN(Config!$B$5-D383,60),IF(I383="Hoje",2500,IF(D383-Config!$B$5&lt;=Config!$B$6,2000-(D383-Config!$B$5),IF(D383-Config!$B$5&lt;=Config!$B$7,1000-(D383-Config!$B$5),500-MIN(D383-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="384">
@@ -11305,7 +11936,7 @@
       </c>
       <c r="J384" s="35">
         <f>IF(OR(I384="",I384="Feito",I384="Sem data"),0,IF(I384="Atrasado",3000+MIN(Config!$B$5-D384,60),IF(I384="Hoje",2500,IF(D384-Config!$B$5&lt;=Config!$B$6,2000-(D384-Config!$B$5),IF(D384-Config!$B$5&lt;=Config!$B$7,1000-(D384-Config!$B$5),500-MIN(D384-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="385">
@@ -11326,7 +11957,7 @@
       </c>
       <c r="J385" s="35">
         <f>IF(OR(I385="",I385="Feito",I385="Sem data"),0,IF(I385="Atrasado",3000+MIN(Config!$B$5-D385,60),IF(I385="Hoje",2500,IF(D385-Config!$B$5&lt;=Config!$B$6,2000-(D385-Config!$B$5),IF(D385-Config!$B$5&lt;=Config!$B$7,1000-(D385-Config!$B$5),500-MIN(D385-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="386">
@@ -11347,7 +11978,7 @@
       </c>
       <c r="J386" s="35">
         <f>IF(OR(I386="",I386="Feito",I386="Sem data"),0,IF(I386="Atrasado",3000+MIN(Config!$B$5-D386,60),IF(I386="Hoje",2500,IF(D386-Config!$B$5&lt;=Config!$B$6,2000-(D386-Config!$B$5),IF(D386-Config!$B$5&lt;=Config!$B$7,1000-(D386-Config!$B$5),500-MIN(D386-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="387">
@@ -11368,7 +11999,7 @@
       </c>
       <c r="J387" s="35">
         <f>IF(OR(I387="",I387="Feito",I387="Sem data"),0,IF(I387="Atrasado",3000+MIN(Config!$B$5-D387,60),IF(I387="Hoje",2500,IF(D387-Config!$B$5&lt;=Config!$B$6,2000-(D387-Config!$B$5),IF(D387-Config!$B$5&lt;=Config!$B$7,1000-(D387-Config!$B$5),500-MIN(D387-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="388">
@@ -11389,7 +12020,7 @@
       </c>
       <c r="J388" s="35">
         <f>IF(OR(I388="",I388="Feito",I388="Sem data"),0,IF(I388="Atrasado",3000+MIN(Config!$B$5-D388,60),IF(I388="Hoje",2500,IF(D388-Config!$B$5&lt;=Config!$B$6,2000-(D388-Config!$B$5),IF(D388-Config!$B$5&lt;=Config!$B$7,1000-(D388-Config!$B$5),500-MIN(D388-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="389">
@@ -11410,7 +12041,7 @@
       </c>
       <c r="J389" s="35">
         <f>IF(OR(I389="",I389="Feito",I389="Sem data"),0,IF(I389="Atrasado",3000+MIN(Config!$B$5-D389,60),IF(I389="Hoje",2500,IF(D389-Config!$B$5&lt;=Config!$B$6,2000-(D389-Config!$B$5),IF(D389-Config!$B$5&lt;=Config!$B$7,1000-(D389-Config!$B$5),500-MIN(D389-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="390">
@@ -11431,7 +12062,7 @@
       </c>
       <c r="J390" s="35">
         <f>IF(OR(I390="",I390="Feito",I390="Sem data"),0,IF(I390="Atrasado",3000+MIN(Config!$B$5-D390,60),IF(I390="Hoje",2500,IF(D390-Config!$B$5&lt;=Config!$B$6,2000-(D390-Config!$B$5),IF(D390-Config!$B$5&lt;=Config!$B$7,1000-(D390-Config!$B$5),500-MIN(D390-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="391">
@@ -11452,7 +12083,7 @@
       </c>
       <c r="J391" s="35">
         <f>IF(OR(I391="",I391="Feito",I391="Sem data"),0,IF(I391="Atrasado",3000+MIN(Config!$B$5-D391,60),IF(I391="Hoje",2500,IF(D391-Config!$B$5&lt;=Config!$B$6,2000-(D391-Config!$B$5),IF(D391-Config!$B$5&lt;=Config!$B$7,1000-(D391-Config!$B$5),500-MIN(D391-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="392">
@@ -11473,7 +12104,7 @@
       </c>
       <c r="J392" s="35">
         <f>IF(OR(I392="",I392="Feito",I392="Sem data"),0,IF(I392="Atrasado",3000+MIN(Config!$B$5-D392,60),IF(I392="Hoje",2500,IF(D392-Config!$B$5&lt;=Config!$B$6,2000-(D392-Config!$B$5),IF(D392-Config!$B$5&lt;=Config!$B$7,1000-(D392-Config!$B$5),500-MIN(D392-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="393">
@@ -11494,7 +12125,7 @@
       </c>
       <c r="J393" s="35">
         <f>IF(OR(I393="",I393="Feito",I393="Sem data"),0,IF(I393="Atrasado",3000+MIN(Config!$B$5-D393,60),IF(I393="Hoje",2500,IF(D393-Config!$B$5&lt;=Config!$B$6,2000-(D393-Config!$B$5),IF(D393-Config!$B$5&lt;=Config!$B$7,1000-(D393-Config!$B$5),500-MIN(D393-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="394">
@@ -11515,7 +12146,7 @@
       </c>
       <c r="J394" s="35">
         <f>IF(OR(I394="",I394="Feito",I394="Sem data"),0,IF(I394="Atrasado",3000+MIN(Config!$B$5-D394,60),IF(I394="Hoje",2500,IF(D394-Config!$B$5&lt;=Config!$B$6,2000-(D394-Config!$B$5),IF(D394-Config!$B$5&lt;=Config!$B$7,1000-(D394-Config!$B$5),500-MIN(D394-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="395">
@@ -11536,7 +12167,7 @@
       </c>
       <c r="J395" s="35">
         <f>IF(OR(I395="",I395="Feito",I395="Sem data"),0,IF(I395="Atrasado",3000+MIN(Config!$B$5-D395,60),IF(I395="Hoje",2500,IF(D395-Config!$B$5&lt;=Config!$B$6,2000-(D395-Config!$B$5),IF(D395-Config!$B$5&lt;=Config!$B$7,1000-(D395-Config!$B$5),500-MIN(D395-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="396">
@@ -11557,7 +12188,7 @@
       </c>
       <c r="J396" s="35">
         <f>IF(OR(I396="",I396="Feito",I396="Sem data"),0,IF(I396="Atrasado",3000+MIN(Config!$B$5-D396,60),IF(I396="Hoje",2500,IF(D396-Config!$B$5&lt;=Config!$B$6,2000-(D396-Config!$B$5),IF(D396-Config!$B$5&lt;=Config!$B$7,1000-(D396-Config!$B$5),500-MIN(D396-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="397">
@@ -11578,7 +12209,7 @@
       </c>
       <c r="J397" s="35">
         <f>IF(OR(I397="",I397="Feito",I397="Sem data"),0,IF(I397="Atrasado",3000+MIN(Config!$B$5-D397,60),IF(I397="Hoje",2500,IF(D397-Config!$B$5&lt;=Config!$B$6,2000-(D397-Config!$B$5),IF(D397-Config!$B$5&lt;=Config!$B$7,1000-(D397-Config!$B$5),500-MIN(D397-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="398">
@@ -11599,7 +12230,7 @@
       </c>
       <c r="J398" s="35">
         <f>IF(OR(I398="",I398="Feito",I398="Sem data"),0,IF(I398="Atrasado",3000+MIN(Config!$B$5-D398,60),IF(I398="Hoje",2500,IF(D398-Config!$B$5&lt;=Config!$B$6,2000-(D398-Config!$B$5),IF(D398-Config!$B$5&lt;=Config!$B$7,1000-(D398-Config!$B$5),500-MIN(D398-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="399">
@@ -11620,7 +12251,7 @@
       </c>
       <c r="J399" s="35">
         <f>IF(OR(I399="",I399="Feito",I399="Sem data"),0,IF(I399="Atrasado",3000+MIN(Config!$B$5-D399,60),IF(I399="Hoje",2500,IF(D399-Config!$B$5&lt;=Config!$B$6,2000-(D399-Config!$B$5),IF(D399-Config!$B$5&lt;=Config!$B$7,1000-(D399-Config!$B$5),500-MIN(D399-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="400">
@@ -11641,7 +12272,7 @@
       </c>
       <c r="J400" s="35">
         <f>IF(OR(I400="",I400="Feito",I400="Sem data"),0,IF(I400="Atrasado",3000+MIN(Config!$B$5-D400,60),IF(I400="Hoje",2500,IF(D400-Config!$B$5&lt;=Config!$B$6,2000-(D400-Config!$B$5),IF(D400-Config!$B$5&lt;=Config!$B$7,1000-(D400-Config!$B$5),500-MIN(D400-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="401">
@@ -11662,7 +12293,7 @@
       </c>
       <c r="J401" s="35">
         <f>IF(OR(I401="",I401="Feito",I401="Sem data"),0,IF(I401="Atrasado",3000+MIN(Config!$B$5-D401,60),IF(I401="Hoje",2500,IF(D401-Config!$B$5&lt;=Config!$B$6,2000-(D401-Config!$B$5),IF(D401-Config!$B$5&lt;=Config!$B$7,1000-(D401-Config!$B$5),500-MIN(D401-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="402">
@@ -11683,7 +12314,7 @@
       </c>
       <c r="J402" s="35">
         <f>IF(OR(I402="",I402="Feito",I402="Sem data"),0,IF(I402="Atrasado",3000+MIN(Config!$B$5-D402,60),IF(I402="Hoje",2500,IF(D402-Config!$B$5&lt;=Config!$B$6,2000-(D402-Config!$B$5),IF(D402-Config!$B$5&lt;=Config!$B$7,1000-(D402-Config!$B$5),500-MIN(D402-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="403">
@@ -11704,7 +12335,7 @@
       </c>
       <c r="J403" s="35">
         <f>IF(OR(I403="",I403="Feito",I403="Sem data"),0,IF(I403="Atrasado",3000+MIN(Config!$B$5-D403,60),IF(I403="Hoje",2500,IF(D403-Config!$B$5&lt;=Config!$B$6,2000-(D403-Config!$B$5),IF(D403-Config!$B$5&lt;=Config!$B$7,1000-(D403-Config!$B$5),500-MIN(D403-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="404">
@@ -11725,7 +12356,7 @@
       </c>
       <c r="J404" s="35">
         <f>IF(OR(I404="",I404="Feito",I404="Sem data"),0,IF(I404="Atrasado",3000+MIN(Config!$B$5-D404,60),IF(I404="Hoje",2500,IF(D404-Config!$B$5&lt;=Config!$B$6,2000-(D404-Config!$B$5),IF(D404-Config!$B$5&lt;=Config!$B$7,1000-(D404-Config!$B$5),500-MIN(D404-Config!$B$5,400)))))-ROW()/100000)</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/01-agenda-de-prazos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/01-agenda-de-prazos.xlsx
@@ -810,7 +810,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>10 minutos: abra o Painel, resolva ou reagende os atrasados, confirme com cada responsável os prazos da semana e registre os prazos novos que chegaram.</t>
+          <t>10 minutos: abra o Painel e trate os atrasados. Prazo processual em atraso NÃO se reagenda aqui: confira na fonte oficial (sistema do tribunal, publicação) e leve ao responsável; a planilha mantém a data original e serve só de registro. Só tarefa administrativa pode ser remarcada. Depois confirme os prazos da semana e registre os que chegaram.</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="str">
         <f>Config!$B$4&amp;" · Painel de prazos · "&amp;TEXT(Config!$B$5,"dd/mm/yyyy")</f>
-        <v>Ferraz &amp; Lima Advocacia (exemplo fictício) · Painel de prazos · 14/09/2026</v>
+        <v>Ferraz &amp; Lima Advocacia (exemplo fictício) · Painel de prazos · 17/09/2026</v>
       </c>
     </row>
     <row r="2">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="E10" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,1)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,1),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,1),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46273.0</v>
+        <v>46276.0</v>
       </c>
       <c r="F10" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,1)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,1),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,1),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E11" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,2)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,2),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,2),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46274.0</v>
+        <v>46277.0</v>
       </c>
       <c r="F11" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,2)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,2),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,2),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E12" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,3)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,3),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,3),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46275.0</v>
+        <v>46278.0</v>
       </c>
       <c r="F12" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,3)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,3),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,3),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="E13" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,4)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,4),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,4),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46276.0</v>
+        <v>46279.0</v>
       </c>
       <c r="F13" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,4)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,4),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,4),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="E14" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,5)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,5),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,5),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46277.0</v>
+        <v>46280.0</v>
       </c>
       <c r="F14" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,5)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,5),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,5),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="E15" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,6)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,6),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,6),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46278.0</v>
+        <v>46281.0</v>
       </c>
       <c r="F15" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,6)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,6),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,6),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="E16" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,7)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,7),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,7),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46278.0</v>
+        <v>46281.0</v>
       </c>
       <c r="F16" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,7)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,7),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,7),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="E17" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,8)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,8),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,8),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46279.0</v>
+        <v>46282.0</v>
       </c>
       <c r="F17" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,8)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,8),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,8),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="E18" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,9)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,9),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,9),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46279.0</v>
+        <v>46282.0</v>
       </c>
       <c r="F18" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,9)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,9),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,9),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="E19" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,10)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,10),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,10),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46279.0</v>
+        <v>46282.0</v>
       </c>
       <c r="F19" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,10)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,10),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,10),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="E20" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,11)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,11),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,11),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46280.0</v>
+        <v>46283.0</v>
       </c>
       <c r="F20" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,11)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,11),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,11),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="E21" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,12)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,12),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,12),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46280.0</v>
+        <v>46283.0</v>
       </c>
       <c r="F21" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,12)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,12),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,12),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="E22" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,13)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,13),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,13),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46281.0</v>
+        <v>46284.0</v>
       </c>
       <c r="F22" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,13)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,13),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,13),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="E23" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,14)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,14),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,14),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46281.0</v>
+        <v>46284.0</v>
       </c>
       <c r="F23" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,14)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,14),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,14),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="E24" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,15)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,15),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,15),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46282.0</v>
+        <v>46285.0</v>
       </c>
       <c r="F24" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,15)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,15),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,15),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="E25" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,16)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,16),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,16),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46282.0</v>
+        <v>46285.0</v>
       </c>
       <c r="F25" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,16)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,16),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,16),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="E26" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,17)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,17),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,17),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46283.0</v>
+        <v>46286.0</v>
       </c>
       <c r="F26" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,17)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,17),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,17),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="E27" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,18)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,18),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,18),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46283.0</v>
+        <v>46286.0</v>
       </c>
       <c r="F27" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,18)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,18),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,18),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E28" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,19)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,19),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,19),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46284.0</v>
+        <v>46287.0</v>
       </c>
       <c r="F28" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,19)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,19),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,19),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="E29" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,20)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,20),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,20),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46284.0</v>
+        <v>46287.0</v>
       </c>
       <c r="F29" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,20)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,20),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,20),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="E30" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,21)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,21),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,21),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46285.0</v>
+        <v>46288.0</v>
       </c>
       <c r="F30" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,21)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,21),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,21),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="E31" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,22)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,22),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,22),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46287.0</v>
+        <v>46290.0</v>
       </c>
       <c r="F31" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,22)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,22),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,22),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="E32" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,23)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,23),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,23),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46288.0</v>
+        <v>46291.0</v>
       </c>
       <c r="F32" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,23)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,23),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,23),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="E33" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,24)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,24),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,24),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46288.0</v>
+        <v>46291.0</v>
       </c>
       <c r="F33" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,24)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,24),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,24),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="E34" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,25)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,25),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,25),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46289.0</v>
+        <v>46292.0</v>
       </c>
       <c r="F34" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,25)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,25),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,25),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="E35" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,26)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,26),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,26),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46291.0</v>
+        <v>46294.0</v>
       </c>
       <c r="F35" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,26)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,26),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,26),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="E36" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,27)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,27),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,27),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46291.0</v>
+        <v>46294.0</v>
       </c>
       <c r="F36" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,27)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,27),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,27),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="E37" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,28)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,28),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,28),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46294.0</v>
+        <v>46297.0</v>
       </c>
       <c r="F37" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,28)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,28),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,28),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="E38" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,29)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,29),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,29),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46295.0</v>
+        <v>46298.0</v>
       </c>
       <c r="F38" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,29)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,29),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,29),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="E39" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,30)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,30),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,30),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46295.0</v>
+        <v>46298.0</v>
       </c>
       <c r="F39" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,30)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,30),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,30),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="G43" s="27">
         <f>IF(Config!$B$10="","",IFERROR(IF(SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$10)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$10)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))&gt;=1E+10,"",SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$10)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$10)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))),""))</f>
-        <v>46276.0</v>
+        <v>46279.0</v>
       </c>
       <c r="H43" s="25">
         <f>IF(Config!$B$10="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$10,Prazos!$I$5:$I$404,"Feito"))</f>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="G44" s="27">
         <f>IF(Config!$B$11="","",IFERROR(IF(SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$11)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$11)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))&gt;=1E+10,"",SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$11)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$11)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))),""))</f>
-        <v>46274.0</v>
+        <v>46277.0</v>
       </c>
       <c r="H44" s="25">
         <f>IF(Config!$B$11="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$11,Prazos!$I$5:$I$404,"Feito"))</f>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="G45" s="27">
         <f>IF(Config!$B$12="","",IFERROR(IF(SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$12)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$12)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))&gt;=1E+10,"",SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$12)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$12)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))),""))</f>
-        <v>46273.0</v>
+        <v>46276.0</v>
       </c>
       <c r="H45" s="25">
         <f>IF(Config!$B$12="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$12,Prazos!$I$5:$I$404,"Feito"))</f>
@@ -2480,12 +2480,12 @@
     <row r="58">
       <c r="A58" s="25" t="str">
         <f>CHOOSE(WEEKDAY(C58),"domingo","segunda","terça","quarta","quinta","sexta","sábado")</f>
-        <v>segunda</v>
+        <v>quinta</v>
       </c>
       <c r="B58" s="25" t="n"/>
       <c r="C58" s="27">
         <f>Config!$B$5+0</f>
-        <v>46279.0</v>
+        <v>46282.0</v>
       </c>
       <c r="D58" s="25">
         <f>COUNTIFS(Prazos!$D$5:$D$404,C58,Prazos!$F$5:$F$404,"&lt;&gt;Sim")</f>
@@ -2507,12 +2507,12 @@
     <row r="59">
       <c r="A59" s="25" t="str">
         <f>CHOOSE(WEEKDAY(C59),"domingo","segunda","terça","quarta","quinta","sexta","sábado")</f>
-        <v>terça</v>
+        <v>sexta</v>
       </c>
       <c r="B59" s="25" t="n"/>
       <c r="C59" s="27">
         <f>Config!$B$5+1</f>
-        <v>46280.0</v>
+        <v>46283.0</v>
       </c>
       <c r="D59" s="25">
         <f>COUNTIFS(Prazos!$D$5:$D$404,C59,Prazos!$F$5:$F$404,"&lt;&gt;Sim")</f>
@@ -2534,12 +2534,12 @@
     <row r="60">
       <c r="A60" s="25" t="str">
         <f>CHOOSE(WEEKDAY(C60),"domingo","segunda","terça","quarta","quinta","sexta","sábado")</f>
-        <v>quarta</v>
+        <v>sábado</v>
       </c>
       <c r="B60" s="25" t="n"/>
       <c r="C60" s="27">
         <f>Config!$B$5+2</f>
-        <v>46281.0</v>
+        <v>46284.0</v>
       </c>
       <c r="D60" s="25">
         <f>COUNTIFS(Prazos!$D$5:$D$404,C60,Prazos!$F$5:$F$404,"&lt;&gt;Sim")</f>
@@ -2561,12 +2561,12 @@
     <row r="61">
       <c r="A61" s="25" t="str">
         <f>CHOOSE(WEEKDAY(C61),"domingo","segunda","terça","quarta","quinta","sexta","sábado")</f>
-        <v>quinta</v>
+        <v>domingo</v>
       </c>
       <c r="B61" s="25" t="n"/>
       <c r="C61" s="27">
         <f>Config!$B$5+3</f>
-        <v>46282.0</v>
+        <v>46285.0</v>
       </c>
       <c r="D61" s="25">
         <f>COUNTIFS(Prazos!$D$5:$D$404,C61,Prazos!$F$5:$F$404,"&lt;&gt;Sim")</f>
@@ -2588,12 +2588,12 @@
     <row r="62">
       <c r="A62" s="25" t="str">
         <f>CHOOSE(WEEKDAY(C62),"domingo","segunda","terça","quarta","quinta","sexta","sábado")</f>
-        <v>sexta</v>
+        <v>segunda</v>
       </c>
       <c r="B62" s="25" t="n"/>
       <c r="C62" s="27">
         <f>Config!$B$5+4</f>
-        <v>46283.0</v>
+        <v>46286.0</v>
       </c>
       <c r="D62" s="25">
         <f>COUNTIFS(Prazos!$D$5:$D$404,C62,Prazos!$F$5:$F$404,"&lt;&gt;Sim")</f>
@@ -2615,12 +2615,12 @@
     <row r="63">
       <c r="A63" s="25" t="str">
         <f>CHOOSE(WEEKDAY(C63),"domingo","segunda","terça","quarta","quinta","sexta","sábado")</f>
-        <v>sábado</v>
+        <v>terça</v>
       </c>
       <c r="B63" s="25" t="n"/>
       <c r="C63" s="27">
         <f>Config!$B$5+5</f>
-        <v>46284.0</v>
+        <v>46287.0</v>
       </c>
       <c r="D63" s="25">
         <f>COUNTIFS(Prazos!$D$5:$D$404,C63,Prazos!$F$5:$F$404,"&lt;&gt;Sim")</f>
@@ -2642,12 +2642,12 @@
     <row r="64">
       <c r="A64" s="25" t="str">
         <f>CHOOSE(WEEKDAY(C64),"domingo","segunda","terça","quarta","quinta","sexta","sábado")</f>
-        <v>domingo</v>
+        <v>quarta</v>
       </c>
       <c r="B64" s="25" t="n"/>
       <c r="C64" s="27">
         <f>Config!$B$5+6</f>
-        <v>46285.0</v>
+        <v>46288.0</v>
       </c>
       <c r="D64" s="25">
         <f>COUNTIFS(Prazos!$D$5:$D$404,C64,Prazos!$F$5:$F$404,"&lt;&gt;Sim")</f>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="B5" s="32">
         <f>TODAY()</f>
-        <v>46279.0</v>
+        <v>46282.0</v>
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="D5" s="34">
         <f>TODAY()+9</f>
-        <v>46288.0</v>
+        <v>46291.0</v>
       </c>
       <c r="E5" s="33" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="D6" s="34">
         <f>TODAY()+2</f>
-        <v>46281.0</v>
+        <v>46284.0</v>
       </c>
       <c r="E6" s="33" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="D7" s="34">
         <f>TODAY()-3</f>
-        <v>46276.0</v>
+        <v>46279.0</v>
       </c>
       <c r="E7" s="33" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="D8" s="34">
         <f>TODAY()+6</f>
-        <v>46285.0</v>
+        <v>46288.0</v>
       </c>
       <c r="E8" s="33" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="D9" s="34">
         <f>TODAY()+4</f>
-        <v>46283.0</v>
+        <v>46286.0</v>
       </c>
       <c r="E9" s="33" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="D10" s="34">
         <f>TODAY()</f>
-        <v>46279.0</v>
+        <v>46282.0</v>
       </c>
       <c r="E10" s="33" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="D11" s="34">
         <f>TODAY()+3</f>
-        <v>46282.0</v>
+        <v>46285.0</v>
       </c>
       <c r="E11" s="33" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="D12" s="34">
         <f>TODAY()+9</f>
-        <v>46288.0</v>
+        <v>46291.0</v>
       </c>
       <c r="E12" s="33" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="D13" s="34">
         <f>TODAY()+15</f>
-        <v>46294.0</v>
+        <v>46297.0</v>
       </c>
       <c r="E13" s="33" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="D14" s="34">
         <f>TODAY()-1</f>
-        <v>46278.0</v>
+        <v>46281.0</v>
       </c>
       <c r="E14" s="33" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="D15" s="34">
         <f>TODAY()+8</f>
-        <v>46287.0</v>
+        <v>46290.0</v>
       </c>
       <c r="E15" s="33" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="D16" s="34">
         <f>TODAY()+5</f>
-        <v>46284.0</v>
+        <v>46287.0</v>
       </c>
       <c r="E16" s="33" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="D17" s="34">
         <f>TODAY()</f>
-        <v>46279.0</v>
+        <v>46282.0</v>
       </c>
       <c r="E17" s="33" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="D18" s="34">
         <f>TODAY()+4</f>
-        <v>46283.0</v>
+        <v>46286.0</v>
       </c>
       <c r="E18" s="33" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="D19" s="34">
         <f>TODAY()+20</f>
-        <v>46299.0</v>
+        <v>46302.0</v>
       </c>
       <c r="E19" s="33" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="D20" s="34">
         <f>TODAY()-5</f>
-        <v>46274.0</v>
+        <v>46277.0</v>
       </c>
       <c r="E20" s="33" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D21" s="34">
         <f>TODAY()</f>
-        <v>46279.0</v>
+        <v>46282.0</v>
       </c>
       <c r="E21" s="33" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="D22" s="34">
         <f>TODAY()-2</f>
-        <v>46277.0</v>
+        <v>46280.0</v>
       </c>
       <c r="E22" s="33" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="D23" s="34">
         <f>TODAY()+2</f>
-        <v>46281.0</v>
+        <v>46284.0</v>
       </c>
       <c r="E23" s="33" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="D24" s="34">
         <f>TODAY()-4</f>
-        <v>46275.0</v>
+        <v>46278.0</v>
       </c>
       <c r="E24" s="33" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="D25" s="34">
         <f>TODAY()+10</f>
-        <v>46289.0</v>
+        <v>46292.0</v>
       </c>
       <c r="E25" s="33" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="D26" s="34">
         <f>TODAY()+12</f>
-        <v>46291.0</v>
+        <v>46294.0</v>
       </c>
       <c r="E26" s="33" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="D27" s="34">
         <f>TODAY()-6</f>
-        <v>46273.0</v>
+        <v>46276.0</v>
       </c>
       <c r="E27" s="33" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="D28" s="34">
         <f>TODAY()+18</f>
-        <v>46297.0</v>
+        <v>46300.0</v>
       </c>
       <c r="E28" s="33" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="D29" s="34">
         <f>TODAY()+27</f>
-        <v>46306.0</v>
+        <v>46309.0</v>
       </c>
       <c r="E29" s="33" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="D30" s="34">
         <f>TODAY()+16</f>
-        <v>46295.0</v>
+        <v>46298.0</v>
       </c>
       <c r="E30" s="33" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="D31" s="34">
         <f>TODAY()+22</f>
-        <v>46301.0</v>
+        <v>46304.0</v>
       </c>
       <c r="E31" s="33" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
       </c>
       <c r="D32" s="34">
         <f>TODAY()+1</f>
-        <v>46280.0</v>
+        <v>46283.0</v>
       </c>
       <c r="E32" s="33" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="D33" s="34">
         <f>TODAY()+3</f>
-        <v>46282.0</v>
+        <v>46285.0</v>
       </c>
       <c r="E33" s="33" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="D34" s="34">
         <f>TODAY()-1</f>
-        <v>46278.0</v>
+        <v>46281.0</v>
       </c>
       <c r="E34" s="33" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="D35" s="34">
         <f>TODAY()+5</f>
-        <v>46284.0</v>
+        <v>46287.0</v>
       </c>
       <c r="E35" s="33" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="D36" s="34">
         <f>TODAY()+12</f>
-        <v>46291.0</v>
+        <v>46294.0</v>
       </c>
       <c r="E36" s="33" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="D37" s="34">
         <f>TODAY()+16</f>
-        <v>46295.0</v>
+        <v>46298.0</v>
       </c>
       <c r="E37" s="33" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="D38" s="34">
         <f>TODAY()+1</f>
-        <v>46280.0</v>
+        <v>46283.0</v>
       </c>
       <c r="E38" s="33" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="D39" s="34">
         <f>TODAY()+31</f>
-        <v>46310.0</v>
+        <v>46313.0</v>
       </c>
       <c r="E39" s="33" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
       </c>
       <c r="D40" s="34">
         <f>TODAY()+45</f>
-        <v>46324.0</v>
+        <v>46327.0</v>
       </c>
       <c r="E40" s="33" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="D41" s="34">
         <f>TODAY()-6</f>
-        <v>46273.0</v>
+        <v>46276.0</v>
       </c>
       <c r="E41" s="33" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="D42" s="34">
         <f>TODAY()-10</f>
-        <v>46269.0</v>
+        <v>46272.0</v>
       </c>
       <c r="E42" s="33" t="inlineStr">
         <is>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/01-agenda-de-prazos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/01-agenda-de-prazos.xlsx
@@ -21,8 +21,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -288,7 +289,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -299,14 +300,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -733,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -906,17 +907,29 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar. Datas de prazo do exemplo são relativas a hoje.</t>
+          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -954,7 +967,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="str">
         <f>Config!$B$4&amp;" · Painel de prazos · "&amp;TEXT(Config!$B$5,"dd/mm/yyyy")</f>
-        <v>Ferraz &amp; Lima Advocacia (exemplo fictício) · Painel de prazos · 17/09/2026</v>
+        <v>Ferraz &amp; Lima Advocacia (exemplo fictício) · Painel de prazos · 14/09/2026</v>
       </c>
     </row>
     <row r="2">
@@ -1106,7 +1119,7 @@
       </c>
       <c r="E10" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,1)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,1),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,1),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46276.0</v>
+        <v>46273.0</v>
       </c>
       <c r="F10" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,1)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,1),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,1),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1139,7 +1152,7 @@
       </c>
       <c r="E11" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,2)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,2),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,2),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46277.0</v>
+        <v>46274.0</v>
       </c>
       <c r="F11" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,2)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,2),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,2),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1172,7 +1185,7 @@
       </c>
       <c r="E12" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,3)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,3),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,3),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46278.0</v>
+        <v>46275.0</v>
       </c>
       <c r="F12" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,3)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,3),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,3),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1205,7 +1218,7 @@
       </c>
       <c r="E13" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,4)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,4),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,4),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46279.0</v>
+        <v>46276.0</v>
       </c>
       <c r="F13" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,4)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,4),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,4),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1238,7 +1251,7 @@
       </c>
       <c r="E14" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,5)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,5),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,5),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46280.0</v>
+        <v>46277.0</v>
       </c>
       <c r="F14" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,5)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,5),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,5),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1271,7 +1284,7 @@
       </c>
       <c r="E15" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,6)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,6),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,6),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46281.0</v>
+        <v>46278.0</v>
       </c>
       <c r="F15" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,6)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,6),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,6),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1304,7 +1317,7 @@
       </c>
       <c r="E16" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,7)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,7),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,7),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46281.0</v>
+        <v>46278.0</v>
       </c>
       <c r="F16" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,7)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,7),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,7),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1337,7 +1350,7 @@
       </c>
       <c r="E17" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,8)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,8),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,8),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46282.0</v>
+        <v>46279.0</v>
       </c>
       <c r="F17" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,8)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,8),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,8),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1370,7 +1383,7 @@
       </c>
       <c r="E18" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,9)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,9),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,9),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46282.0</v>
+        <v>46279.0</v>
       </c>
       <c r="F18" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,9)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,9),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,9),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1403,7 +1416,7 @@
       </c>
       <c r="E19" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,10)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,10),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,10),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46282.0</v>
+        <v>46279.0</v>
       </c>
       <c r="F19" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,10)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,10),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,10),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1436,7 +1449,7 @@
       </c>
       <c r="E20" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,11)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,11),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,11),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46283.0</v>
+        <v>46280.0</v>
       </c>
       <c r="F20" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,11)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,11),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,11),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1469,7 +1482,7 @@
       </c>
       <c r="E21" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,12)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,12),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,12),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46283.0</v>
+        <v>46280.0</v>
       </c>
       <c r="F21" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,12)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,12),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,12),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1502,7 +1515,7 @@
       </c>
       <c r="E22" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,13)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,13),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,13),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46284.0</v>
+        <v>46281.0</v>
       </c>
       <c r="F22" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,13)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,13),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,13),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1535,7 +1548,7 @@
       </c>
       <c r="E23" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,14)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,14),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,14),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46284.0</v>
+        <v>46281.0</v>
       </c>
       <c r="F23" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,14)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,14),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,14),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1568,7 +1581,7 @@
       </c>
       <c r="E24" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,15)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,15),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,15),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46285.0</v>
+        <v>46282.0</v>
       </c>
       <c r="F24" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,15)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,15),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,15),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1601,7 +1614,7 @@
       </c>
       <c r="E25" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,16)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,16),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,16),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46285.0</v>
+        <v>46282.0</v>
       </c>
       <c r="F25" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,16)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,16),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,16),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1634,7 +1647,7 @@
       </c>
       <c r="E26" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,17)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,17),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,17),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46286.0</v>
+        <v>46283.0</v>
       </c>
       <c r="F26" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,17)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,17),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,17),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1667,7 +1680,7 @@
       </c>
       <c r="E27" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,18)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,18),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,18),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46286.0</v>
+        <v>46283.0</v>
       </c>
       <c r="F27" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,18)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,18),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,18),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1700,7 +1713,7 @@
       </c>
       <c r="E28" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,19)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,19),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,19),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46287.0</v>
+        <v>46284.0</v>
       </c>
       <c r="F28" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,19)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,19),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,19),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1733,7 +1746,7 @@
       </c>
       <c r="E29" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,20)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,20),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,20),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46287.0</v>
+        <v>46284.0</v>
       </c>
       <c r="F29" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,20)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,20),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,20),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1766,7 +1779,7 @@
       </c>
       <c r="E30" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,21)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,21),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,21),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46288.0</v>
+        <v>46285.0</v>
       </c>
       <c r="F30" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,21)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,21),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,21),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1799,7 +1812,7 @@
       </c>
       <c r="E31" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,22)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,22),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,22),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46290.0</v>
+        <v>46287.0</v>
       </c>
       <c r="F31" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,22)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,22),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,22),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1832,7 +1845,7 @@
       </c>
       <c r="E32" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,23)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,23),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,23),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46291.0</v>
+        <v>46288.0</v>
       </c>
       <c r="F32" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,23)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,23),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,23),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1865,7 +1878,7 @@
       </c>
       <c r="E33" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,24)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,24),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,24),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46291.0</v>
+        <v>46288.0</v>
       </c>
       <c r="F33" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,24)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,24),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,24),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1898,7 +1911,7 @@
       </c>
       <c r="E34" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,25)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,25),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,25),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46292.0</v>
+        <v>46289.0</v>
       </c>
       <c r="F34" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,25)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,25),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,25),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1931,7 +1944,7 @@
       </c>
       <c r="E35" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,26)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,26),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,26),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46294.0</v>
+        <v>46291.0</v>
       </c>
       <c r="F35" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,26)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,26),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,26),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1964,7 +1977,7 @@
       </c>
       <c r="E36" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,27)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,27),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,27),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46294.0</v>
+        <v>46291.0</v>
       </c>
       <c r="F36" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,27)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,27),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,27),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -1997,7 +2010,7 @@
       </c>
       <c r="E37" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,28)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,28),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,28),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46297.0</v>
+        <v>46294.0</v>
       </c>
       <c r="F37" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,28)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,28),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,28),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -2030,7 +2043,7 @@
       </c>
       <c r="E38" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,29)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,29),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,29),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46298.0</v>
+        <v>46295.0</v>
       </c>
       <c r="F38" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,29)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,29),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,29),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -2063,7 +2076,7 @@
       </c>
       <c r="E39" s="27">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,30)&gt;0,IF(INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,30),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$D$5:$D$404,MATCH(LARGE(Prazos!$J$5:$J$404,30),Prazos!$J$5:$J$404,0))),""),"")</f>
-        <v>46298.0</v>
+        <v>46295.0</v>
       </c>
       <c r="F39" s="28">
         <f>IFERROR(IF(LARGE(Prazos!$J$5:$J$404,30)&gt;0,IF(INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,30),Prazos!$J$5:$J$404,0))="","",INDEX(Prazos!$H$5:$H$404,MATCH(LARGE(Prazos!$J$5:$J$404,30),Prazos!$J$5:$J$404,0))),""),"")</f>
@@ -2147,7 +2160,7 @@
       </c>
       <c r="G43" s="27">
         <f>IF(Config!$B$10="","",IFERROR(IF(SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$10)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$10)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))&gt;=1E+10,"",SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$10)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$10)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))),""))</f>
-        <v>46279.0</v>
+        <v>46276.0</v>
       </c>
       <c r="H43" s="25">
         <f>IF(Config!$B$10="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$10,Prazos!$I$5:$I$404,"Feito"))</f>
@@ -2178,7 +2191,7 @@
       </c>
       <c r="G44" s="27">
         <f>IF(Config!$B$11="","",IFERROR(IF(SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$11)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$11)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))&gt;=1E+10,"",SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$11)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$11)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))),""))</f>
-        <v>46277.0</v>
+        <v>46274.0</v>
       </c>
       <c r="H44" s="25">
         <f>IF(Config!$B$11="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$11,Prazos!$I$5:$I$404,"Feito"))</f>
@@ -2209,7 +2222,7 @@
       </c>
       <c r="G45" s="27">
         <f>IF(Config!$B$12="","",IFERROR(IF(SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$12)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$12)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))&gt;=1E+10,"",SUMPRODUCT(MIN(((Prazos!$E$5:$E$404=Config!$B$12)*(Prazos!$J$5:$J$404&gt;0))*Prazos!$D$5:$D$404+(1-((Prazos!$E$5:$E$404=Config!$B$12)*(Prazos!$J$5:$J$404&gt;0)))*1E+10))),""))</f>
-        <v>46276.0</v>
+        <v>46273.0</v>
       </c>
       <c r="H45" s="25">
         <f>IF(Config!$B$12="","",COUNTIFS(Prazos!$E$5:$E$404,Config!$B$12,Prazos!$I$5:$I$404,"Feito"))</f>
@@ -2480,12 +2493,12 @@
     <row r="58">
       <c r="A58" s="25" t="str">
         <f>CHOOSE(WEEKDAY(C58),"domingo","segunda","terça","quarta","quinta","sexta","sábado")</f>
-        <v>quinta</v>
+        <v>segunda</v>
       </c>
       <c r="B58" s="25" t="n"/>
       <c r="C58" s="27">
         <f>Config!$B$5+0</f>
-        <v>46282.0</v>
+        <v>46279.0</v>
       </c>
       <c r="D58" s="25">
         <f>COUNTIFS(Prazos!$D$5:$D$404,C58,Prazos!$F$5:$F$404,"&lt;&gt;Sim")</f>
@@ -2507,12 +2520,12 @@
     <row r="59">
       <c r="A59" s="25" t="str">
         <f>CHOOSE(WEEKDAY(C59),"domingo","segunda","terça","quarta","quinta","sexta","sábado")</f>
-        <v>sexta</v>
+        <v>terça</v>
       </c>
       <c r="B59" s="25" t="n"/>
       <c r="C59" s="27">
         <f>Config!$B$5+1</f>
-        <v>46283.0</v>
+        <v>46280.0</v>
       </c>
       <c r="D59" s="25">
         <f>COUNTIFS(Prazos!$D$5:$D$404,C59,Prazos!$F$5:$F$404,"&lt;&gt;Sim")</f>
@@ -2534,12 +2547,12 @@
     <row r="60">
       <c r="A60" s="25" t="str">
         <f>CHOOSE(WEEKDAY(C60),"domingo","segunda","terça","quarta","quinta","sexta","sábado")</f>
-        <v>sábado</v>
+        <v>quarta</v>
       </c>
       <c r="B60" s="25" t="n"/>
       <c r="C60" s="27">
         <f>Config!$B$5+2</f>
-        <v>46284.0</v>
+        <v>46281.0</v>
       </c>
       <c r="D60" s="25">
         <f>COUNTIFS(Prazos!$D$5:$D$404,C60,Prazos!$F$5:$F$404,"&lt;&gt;Sim")</f>
@@ -2561,12 +2574,12 @@
     <row r="61">
       <c r="A61" s="25" t="str">
         <f>CHOOSE(WEEKDAY(C61),"domingo","segunda","terça","quarta","quinta","sexta","sábado")</f>
-        <v>domingo</v>
+        <v>quinta</v>
       </c>
       <c r="B61" s="25" t="n"/>
       <c r="C61" s="27">
         <f>Config!$B$5+3</f>
-        <v>46285.0</v>
+        <v>46282.0</v>
       </c>
       <c r="D61" s="25">
         <f>COUNTIFS(Prazos!$D$5:$D$404,C61,Prazos!$F$5:$F$404,"&lt;&gt;Sim")</f>
@@ -2588,12 +2601,12 @@
     <row r="62">
       <c r="A62" s="25" t="str">
         <f>CHOOSE(WEEKDAY(C62),"domingo","segunda","terça","quarta","quinta","sexta","sábado")</f>
-        <v>segunda</v>
+        <v>sexta</v>
       </c>
       <c r="B62" s="25" t="n"/>
       <c r="C62" s="27">
         <f>Config!$B$5+4</f>
-        <v>46286.0</v>
+        <v>46283.0</v>
       </c>
       <c r="D62" s="25">
         <f>COUNTIFS(Prazos!$D$5:$D$404,C62,Prazos!$F$5:$F$404,"&lt;&gt;Sim")</f>
@@ -2615,12 +2628,12 @@
     <row r="63">
       <c r="A63" s="25" t="str">
         <f>CHOOSE(WEEKDAY(C63),"domingo","segunda","terça","quarta","quinta","sexta","sábado")</f>
-        <v>terça</v>
+        <v>sábado</v>
       </c>
       <c r="B63" s="25" t="n"/>
       <c r="C63" s="27">
         <f>Config!$B$5+5</f>
-        <v>46287.0</v>
+        <v>46284.0</v>
       </c>
       <c r="D63" s="25">
         <f>COUNTIFS(Prazos!$D$5:$D$404,C63,Prazos!$F$5:$F$404,"&lt;&gt;Sim")</f>
@@ -2642,12 +2655,12 @@
     <row r="64">
       <c r="A64" s="25" t="str">
         <f>CHOOSE(WEEKDAY(C64),"domingo","segunda","terça","quarta","quinta","sexta","sábado")</f>
-        <v>quarta</v>
+        <v>domingo</v>
       </c>
       <c r="B64" s="25" t="n"/>
       <c r="C64" s="27">
         <f>Config!$B$5+6</f>
-        <v>46288.0</v>
+        <v>46285.0</v>
       </c>
       <c r="D64" s="25">
         <f>COUNTIFS(Prazos!$D$5:$D$404,C64,Prazos!$F$5:$F$404,"&lt;&gt;Sim")</f>
@@ -2785,9 +2798,8 @@
           <t>Data de referência (hoje)</t>
         </is>
       </c>
-      <c r="B5" s="32">
-        <f>TODAY()</f>
-        <v>46282.0</v>
+      <c r="B5" s="32" t="n">
+        <v>46279</v>
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
@@ -3129,9 +3141,8 @@
           <t>Reunião com cliente</t>
         </is>
       </c>
-      <c r="D5" s="34">
-        <f>TODAY()+9</f>
-        <v>46291.0</v>
+      <c r="D5" s="34" t="n">
+        <v>46288</v>
       </c>
       <c r="E5" s="33" t="inlineStr">
         <is>
@@ -3173,9 +3184,8 @@
           <t>Audiência de conciliação</t>
         </is>
       </c>
-      <c r="D6" s="34">
-        <f>TODAY()+2</f>
-        <v>46284.0</v>
+      <c r="D6" s="34" t="n">
+        <v>46281</v>
       </c>
       <c r="E6" s="33" t="inlineStr">
         <is>
@@ -3217,9 +3227,8 @@
           <t>Réplica</t>
         </is>
       </c>
-      <c r="D7" s="34">
-        <f>TODAY()-3</f>
-        <v>46279.0</v>
+      <c r="D7" s="34" t="n">
+        <v>46276</v>
       </c>
       <c r="E7" s="33" t="inlineStr">
         <is>
@@ -3261,9 +3270,8 @@
           <t>Juntada de documentos</t>
         </is>
       </c>
-      <c r="D8" s="34">
-        <f>TODAY()+6</f>
-        <v>46288.0</v>
+      <c r="D8" s="34" t="n">
+        <v>46285</v>
       </c>
       <c r="E8" s="33" t="inlineStr">
         <is>
@@ -3305,9 +3313,8 @@
           <t>Entrega de parecer</t>
         </is>
       </c>
-      <c r="D9" s="34">
-        <f>TODAY()+4</f>
-        <v>46286.0</v>
+      <c r="D9" s="34" t="n">
+        <v>46283</v>
       </c>
       <c r="E9" s="33" t="inlineStr">
         <is>
@@ -3349,9 +3356,8 @@
           <t>Entrega de parecer</t>
         </is>
       </c>
-      <c r="D10" s="34">
-        <f>TODAY()</f>
-        <v>46282.0</v>
+      <c r="D10" s="34" t="n">
+        <v>46279</v>
       </c>
       <c r="E10" s="33" t="inlineStr">
         <is>
@@ -3393,9 +3399,8 @@
           <t>Reunião com cliente</t>
         </is>
       </c>
-      <c r="D11" s="34">
-        <f>TODAY()+3</f>
-        <v>46285.0</v>
+      <c r="D11" s="34" t="n">
+        <v>46282</v>
       </c>
       <c r="E11" s="33" t="inlineStr">
         <is>
@@ -3437,9 +3442,8 @@
           <t>Audiência de instrução</t>
         </is>
       </c>
-      <c r="D12" s="34">
-        <f>TODAY()+9</f>
-        <v>46291.0</v>
+      <c r="D12" s="34" t="n">
+        <v>46288</v>
       </c>
       <c r="E12" s="33" t="inlineStr">
         <is>
@@ -3481,9 +3485,8 @@
           <t>Cumprimento de sentença</t>
         </is>
       </c>
-      <c r="D13" s="34">
-        <f>TODAY()+15</f>
-        <v>46297.0</v>
+      <c r="D13" s="34" t="n">
+        <v>46294</v>
       </c>
       <c r="E13" s="33" t="inlineStr">
         <is>
@@ -3521,9 +3524,8 @@
           <t>Embargos de declaração</t>
         </is>
       </c>
-      <c r="D14" s="34">
-        <f>TODAY()-1</f>
-        <v>46281.0</v>
+      <c r="D14" s="34" t="n">
+        <v>46278</v>
       </c>
       <c r="E14" s="33" t="inlineStr">
         <is>
@@ -3565,9 +3567,8 @@
           <t>Contrarrazões</t>
         </is>
       </c>
-      <c r="D15" s="34">
-        <f>TODAY()+8</f>
-        <v>46290.0</v>
+      <c r="D15" s="34" t="n">
+        <v>46287</v>
       </c>
       <c r="E15" s="33" t="inlineStr">
         <is>
@@ -3605,9 +3606,8 @@
           <t>Reunião com cliente</t>
         </is>
       </c>
-      <c r="D16" s="34">
-        <f>TODAY()+5</f>
-        <v>46287.0</v>
+      <c r="D16" s="34" t="n">
+        <v>46284</v>
       </c>
       <c r="E16" s="33" t="inlineStr">
         <is>
@@ -3649,9 +3649,8 @@
           <t>Contestação</t>
         </is>
       </c>
-      <c r="D17" s="34">
-        <f>TODAY()</f>
-        <v>46282.0</v>
+      <c r="D17" s="34" t="n">
+        <v>46279</v>
       </c>
       <c r="E17" s="33" t="inlineStr">
         <is>
@@ -3693,9 +3692,8 @@
           <t>Manifestação sobre laudo</t>
         </is>
       </c>
-      <c r="D18" s="34">
-        <f>TODAY()+4</f>
-        <v>46286.0</v>
+      <c r="D18" s="34" t="n">
+        <v>46283</v>
       </c>
       <c r="E18" s="33" t="inlineStr">
         <is>
@@ -3737,9 +3735,8 @@
           <t>Audiência de conciliação</t>
         </is>
       </c>
-      <c r="D19" s="34">
-        <f>TODAY()+20</f>
-        <v>46302.0</v>
+      <c r="D19" s="34" t="n">
+        <v>46299</v>
       </c>
       <c r="E19" s="33" t="inlineStr">
         <is>
@@ -3777,9 +3774,8 @@
           <t>Reunião com cliente</t>
         </is>
       </c>
-      <c r="D20" s="34">
-        <f>TODAY()-5</f>
-        <v>46277.0</v>
+      <c r="D20" s="34" t="n">
+        <v>46274</v>
       </c>
       <c r="E20" s="33" t="inlineStr">
         <is>
@@ -3821,9 +3817,8 @@
           <t>Minuta de acordo</t>
         </is>
       </c>
-      <c r="D21" s="34">
-        <f>TODAY()</f>
-        <v>46282.0</v>
+      <c r="D21" s="34" t="n">
+        <v>46279</v>
       </c>
       <c r="E21" s="33" t="inlineStr">
         <is>
@@ -3865,9 +3860,8 @@
           <t>Impugnação</t>
         </is>
       </c>
-      <c r="D22" s="34">
-        <f>TODAY()-2</f>
-        <v>46280.0</v>
+      <c r="D22" s="34" t="n">
+        <v>46277</v>
       </c>
       <c r="E22" s="33" t="inlineStr">
         <is>
@@ -3909,9 +3903,8 @@
           <t>Recurso de apelação</t>
         </is>
       </c>
-      <c r="D23" s="34">
-        <f>TODAY()+2</f>
-        <v>46284.0</v>
+      <c r="D23" s="34" t="n">
+        <v>46281</v>
       </c>
       <c r="E23" s="33" t="inlineStr">
         <is>
@@ -3953,9 +3946,8 @@
           <t>Manifestação sobre laudo</t>
         </is>
       </c>
-      <c r="D24" s="34">
-        <f>TODAY()-4</f>
-        <v>46278.0</v>
+      <c r="D24" s="34" t="n">
+        <v>46275</v>
       </c>
       <c r="E24" s="33" t="inlineStr">
         <is>
@@ -3997,9 +3989,8 @@
           <t>Alegações finais</t>
         </is>
       </c>
-      <c r="D25" s="34">
-        <f>TODAY()+10</f>
-        <v>46292.0</v>
+      <c r="D25" s="34" t="n">
+        <v>46289</v>
       </c>
       <c r="E25" s="33" t="inlineStr">
         <is>
@@ -4037,9 +4028,8 @@
           <t>Audiência de conciliação</t>
         </is>
       </c>
-      <c r="D26" s="34">
-        <f>TODAY()+12</f>
-        <v>46294.0</v>
+      <c r="D26" s="34" t="n">
+        <v>46291</v>
       </c>
       <c r="E26" s="33" t="inlineStr">
         <is>
@@ -4077,9 +4067,8 @@
           <t>Juntada de documentos</t>
         </is>
       </c>
-      <c r="D27" s="34">
-        <f>TODAY()-6</f>
-        <v>46276.0</v>
+      <c r="D27" s="34" t="n">
+        <v>46273</v>
       </c>
       <c r="E27" s="33" t="inlineStr">
         <is>
@@ -4121,9 +4110,8 @@
           <t>Homologação do acordo</t>
         </is>
       </c>
-      <c r="D28" s="34">
-        <f>TODAY()+18</f>
-        <v>46300.0</v>
+      <c r="D28" s="34" t="n">
+        <v>46297</v>
       </c>
       <c r="E28" s="33" t="inlineStr">
         <is>
@@ -4165,9 +4153,8 @@
           <t>Contrarrazões</t>
         </is>
       </c>
-      <c r="D29" s="34">
-        <f>TODAY()+27</f>
-        <v>46309.0</v>
+      <c r="D29" s="34" t="n">
+        <v>46306</v>
       </c>
       <c r="E29" s="33" t="inlineStr">
         <is>
@@ -4205,9 +4192,8 @@
           <t>Entrega de parecer</t>
         </is>
       </c>
-      <c r="D30" s="34">
-        <f>TODAY()+16</f>
-        <v>46298.0</v>
+      <c r="D30" s="34" t="n">
+        <v>46295</v>
       </c>
       <c r="E30" s="33" t="inlineStr">
         <is>
@@ -4249,9 +4235,8 @@
           <t>Cumprimento de sentença</t>
         </is>
       </c>
-      <c r="D31" s="34">
-        <f>TODAY()+22</f>
-        <v>46304.0</v>
+      <c r="D31" s="34" t="n">
+        <v>46301</v>
       </c>
       <c r="E31" s="33" t="inlineStr">
         <is>
@@ -4289,9 +4274,8 @@
           <t>Réplica</t>
         </is>
       </c>
-      <c r="D32" s="34">
-        <f>TODAY()+1</f>
-        <v>46283.0</v>
+      <c r="D32" s="34" t="n">
+        <v>46280</v>
       </c>
       <c r="E32" s="33" t="inlineStr">
         <is>
@@ -4329,9 +4313,8 @@
           <t>Embargos de declaração</t>
         </is>
       </c>
-      <c r="D33" s="34">
-        <f>TODAY()+3</f>
-        <v>46285.0</v>
+      <c r="D33" s="34" t="n">
+        <v>46282</v>
       </c>
       <c r="E33" s="33" t="inlineStr">
         <is>
@@ -4369,9 +4352,8 @@
           <t>Manifestação sobre o recurso</t>
         </is>
       </c>
-      <c r="D34" s="34">
-        <f>TODAY()-1</f>
-        <v>46281.0</v>
+      <c r="D34" s="34" t="n">
+        <v>46278</v>
       </c>
       <c r="E34" s="33" t="inlineStr">
         <is>
@@ -4413,9 +4395,8 @@
           <t>Juntada de documentos</t>
         </is>
       </c>
-      <c r="D35" s="34">
-        <f>TODAY()+5</f>
-        <v>46287.0</v>
+      <c r="D35" s="34" t="n">
+        <v>46284</v>
       </c>
       <c r="E35" s="33" t="inlineStr">
         <is>
@@ -4457,9 +4438,8 @@
           <t>Reunião com cliente</t>
         </is>
       </c>
-      <c r="D36" s="34">
-        <f>TODAY()+12</f>
-        <v>46294.0</v>
+      <c r="D36" s="34" t="n">
+        <v>46291</v>
       </c>
       <c r="E36" s="33" t="inlineStr">
         <is>
@@ -4501,9 +4481,8 @@
           <t>Juntada de documentos</t>
         </is>
       </c>
-      <c r="D37" s="34">
-        <f>TODAY()+16</f>
-        <v>46298.0</v>
+      <c r="D37" s="34" t="n">
+        <v>46295</v>
       </c>
       <c r="E37" s="33" t="inlineStr">
         <is>
@@ -4545,9 +4524,8 @@
           <t>Prazo interno</t>
         </is>
       </c>
-      <c r="D38" s="34">
-        <f>TODAY()+1</f>
-        <v>46283.0</v>
+      <c r="D38" s="34" t="n">
+        <v>46280</v>
       </c>
       <c r="E38" s="33" t="inlineStr">
         <is>
@@ -4589,9 +4567,8 @@
           <t>Reunião com cliente</t>
         </is>
       </c>
-      <c r="D39" s="34">
-        <f>TODAY()+31</f>
-        <v>46313.0</v>
+      <c r="D39" s="34" t="n">
+        <v>46310</v>
       </c>
       <c r="E39" s="33" t="inlineStr">
         <is>
@@ -4633,9 +4610,8 @@
           <t>Juntada de documentos</t>
         </is>
       </c>
-      <c r="D40" s="34">
-        <f>TODAY()+45</f>
-        <v>46327.0</v>
+      <c r="D40" s="34" t="n">
+        <v>46324</v>
       </c>
       <c r="E40" s="33" t="inlineStr">
         <is>
@@ -4677,9 +4653,8 @@
           <t>Juntada de documentos</t>
         </is>
       </c>
-      <c r="D41" s="34">
-        <f>TODAY()-6</f>
-        <v>46276.0</v>
+      <c r="D41" s="34" t="n">
+        <v>46273</v>
       </c>
       <c r="E41" s="33" t="inlineStr">
         <is>
@@ -4725,9 +4700,8 @@
           <t>Reunião com cliente</t>
         </is>
       </c>
-      <c r="D42" s="34">
-        <f>TODAY()-10</f>
-        <v>46272.0</v>
+      <c r="D42" s="34" t="n">
+        <v>46269</v>
       </c>
       <c r="E42" s="33" t="inlineStr">
         <is>
@@ -12381,16 +12355,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation sqref="C5:C404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$D$10,0,0,MAX(1,COUNTA(Config!$D$10:$D$29)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$B$10,0,0,MAX(1,COUNTA(Config!$B$10:$B$19)),1)</formula1>
     </dataValidation>
     <dataValidation sqref="F5:F404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Sim"</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:D404" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="D5:D404" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" operator="greaterThan">
       <formula1>1</formula1>
     </dataValidation>
   </dataValidations>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/01-agenda-de-prazos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/01-agenda-de-prazos.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Em Config, confira a data de referência (fica em =HOJE()), cadastre as pessoas do escritório e ajuste a lista de tipos de prazo. Preencha de cima para baixo, sem pular linha.</t>
+          <t>Em Config, troque a data de referência por =HOJE() (no exemplo ela está congelada em 14/09/2026), cadastre as pessoas do escritório e ajuste a lista de tipos de prazo. Preencha de cima para baixo, sem pular linha.</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>Deixe =HOJE() para acompanhar o dia; troque por uma data para simular outro dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para os arquivos do kit mostrarem a mesma foto. Ao usar com os seus dados, troque por =HOJE().</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/01-agenda-de-prazos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/01-agenda-de-prazos.xlsx
@@ -895,7 +895,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/01-agenda-de-prazos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/01-agenda-de-prazos.xlsx
@@ -966,7 +966,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="str">
-        <f>Config!$B$4&amp;" · Painel de prazos · "&amp;TEXT(Config!$B$5,"dd/mm/yyyy")</f>
+        <f>Config!$B$4&amp;" · Painel de prazos · "&amp;TEXT(DAY(Config!$B$5),"00")&amp;"/"&amp;TEXT(MONTH(Config!$B$5),"00")&amp;"/"&amp;YEAR(Config!$B$5)</f>
         <v>Ferraz &amp; Lima Advocacia (exemplo fictício) · Painel de prazos · 14/09/2026</v>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/01-agenda-de-prazos.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/01-agenda-de-prazos.xlsx
@@ -755,6 +755,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -895,7 +896,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e semáforos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
